--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Публикации" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Канал_по_дням" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подписчики" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Публикации" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Канал_по_дням" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Подписчики" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Публикации'!$A$1:$P$1</definedName>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1011</v>
+        <v>1025</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P83"/>
+  <dimension ref="A1:P111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5840,6 +5840,1686 @@
         <v>14.81</v>
       </c>
       <c r="P83" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E84" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H84" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D85" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E85" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F85" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="G85" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E86" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F86" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="G86" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H86" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I86" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J86" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="P86" s="19" t="n">
+        <v>66.67</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D87" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E87" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F87" s="21" t="n">
+        <v>95</v>
+      </c>
+      <c r="G87" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H87" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L87" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="23" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="P87" s="23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E88" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="G88" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H88" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P88" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D89" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E89" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F89" s="21" t="n">
+        <v>70</v>
+      </c>
+      <c r="G89" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H89" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I89" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O89" s="23" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P89" s="23" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E90" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="G90" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H90" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L90" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="19" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="P90" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D91" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E91" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F91" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G91" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H91" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O91" s="23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P91" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E92" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F92" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="G92" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D93" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E93" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F93" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="G93" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H93" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D94" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E94" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G94" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H94" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D95" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E95" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F95" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="G95" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H95" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P95" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D96" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E96" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F96" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G96" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H96" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D97" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E97" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F97" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G97" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H97" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D98" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E98" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F98" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="G98" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H98" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D99" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E99" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F99" s="21" t="n">
+        <v>65</v>
+      </c>
+      <c r="G99" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H99" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I99" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J99" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K99" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O99" s="23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P99" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D100" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E100" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F100" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G100" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H100" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I100" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J100" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O100" s="19" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="P100" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D101" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E101" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F101" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="G101" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H101" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L101" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O101" s="23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P101" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D102" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E102" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F102" s="17" t="n">
+        <v>56</v>
+      </c>
+      <c r="G102" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="19" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P102" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D103" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E103" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F103" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G103" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H103" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L103" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P103" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D104" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E104" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F104" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G104" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H104" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L104" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D105" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E105" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F105" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G105" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D106" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E106" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F106" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G106" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H106" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I106" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O106" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P106" s="19" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D107" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E107" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F107" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G107" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H107" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O107" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P107" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D108" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E108" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F108" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="G108" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H108" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L108" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O108" s="19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P108" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D109" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E109" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F109" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G109" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H109" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L109" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P109" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D110" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E110" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F110" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G110" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H110" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="19" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="P110" s="19" t="n">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D111" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E111" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F111" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="G111" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H111" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I111" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J111" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O111" s="23" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="P111" s="23" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4"/>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1025</v>
+        <v>1088</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P111"/>
+  <dimension ref="A1:P140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7523,6 +7523,1746 @@
         <v>26.67</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D112" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E112" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F112" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D113" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E113" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="G113" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H113" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="23" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="P113" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D114" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E114" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F114" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="G114" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H114" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P114" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D115" s="20" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E115" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F115" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="G115" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="H115" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I115" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J115" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L115" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="P115" s="23" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D116" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E116" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F116" s="17" t="n">
+        <v>101</v>
+      </c>
+      <c r="G116" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H116" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L116" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="19" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="P116" s="19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D117" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E117" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F117" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="G117" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H117" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L117" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P117" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D118" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E118" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F118" s="17" t="n">
+        <v>73</v>
+      </c>
+      <c r="G118" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H118" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I118" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J118" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L118" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O118" s="19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P118" s="19" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D119" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E119" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F119" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G119" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H119" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I119" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L119" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="23" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="P119" s="23" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D120" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E120" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F120" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G120" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H120" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I120" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L120" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O120" s="19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P120" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D121" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E121" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F121" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="G121" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D122" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E122" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F122" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G122" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H122" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D123" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E123" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F123" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="G123" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H123" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L123" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D124" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E124" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F124" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G124" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H124" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L124" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P124" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D125" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E125" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F125" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G125" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H125" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L125" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D126" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E126" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F126" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G126" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D127" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E127" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F127" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="G127" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H127" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L127" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D128" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E128" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F128" s="17" t="n">
+        <v>69</v>
+      </c>
+      <c r="G128" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H128" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I128" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J128" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L128" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" s="29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O128" s="19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P128" s="19" t="n">
+        <v>45.45</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D129" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E129" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F129" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G129" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H129" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I129" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J129" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O129" s="23" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="P129" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D130" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E130" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F130" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="G130" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H130" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J130" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L130" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" s="29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O130" s="19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P130" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D131" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E131" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F131" s="21" t="n">
+        <v>56</v>
+      </c>
+      <c r="G131" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P131" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D132" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E132" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F132" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="G132" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H132" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L132" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" s="19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P132" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D133" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E133" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F133" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="G133" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H133" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L133" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D134" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E134" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F134" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G134" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H134" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L134" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D135" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E135" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F135" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G135" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H135" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I135" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J135" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L135" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O135" s="23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P135" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C136" s="8" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D136" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E136" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F136" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G136" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H136" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I136" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L136" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O136" s="19" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P136" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D137" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E137" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F137" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="G137" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H137" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L137" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O137" s="23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="P137" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C138" s="8" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D138" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E138" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F138" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G138" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H138" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L138" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" s="19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P138" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D139" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E139" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F139" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="G139" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H139" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L139" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" s="23" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="P139" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C140" s="8" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D140" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E140" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F140" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="G140" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H140" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I140" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J140" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K140" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L140" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O140" s="19" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="P140" s="19" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7535,7 +9275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8402,6 +10142,34 @@
         <v>0</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="C31" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="D31" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8414,7 +10182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8816,6 +10584,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="C31" s="33" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P140"/>
+  <dimension ref="A1:P169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9260,6 +9260,1746 @@
         <v>14.55</v>
       </c>
       <c r="P140" s="19" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D141" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E141" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F141" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D142" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E142" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F142" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="G142" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H142" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" s="23" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="P142" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D143" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E143" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F143" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="G143" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H143" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" s="19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P143" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C144" s="11" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D144" s="20" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E144" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F144" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="G144" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="H144" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I144" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J144" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L144" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="P144" s="23" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D145" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E145" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F145" s="17" t="n">
+        <v>101</v>
+      </c>
+      <c r="G145" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H145" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L145" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" s="19" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="P145" s="19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D146" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E146" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F146" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="G146" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H146" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P146" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D147" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E147" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F147" s="17" t="n">
+        <v>73</v>
+      </c>
+      <c r="G147" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H147" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I147" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J147" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L147" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O147" s="19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P147" s="19" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C148" s="11" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D148" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E148" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F148" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G148" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H148" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L148" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" s="23" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="P148" s="23" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D149" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E149" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F149" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G149" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H149" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I149" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J149" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L149" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" s="29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O149" s="19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P149" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B150" s="11" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C150" s="11" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D150" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E150" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F150" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="G150" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H150" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L150" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B151" s="8" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C151" s="8" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D151" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E151" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F151" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G151" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H151" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L151" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C152" s="11" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D152" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E152" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F152" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="G152" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H152" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L152" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D153" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E153" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F153" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G153" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P153" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C154" s="11" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D154" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E154" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F154" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G154" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H154" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L154" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D155" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E155" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F155" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G155" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H155" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L155" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B156" s="11" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C156" s="11" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D156" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E156" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F156" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="G156" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H156" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I156" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L156" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B157" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C157" s="8" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D157" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E157" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F157" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="G157" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H157" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I157" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J157" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K157" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L157" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" s="29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O157" s="19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P157" s="19" t="n">
+        <v>45.45</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B158" s="11" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C158" s="11" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D158" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E158" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F158" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G158" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H158" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I158" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J158" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L158" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O158" s="23" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="P158" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B159" s="8" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D159" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E159" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F159" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="G159" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H159" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I159" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J159" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L159" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" s="29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O159" s="19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P159" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B160" s="11" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C160" s="11" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D160" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E160" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F160" s="21" t="n">
+        <v>56</v>
+      </c>
+      <c r="G160" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H160" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L160" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P160" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B161" s="8" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C161" s="8" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D161" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E161" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F161" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="G161" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H161" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L161" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" s="19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P161" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B162" s="11" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C162" s="11" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D162" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E162" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F162" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="G162" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H162" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L162" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B163" s="8" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C163" s="8" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D163" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E163" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F163" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G163" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H163" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L163" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B164" s="11" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C164" s="11" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D164" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E164" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F164" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G164" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H164" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I164" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J164" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L164" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O164" s="23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P164" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D165" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E165" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F165" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G165" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H165" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L165" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O165" s="19" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P165" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B166" s="11" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C166" s="11" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D166" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E166" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F166" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="G166" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H166" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I166" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J166" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L166" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O166" s="23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="P166" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D167" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E167" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F167" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G167" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H167" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L167" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" s="19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P167" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B168" s="11" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C168" s="11" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D168" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E168" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F168" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="G168" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H168" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I168" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L168" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" s="23" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="P168" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D169" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E169" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F169" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="G169" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H169" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I169" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J169" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K169" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L169" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O169" s="19" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="P169" s="19" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P169"/>
+  <dimension ref="A1:P198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11000,6 +11000,1746 @@
         <v>14.55</v>
       </c>
       <c r="P169" s="19" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C170" s="8" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D170" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E170" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F170" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B171" s="11" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C171" s="11" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D171" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E171" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F171" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="G171" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H171" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" s="23" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="P171" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C172" s="8" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D172" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E172" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F172" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="G172" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H172" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" s="19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P172" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B173" s="11" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C173" s="11" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D173" s="20" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E173" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F173" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="G173" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="H173" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I173" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J173" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L173" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="P173" s="23" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C174" s="8" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D174" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E174" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F174" s="17" t="n">
+        <v>101</v>
+      </c>
+      <c r="G174" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H174" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I174" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J174" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L174" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" s="19" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="P174" s="19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C175" s="11" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D175" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E175" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F175" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="G175" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H175" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I175" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L175" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P175" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B176" s="8" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C176" s="8" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D176" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E176" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F176" s="17" t="n">
+        <v>73</v>
+      </c>
+      <c r="G176" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H176" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I176" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J176" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L176" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O176" s="19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P176" s="19" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B177" s="11" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C177" s="11" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D177" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E177" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F177" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G177" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H177" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I177" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L177" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" s="23" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="P177" s="23" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B178" s="8" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C178" s="8" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D178" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E178" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F178" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G178" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H178" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I178" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J178" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L178" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" s="29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O178" s="19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P178" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B179" s="11" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C179" s="11" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D179" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E179" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F179" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="G179" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H179" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L179" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B180" s="8" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C180" s="8" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D180" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E180" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F180" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G180" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H180" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L180" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B181" s="11" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C181" s="11" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D181" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E181" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F181" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="G181" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H181" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L181" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C182" s="8" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D182" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E182" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F182" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G182" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H182" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L182" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P182" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B183" s="11" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C183" s="11" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D183" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E183" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F183" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G183" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H183" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L183" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B184" s="8" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C184" s="8" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D184" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E184" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F184" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G184" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H184" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I184" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L184" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M184" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B185" s="11" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C185" s="11" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D185" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E185" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F185" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="G185" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H185" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I185" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J185" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L185" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O185" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B186" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C186" s="8" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D186" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E186" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F186" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="G186" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H186" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I186" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J186" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K186" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L186" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" s="29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O186" s="19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P186" s="19" t="n">
+        <v>45.45</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B187" s="11" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C187" s="11" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D187" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E187" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F187" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G187" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H187" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I187" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J187" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L187" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O187" s="23" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="P187" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B188" s="8" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C188" s="8" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D188" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E188" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F188" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="G188" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H188" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I188" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J188" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L188" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" s="29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O188" s="19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P188" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B189" s="11" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C189" s="11" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D189" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E189" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F189" s="21" t="n">
+        <v>56</v>
+      </c>
+      <c r="G189" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H189" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L189" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P189" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B190" s="8" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C190" s="8" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D190" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E190" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F190" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="G190" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H190" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L190" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" s="19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P190" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B191" s="11" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C191" s="11" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D191" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E191" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F191" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="G191" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H191" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L191" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B192" s="8" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C192" s="8" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D192" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E192" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F192" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G192" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H192" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L192" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B193" s="11" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C193" s="11" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D193" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E193" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F193" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G193" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H193" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I193" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J193" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L193" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O193" s="23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P193" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B194" s="8" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C194" s="8" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D194" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E194" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F194" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G194" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H194" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I194" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J194" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L194" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O194" s="19" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P194" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B195" s="11" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C195" s="11" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D195" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E195" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F195" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="G195" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H195" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I195" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J195" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L195" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O195" s="23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="P195" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B196" s="8" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C196" s="8" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D196" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E196" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F196" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G196" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H196" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I196" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J196" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L196" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" s="19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P196" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B197" s="11" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C197" s="11" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D197" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E197" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F197" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="G197" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H197" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J197" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L197" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" s="23" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="P197" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B198" s="8" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C198" s="8" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D198" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E198" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F198" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="G198" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H198" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I198" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J198" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K198" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L198" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O198" s="19" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="P198" s="19" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4"/>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1089</v>
+        <v>1123</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12740,6 +12740,1806 @@
         <v>14.55</v>
       </c>
       <c r="P198" s="19" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B199" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C199" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D199" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E199" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F199" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G199" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H199" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I199" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J199" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B200" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C200" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D200" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E200" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F200" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G200" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H200" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P200" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B201" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C201" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D201" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E201" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F201" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="G201" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H201" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" s="19" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="P201" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B202" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C202" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D202" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E202" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F202" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G202" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H202" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" s="23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P202" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B203" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C203" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D203" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E203" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F203" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G203" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H203" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I203" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J203" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L203" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" s="19" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="P203" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B204" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C204" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D204" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E204" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F204" s="21" t="n">
+        <v>103</v>
+      </c>
+      <c r="G204" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H204" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I204" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J204" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L204" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M204" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" s="23" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="P204" s="23" t="n">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B205" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C205" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D205" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E205" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F205" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="G205" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H205" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I205" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J205" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L205" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M205" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" s="19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P205" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B206" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C206" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D206" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E206" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F206" s="21" t="n">
+        <v>74</v>
+      </c>
+      <c r="G206" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H206" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I206" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J206" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L206" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M206" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O206" s="23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P206" s="23" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B207" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C207" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D207" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E207" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F207" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="G207" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H207" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I207" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J207" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L207" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" s="19" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="P207" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B208" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C208" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D208" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E208" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F208" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G208" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H208" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I208" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J208" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L208" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O208" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P208" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B209" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C209" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D209" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E209" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F209" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="G209" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H209" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L209" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B210" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C210" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D210" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E210" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F210" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="G210" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H210" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L210" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B211" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C211" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D211" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E211" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F211" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G211" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H211" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L211" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B212" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C212" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D212" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E212" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F212" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G212" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H212" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L212" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P212" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B213" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C213" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D213" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E213" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F213" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G213" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H213" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L213" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B214" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C214" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D214" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E214" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F214" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G214" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H214" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L214" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B215" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C215" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D215" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E215" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F215" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G215" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H215" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I215" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J215" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B216" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C216" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D216" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E216" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F216" s="21" t="n">
+        <v>74</v>
+      </c>
+      <c r="G216" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H216" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I216" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J216" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K216" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L216" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O216" s="23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P216" s="23" t="n">
+        <v>45.45</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B217" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C217" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D217" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E217" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F217" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G217" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H217" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I217" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J217" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L217" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O217" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P217" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B218" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C218" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D218" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E218" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F218" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="G218" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H218" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I218" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J218" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L218" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O218" s="23" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="P218" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B219" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C219" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D219" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E219" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F219" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G219" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H219" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I219" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L219" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P219" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B220" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C220" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D220" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E220" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F220" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G220" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H220" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L220" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O220" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P220" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B221" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C221" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D221" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E221" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F221" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G221" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H221" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L221" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B222" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C222" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D222" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E222" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F222" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G222" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H222" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L222" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B223" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C223" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D223" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E223" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F223" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G223" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="H223" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I223" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J223" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L223" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O223" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P223" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B224" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C224" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D224" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E224" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F224" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G224" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H224" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I224" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J224" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L224" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O224" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P224" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B225" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C225" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D225" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E225" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F225" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G225" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H225" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I225" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J225" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L225" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O225" s="19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P225" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B226" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C226" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D226" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E226" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F226" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G226" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H226" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I226" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J226" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L226" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P226" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D227" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E227" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F227" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="G227" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H227" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I227" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J227" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L227" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" s="19" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="P227" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B228" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C228" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D228" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E228" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F228" s="21" t="n">
+        <v>56</v>
+      </c>
+      <c r="G228" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H228" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I228" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J228" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K228" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L228" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O228" s="23" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P228" s="23" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4"/>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1123</v>
+        <v>1180</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P228"/>
+  <dimension ref="A1:P260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14543,6 +14543,1926 @@
         <v>26.67</v>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C229" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D229" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E229" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F229" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G229" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H229" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I229" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N229" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O229" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B230" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C230" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D230" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E230" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F230" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="G230" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H230" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J230" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B231" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C231" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D231" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E231" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F231" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G231" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H231" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I231" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J231" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L231" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N231" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O231" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B232" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C232" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D232" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E232" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F232" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G232" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H232" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I232" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J232" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L232" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M232" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N232" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O232" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C233" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D233" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E233" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F233" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G233" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H233" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M233" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N233" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O233" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="P233" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B234" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C234" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D234" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E234" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F234" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G234" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H234" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I234" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M234" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N234" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P234" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B235" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C235" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D235" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E235" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F235" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G235" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H235" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I235" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J235" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L235" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M235" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N235" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" s="19" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="P235" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B236" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C236" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D236" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E236" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F236" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G236" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H236" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I236" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J236" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L236" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M236" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N236" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O236" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P236" s="23" t="n">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B237" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C237" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D237" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E237" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F237" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G237" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H237" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I237" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J237" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L237" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M237" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N237" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O237" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P237" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B238" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C238" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D238" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E238" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F238" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="G238" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H238" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I238" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J238" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L238" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M238" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N238" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O238" s="23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P238" s="23" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B239" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C239" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D239" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E239" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F239" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G239" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H239" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I239" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J239" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L239" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N239" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O239" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P239" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B240" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C240" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D240" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E240" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F240" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="G240" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H240" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I240" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J240" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L240" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M240" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N240" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O240" s="23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P240" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B241" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C241" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D241" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E241" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F241" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="G241" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H241" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I241" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L241" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M241" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N241" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P241" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B242" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C242" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D242" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E242" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F242" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G242" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H242" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I242" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L242" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M242" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N242" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O242" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P242" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B243" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C243" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D243" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E243" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F243" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G243" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H243" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L243" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M243" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N243" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P243" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B244" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C244" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D244" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E244" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F244" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G244" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H244" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I244" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L244" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M244" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N244" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P244" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B245" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C245" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D245" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E245" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F245" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G245" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H245" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I245" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L245" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M245" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N245" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O245" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P245" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B246" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C246" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D246" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E246" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F246" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G246" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H246" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I246" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L246" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M246" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N246" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O246" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P246" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B247" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C247" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D247" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E247" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F247" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G247" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H247" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I247" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J247" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L247" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M247" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N247" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O247" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P247" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B248" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C248" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D248" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E248" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F248" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="G248" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H248" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I248" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J248" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K248" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L248" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M248" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N248" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O248" s="23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P248" s="23" t="n">
+        <v>45.45</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B249" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C249" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D249" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E249" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F249" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G249" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H249" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I249" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J249" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L249" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M249" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N249" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O249" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P249" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B250" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C250" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D250" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E250" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F250" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G250" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H250" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I250" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J250" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L250" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M250" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N250" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O250" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P250" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B251" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C251" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D251" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E251" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F251" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G251" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H251" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I251" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L251" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M251" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N251" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O251" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P251" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B252" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C252" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D252" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E252" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F252" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G252" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H252" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I252" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L252" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M252" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N252" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O252" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P252" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B253" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C253" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D253" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E253" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F253" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G253" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H253" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I253" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K253" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L253" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M253" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N253" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O253" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P253" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B254" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C254" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D254" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E254" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F254" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G254" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H254" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I254" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L254" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M254" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N254" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O254" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B255" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C255" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D255" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E255" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F255" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G255" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H255" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I255" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J255" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L255" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M255" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N255" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O255" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P255" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B256" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C256" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D256" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E256" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F256" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G256" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H256" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I256" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J256" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L256" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M256" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N256" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O256" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P256" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B257" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C257" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D257" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E257" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F257" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="G257" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H257" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I257" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J257" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L257" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M257" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N257" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O257" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P257" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B258" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C258" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D258" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E258" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F258" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G258" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H258" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I258" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J258" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L258" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M258" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N258" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O258" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P258" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B259" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C259" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D259" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E259" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F259" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="G259" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H259" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I259" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J259" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L259" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M259" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N259" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" s="19" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="P259" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B260" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C260" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D260" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E260" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F260" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G260" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H260" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I260" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J260" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K260" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L260" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M260" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N260" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O260" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P260" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14555,7 +16475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15450,6 +17370,34 @@
         <v>0</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15462,7 +17410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15877,6 +17825,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="C32" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P260"/>
+  <dimension ref="A1:P292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16460,6 +16460,1926 @@
         <v>14.04</v>
       </c>
       <c r="P260" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B261" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C261" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D261" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E261" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F261" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G261" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H261" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L261" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M261" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N261" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O261" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P261" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B262" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C262" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D262" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E262" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F262" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="G262" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H262" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I262" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J262" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L262" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M262" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N262" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O262" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P262" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B263" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C263" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D263" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E263" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F263" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G263" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H263" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I263" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J263" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L263" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M263" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N263" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O263" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P263" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B264" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C264" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D264" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E264" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F264" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G264" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H264" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I264" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J264" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M264" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N264" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B265" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C265" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D265" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E265" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F265" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G265" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H265" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L265" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M265" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N265" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O265" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="P265" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B266" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C266" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D266" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E266" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F266" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G266" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H266" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L266" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M266" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N266" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O266" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P266" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B267" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C267" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D267" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E267" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F267" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G267" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H267" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I267" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J267" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L267" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M267" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N267" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O267" s="19" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="P267" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B268" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C268" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D268" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E268" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F268" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G268" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H268" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I268" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J268" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L268" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M268" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N268" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O268" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P268" s="23" t="n">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B269" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C269" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D269" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E269" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F269" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G269" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H269" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I269" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J269" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L269" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M269" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N269" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P269" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B270" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C270" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D270" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E270" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F270" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="G270" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H270" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I270" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J270" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L270" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M270" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N270" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O270" s="23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P270" s="23" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B271" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C271" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D271" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E271" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F271" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G271" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H271" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I271" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J271" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L271" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M271" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N271" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O271" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P271" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B272" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C272" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D272" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E272" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F272" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="G272" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H272" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I272" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J272" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L272" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M272" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N272" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O272" s="23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P272" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B273" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C273" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D273" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E273" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F273" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="G273" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H273" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I273" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K273" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L273" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M273" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N273" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O273" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P273" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B274" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C274" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D274" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E274" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F274" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G274" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H274" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I274" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K274" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L274" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M274" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N274" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O274" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P274" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B275" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C275" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D275" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E275" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F275" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G275" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H275" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L275" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M275" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N275" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O275" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P275" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B276" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C276" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D276" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E276" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F276" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G276" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H276" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I276" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L276" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M276" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N276" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O276" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P276" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B277" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C277" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D277" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E277" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F277" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G277" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H277" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I277" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J277" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L277" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M277" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N277" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O277" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P277" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B278" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C278" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D278" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E278" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F278" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G278" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H278" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L278" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M278" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B279" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C279" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D279" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E279" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F279" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G279" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H279" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I279" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J279" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K279" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L279" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M279" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N279" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P279" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B280" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C280" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D280" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E280" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F280" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="G280" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H280" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I280" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J280" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K280" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L280" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M280" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O280" s="23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P280" s="23" t="n">
+        <v>45.45</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B281" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C281" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D281" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E281" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F281" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G281" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H281" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I281" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J281" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K281" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L281" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M281" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N281" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O281" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P281" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B282" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C282" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D282" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E282" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F282" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G282" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H282" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I282" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J282" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K282" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L282" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M282" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N282" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O282" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P282" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B283" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C283" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D283" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E283" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F283" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G283" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H283" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I283" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K283" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L283" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M283" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N283" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P283" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B284" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C284" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D284" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E284" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F284" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G284" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H284" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I284" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K284" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L284" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M284" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N284" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O284" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P284" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B285" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C285" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D285" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E285" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F285" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G285" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H285" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I285" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L285" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M285" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N285" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O285" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P285" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B286" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C286" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D286" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E286" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F286" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G286" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H286" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I286" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K286" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L286" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M286" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N286" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O286" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P286" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B287" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C287" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D287" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E287" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F287" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G287" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H287" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I287" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J287" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K287" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L287" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M287" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N287" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O287" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P287" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B288" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C288" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D288" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E288" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F288" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G288" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H288" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I288" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J288" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K288" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L288" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M288" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N288" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O288" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P288" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B289" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C289" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D289" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E289" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F289" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="G289" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H289" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I289" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J289" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L289" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M289" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N289" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O289" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P289" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B290" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C290" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D290" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E290" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F290" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G290" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H290" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I290" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J290" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K290" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L290" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M290" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N290" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O290" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P290" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B291" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C291" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D291" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E291" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F291" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="G291" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H291" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I291" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J291" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L291" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M291" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N291" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O291" s="19" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="P291" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B292" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C292" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D292" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E292" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F292" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G292" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H292" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I292" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J292" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K292" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L292" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M292" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N292" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O292" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P292" s="23" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1181</v>
+        <v>1208</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P292"/>
+  <dimension ref="A1:P324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18380,6 +18380,1926 @@
         <v>14.04</v>
       </c>
       <c r="P292" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B293" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C293" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D293" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E293" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F293" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G293" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H293" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I293" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J293" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K293" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L293" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M293" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N293" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O293" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P293" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B294" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C294" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D294" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E294" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F294" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="G294" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H294" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I294" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J294" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K294" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L294" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M294" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N294" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P294" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B295" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C295" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D295" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E295" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F295" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G295" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H295" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I295" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J295" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L295" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M295" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N295" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O295" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P295" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B296" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C296" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D296" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E296" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F296" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G296" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H296" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I296" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J296" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L296" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M296" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N296" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P296" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B297" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C297" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D297" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E297" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F297" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G297" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H297" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I297" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K297" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L297" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M297" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N297" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O297" s="19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P297" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B298" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C298" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D298" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E298" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F298" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G298" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H298" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I298" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L298" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M298" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N298" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O298" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P298" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B299" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C299" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D299" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E299" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F299" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G299" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H299" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I299" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J299" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L299" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M299" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N299" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O299" s="19" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="P299" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B300" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C300" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D300" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E300" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F300" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G300" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H300" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I300" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J300" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L300" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M300" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N300" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O300" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P300" s="23" t="n">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B301" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C301" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D301" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E301" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F301" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G301" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H301" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I301" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J301" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L301" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M301" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N301" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O301" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P301" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B302" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C302" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D302" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E302" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F302" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="G302" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H302" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I302" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J302" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L302" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M302" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N302" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O302" s="23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P302" s="23" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B303" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C303" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D303" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E303" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F303" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G303" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H303" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I303" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J303" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K303" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L303" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M303" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N303" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O303" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P303" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B304" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C304" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D304" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E304" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F304" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="G304" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H304" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I304" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J304" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K304" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L304" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M304" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N304" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O304" s="23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P304" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B305" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C305" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D305" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E305" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F305" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="G305" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H305" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I305" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L305" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M305" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N305" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O305" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P305" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B306" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C306" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D306" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E306" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F306" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G306" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H306" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I306" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J306" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K306" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L306" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M306" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N306" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O306" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P306" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B307" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C307" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D307" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E307" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F307" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G307" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H307" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I307" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J307" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K307" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L307" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M307" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N307" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O307" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P307" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B308" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C308" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D308" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E308" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F308" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G308" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H308" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K308" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L308" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M308" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N308" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O308" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P308" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B309" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C309" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D309" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E309" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F309" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G309" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H309" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K309" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L309" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M309" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N309" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O309" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P309" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B310" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C310" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D310" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E310" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F310" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G310" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H310" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I310" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J310" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K310" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L310" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M310" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N310" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O310" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P310" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B311" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C311" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D311" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E311" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F311" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G311" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H311" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I311" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J311" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L311" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M311" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N311" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O311" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P311" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B312" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C312" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D312" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E312" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F312" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="G312" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H312" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I312" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J312" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K312" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L312" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M312" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N312" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O312" s="23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P312" s="23" t="n">
+        <v>45.45</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B313" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C313" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D313" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E313" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F313" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G313" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H313" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I313" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J313" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K313" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L313" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M313" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N313" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O313" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P313" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B314" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C314" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D314" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E314" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F314" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G314" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H314" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I314" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J314" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K314" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L314" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M314" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N314" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O314" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P314" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B315" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C315" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D315" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E315" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F315" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G315" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H315" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I315" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K315" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L315" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M315" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N315" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O315" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P315" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B316" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C316" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D316" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E316" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F316" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G316" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H316" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I316" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J316" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K316" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L316" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M316" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N316" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O316" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P316" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B317" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C317" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D317" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E317" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F317" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G317" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H317" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I317" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K317" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L317" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M317" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N317" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O317" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P317" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B318" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C318" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D318" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E318" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F318" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G318" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H318" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I318" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K318" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L318" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M318" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N318" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O318" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P318" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B319" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C319" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D319" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E319" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F319" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G319" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H319" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I319" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J319" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K319" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L319" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M319" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N319" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O319" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P319" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B320" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C320" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D320" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E320" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F320" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G320" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H320" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I320" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J320" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K320" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L320" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M320" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N320" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O320" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P320" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B321" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C321" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D321" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E321" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F321" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="G321" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H321" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I321" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J321" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K321" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L321" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M321" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N321" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O321" s="19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P321" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B322" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C322" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D322" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E322" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F322" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G322" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H322" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I322" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J322" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K322" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L322" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M322" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N322" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O322" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P322" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B323" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C323" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D323" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E323" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F323" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="G323" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H323" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I323" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J323" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K323" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L323" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M323" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N323" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O323" s="19" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="P323" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B324" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C324" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D324" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E324" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F324" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G324" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H324" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I324" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J324" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K324" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L324" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M324" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N324" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O324" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P324" s="23" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1208</v>
+        <v>1242</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="B14" s="27" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P324"/>
+  <dimension ref="A1:P356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20303,6 +20303,1926 @@
         <v>26.67</v>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B325" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C325" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D325" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E325" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F325" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G325" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H325" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I325" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J325" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K325" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L325" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M325" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N325" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O325" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P325" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B326" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C326" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D326" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E326" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F326" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G326" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H326" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I326" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J326" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K326" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L326" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M326" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N326" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O326" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P326" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B327" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C327" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D327" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E327" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F327" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G327" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H327" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I327" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J327" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K327" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L327" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M327" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N327" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O327" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P327" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B328" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C328" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D328" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E328" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F328" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G328" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H328" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I328" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J328" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K328" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L328" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M328" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N328" s="30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O328" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P328" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B329" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C329" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D329" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E329" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F329" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G329" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H329" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I329" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J329" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K329" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L329" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M329" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N329" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O329" s="19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P329" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B330" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C330" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D330" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E330" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F330" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G330" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H330" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I330" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K330" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L330" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M330" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N330" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O330" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P330" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B331" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C331" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D331" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E331" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F331" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G331" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H331" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I331" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J331" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K331" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L331" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M331" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N331" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O331" s="19" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="P331" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B332" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C332" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D332" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E332" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F332" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G332" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H332" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I332" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J332" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K332" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L332" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M332" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N332" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O332" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P332" s="23" t="n">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B333" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C333" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D333" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E333" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F333" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G333" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H333" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I333" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J333" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K333" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L333" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M333" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N333" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O333" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P333" s="19" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B334" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C334" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D334" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E334" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F334" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="G334" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H334" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I334" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J334" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K334" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L334" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M334" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N334" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O334" s="23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P334" s="23" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B335" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C335" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D335" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E335" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F335" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G335" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H335" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I335" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J335" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K335" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L335" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M335" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N335" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O335" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P335" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B336" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C336" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D336" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E336" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F336" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="G336" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H336" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I336" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J336" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K336" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L336" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M336" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N336" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O336" s="23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P336" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B337" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C337" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D337" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E337" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F337" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G337" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H337" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I337" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J337" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K337" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L337" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M337" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N337" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O337" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P337" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B338" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C338" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D338" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E338" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F338" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G338" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H338" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I338" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J338" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K338" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L338" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M338" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N338" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O338" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P338" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B339" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C339" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D339" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E339" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F339" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G339" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H339" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I339" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J339" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K339" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L339" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M339" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N339" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O339" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P339" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B340" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C340" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D340" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E340" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F340" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G340" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H340" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I340" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J340" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K340" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L340" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M340" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N340" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O340" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P340" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B341" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C341" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D341" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E341" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F341" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G341" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H341" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I341" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K341" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L341" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M341" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N341" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O341" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P341" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B342" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C342" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D342" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E342" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F342" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G342" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H342" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I342" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J342" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K342" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L342" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M342" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N342" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O342" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P342" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B343" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C343" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D343" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E343" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F343" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G343" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H343" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I343" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J343" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K343" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L343" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M343" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N343" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O343" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P343" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B344" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C344" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D344" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E344" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F344" s="21" t="n">
+        <v>76</v>
+      </c>
+      <c r="G344" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H344" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I344" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J344" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K344" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L344" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M344" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N344" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O344" s="23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P344" s="23" t="n">
+        <v>45.45</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B345" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C345" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D345" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E345" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F345" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G345" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H345" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I345" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J345" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K345" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L345" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M345" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N345" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O345" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P345" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B346" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C346" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D346" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E346" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F346" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G346" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H346" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I346" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J346" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K346" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L346" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M346" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N346" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O346" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P346" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B347" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C347" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D347" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E347" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F347" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G347" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H347" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I347" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J347" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K347" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L347" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M347" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N347" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O347" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P347" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B348" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C348" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D348" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E348" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F348" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G348" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H348" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I348" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J348" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K348" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L348" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M348" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N348" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O348" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P348" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B349" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C349" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D349" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E349" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F349" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G349" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H349" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I349" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J349" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K349" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L349" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M349" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N349" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O349" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P349" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B350" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C350" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D350" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E350" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F350" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G350" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H350" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I350" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J350" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K350" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L350" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M350" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N350" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O350" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P350" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B351" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C351" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D351" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E351" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F351" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G351" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H351" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I351" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J351" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K351" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L351" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M351" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N351" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O351" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P351" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B352" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C352" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D352" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E352" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F352" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G352" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H352" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I352" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J352" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K352" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L352" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M352" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N352" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O352" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P352" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B353" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C353" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D353" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E353" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F353" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="G353" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H353" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I353" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J353" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K353" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L353" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M353" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N353" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O353" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P353" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B354" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C354" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D354" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E354" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F354" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G354" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H354" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I354" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J354" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K354" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L354" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M354" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N354" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O354" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P354" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B355" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C355" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D355" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E355" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F355" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G355" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H355" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I355" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J355" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K355" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L355" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M355" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N355" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O355" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P355" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B356" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C356" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D356" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E356" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F356" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G356" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H356" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I356" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J356" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K356" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L356" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M356" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N356" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O356" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P356" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20315,7 +22235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21238,6 +23158,34 @@
         <v>0</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="C33" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21250,7 +23198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21678,6 +23626,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="C33" s="33" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4"/>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1242</v>
+        <v>1263</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P356"/>
+  <dimension ref="A1:P391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22220,6 +22220,2106 @@
         <v>14.04</v>
       </c>
       <c r="P356" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B357" s="8" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C357" s="8" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D357" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E357" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F357" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G357" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H357" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I357" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J357" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K357" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L357" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M357" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N357" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O357" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="P357" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B358" s="11" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C358" s="11" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D358" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E358" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F358" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G358" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H358" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I358" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J358" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K358" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L358" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M358" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N358" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O358" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P358" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B359" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C359" s="8" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D359" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E359" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F359" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G359" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H359" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I359" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J359" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K359" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L359" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M359" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N359" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O359" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P359" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B360" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C360" s="11" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D360" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E360" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F360" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G360" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H360" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I360" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J360" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K360" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L360" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M360" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N360" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O360" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P360" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B361" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C361" s="8" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D361" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E361" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F361" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G361" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H361" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I361" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J361" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K361" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L361" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M361" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N361" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O361" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P361" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B362" s="11" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C362" s="11" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D362" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E362" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F362" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="G362" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H362" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I362" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J362" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K362" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L362" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M362" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N362" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O362" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P362" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B363" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C363" s="8" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D363" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E363" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F363" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G363" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H363" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I363" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J363" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K363" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L363" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M363" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N363" s="29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O363" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P363" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B364" s="11" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C364" s="11" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D364" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E364" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F364" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="G364" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H364" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I364" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J364" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K364" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L364" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M364" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N364" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O364" s="23" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P364" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B365" s="8" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C365" s="8" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D365" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E365" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F365" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G365" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H365" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I365" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J365" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K365" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L365" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M365" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N365" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O365" s="19" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P365" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B366" s="11" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C366" s="11" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D366" s="20" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E366" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F366" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="G366" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H366" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I366" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J366" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K366" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L366" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M366" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N366" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O366" s="23" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="P366" s="23" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B367" s="8" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C367" s="8" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D367" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E367" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F367" s="17" t="n">
+        <v>105</v>
+      </c>
+      <c r="G367" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H367" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I367" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J367" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K367" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L367" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M367" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N367" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O367" s="19" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P367" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B368" s="11" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C368" s="11" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D368" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E368" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F368" s="21" t="n">
+        <v>84</v>
+      </c>
+      <c r="G368" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H368" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I368" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J368" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K368" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L368" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M368" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N368" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O368" s="23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P368" s="23" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B369" s="8" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C369" s="8" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D369" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E369" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F369" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="G369" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H369" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I369" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J369" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K369" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L369" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M369" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N369" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O369" s="19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P369" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B370" s="11" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C370" s="11" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D370" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E370" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F370" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="G370" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H370" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I370" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J370" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K370" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L370" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M370" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N370" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O370" s="23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P370" s="23" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B371" s="8" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C371" s="8" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D371" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E371" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F371" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G371" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H371" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I371" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J371" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K371" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L371" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M371" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N371" s="29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O371" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P371" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B372" s="11" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C372" s="11" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D372" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E372" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F372" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="G372" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H372" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I372" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J372" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K372" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L372" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M372" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N372" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O372" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P372" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B373" s="8" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C373" s="8" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D373" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E373" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F373" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="G373" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H373" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I373" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J373" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K373" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L373" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M373" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N373" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O373" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P373" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B374" s="11" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C374" s="11" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D374" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E374" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F374" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="G374" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H374" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I374" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J374" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K374" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L374" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M374" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N374" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O374" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P374" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B375" s="8" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C375" s="8" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D375" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E375" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F375" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="G375" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H375" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I375" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J375" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K375" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L375" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M375" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N375" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O375" s="19" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P375" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B376" s="11" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C376" s="11" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D376" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E376" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F376" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G376" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H376" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I376" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J376" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K376" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L376" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M376" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N376" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O376" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P376" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B377" s="8" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C377" s="8" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D377" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E377" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F377" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G377" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H377" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I377" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J377" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K377" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L377" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M377" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N377" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O377" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P377" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B378" s="11" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C378" s="11" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D378" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E378" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F378" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="G378" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H378" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I378" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J378" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K378" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L378" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M378" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N378" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O378" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P378" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B379" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C379" s="8" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D379" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E379" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F379" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="G379" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H379" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I379" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J379" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K379" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L379" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M379" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N379" s="29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O379" s="19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P379" s="19" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B380" s="11" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C380" s="11" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D380" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E380" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F380" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G380" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H380" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I380" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J380" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K380" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L380" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M380" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N380" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O380" s="23" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P380" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B381" s="8" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C381" s="8" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D381" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E381" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F381" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="G381" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H381" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I381" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J381" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K381" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L381" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M381" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N381" s="29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O381" s="19" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P381" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B382" s="11" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C382" s="11" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D382" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E382" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F382" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G382" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H382" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I382" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J382" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K382" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L382" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M382" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N382" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O382" s="23" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P382" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B383" s="8" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C383" s="8" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D383" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E383" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F383" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="G383" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H383" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I383" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J383" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K383" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L383" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M383" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N383" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O383" s="19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P383" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B384" s="11" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C384" s="11" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D384" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E384" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F384" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="G384" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H384" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I384" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J384" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K384" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L384" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M384" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N384" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O384" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P384" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B385" s="8" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C385" s="8" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D385" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E385" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F385" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G385" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H385" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I385" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J385" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K385" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L385" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M385" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N385" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O385" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P385" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B386" s="11" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C386" s="11" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D386" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E386" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F386" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G386" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H386" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I386" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J386" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K386" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L386" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M386" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N386" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O386" s="23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P386" s="23" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B387" s="8" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C387" s="8" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D387" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E387" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F387" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G387" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H387" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I387" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J387" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K387" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L387" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M387" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N387" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O387" s="19" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P387" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B388" s="11" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C388" s="11" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D388" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E388" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F388" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="G388" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H388" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I388" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J388" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K388" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L388" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M388" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N388" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O388" s="23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P388" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B389" s="8" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C389" s="8" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D389" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E389" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F389" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G389" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H389" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I389" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J389" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K389" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L389" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M389" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N389" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O389" s="19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P389" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B390" s="11" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C390" s="11" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D390" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E390" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F390" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="G390" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H390" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I390" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J390" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K390" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L390" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M390" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N390" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O390" s="23" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P390" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B391" s="8" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C391" s="8" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D391" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E391" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F391" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G391" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H391" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I391" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J391" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K391" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L391" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M391" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N391" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O391" s="19" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P391" s="19" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4"/>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1263</v>
+        <v>1296</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P391"/>
+  <dimension ref="A1:P431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24320,6 +24320,2406 @@
         <v>14.04</v>
       </c>
       <c r="P391" s="19" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B392" s="8" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C392" s="8" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D392" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E392" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F392" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G392" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H392" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I392" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J392" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K392" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L392" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M392" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N392" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O392" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P392" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B393" s="11" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C393" s="11" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D393" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E393" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F393" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G393" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H393" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I393" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J393" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K393" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L393" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M393" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N393" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O393" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P393" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B394" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C394" s="8" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D394" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E394" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F394" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G394" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H394" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I394" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J394" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K394" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L394" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M394" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N394" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O394" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P394" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B395" s="11" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C395" s="11" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D395" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E395" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F395" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G395" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H395" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I395" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J395" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K395" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L395" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M395" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N395" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O395" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P395" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B396" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C396" s="8" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D396" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E396" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F396" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G396" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H396" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I396" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J396" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K396" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L396" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M396" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N396" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O396" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P396" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B397" s="11" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C397" s="11" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D397" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E397" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F397" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G397" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H397" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I397" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J397" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K397" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L397" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M397" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N397" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O397" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="P397" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B398" s="8" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C398" s="8" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D398" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E398" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F398" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G398" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H398" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I398" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J398" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K398" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L398" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M398" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N398" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O398" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P398" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B399" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C399" s="11" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D399" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E399" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F399" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G399" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H399" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I399" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J399" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K399" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L399" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M399" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N399" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O399" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P399" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B400" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C400" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D400" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E400" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F400" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G400" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H400" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I400" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J400" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K400" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L400" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M400" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N400" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O400" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P400" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B401" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C401" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D401" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E401" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F401" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G401" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H401" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I401" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J401" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K401" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L401" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M401" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N401" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O401" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P401" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B402" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C402" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D402" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E402" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F402" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="G402" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H402" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I402" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J402" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K402" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L402" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M402" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N402" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O402" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P402" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B403" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C403" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D403" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E403" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F403" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G403" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H403" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I403" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J403" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K403" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L403" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M403" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N403" s="30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O403" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P403" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B404" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C404" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D404" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E404" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F404" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G404" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H404" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I404" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J404" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K404" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L404" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M404" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N404" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O404" s="19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P404" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B405" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C405" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D405" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E405" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F405" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G405" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H405" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I405" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J405" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K405" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L405" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M405" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N405" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O405" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P405" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B406" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C406" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D406" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E406" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F406" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G406" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="H406" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I406" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J406" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K406" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L406" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M406" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N406" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O406" s="19" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="P406" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B407" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C407" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D407" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E407" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F407" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G407" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H407" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I407" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J407" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K407" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L407" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M407" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N407" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O407" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P407" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B408" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C408" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D408" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E408" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F408" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G408" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H408" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I408" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J408" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K408" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L408" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M408" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N408" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O408" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P408" s="19" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B409" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C409" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D409" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E409" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F409" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="G409" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H409" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I409" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J409" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K409" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L409" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M409" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N409" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O409" s="23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P409" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B410" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C410" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D410" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E410" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F410" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G410" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H410" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I410" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J410" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K410" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L410" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M410" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N410" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O410" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P410" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B411" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C411" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D411" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E411" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F411" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="G411" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H411" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I411" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J411" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K411" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L411" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M411" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N411" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O411" s="23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P411" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B412" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C412" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D412" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E412" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F412" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G412" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H412" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I412" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J412" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K412" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L412" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M412" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N412" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O412" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P412" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B413" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C413" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D413" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E413" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F413" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G413" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H413" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I413" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J413" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K413" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L413" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M413" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N413" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O413" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P413" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B414" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C414" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D414" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E414" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F414" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G414" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H414" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I414" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J414" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K414" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L414" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M414" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N414" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O414" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P414" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B415" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C415" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D415" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E415" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F415" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G415" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H415" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I415" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J415" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K415" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L415" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M415" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N415" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O415" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P415" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B416" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C416" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D416" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E416" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F416" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G416" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H416" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I416" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J416" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K416" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L416" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M416" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N416" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O416" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P416" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B417" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C417" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D417" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E417" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F417" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G417" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H417" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I417" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J417" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K417" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L417" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M417" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N417" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O417" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P417" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B418" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C418" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D418" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E418" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F418" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G418" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H418" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I418" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J418" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K418" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L418" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M418" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N418" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O418" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P418" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B419" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C419" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D419" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E419" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F419" s="21" t="n">
+        <v>77</v>
+      </c>
+      <c r="G419" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H419" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I419" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J419" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K419" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L419" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M419" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N419" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O419" s="23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P419" s="23" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B420" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C420" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D420" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E420" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F420" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G420" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H420" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I420" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J420" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K420" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L420" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M420" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N420" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O420" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P420" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B421" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C421" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D421" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E421" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F421" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G421" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H421" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I421" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J421" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K421" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L421" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M421" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N421" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O421" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P421" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B422" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C422" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D422" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E422" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F422" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G422" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H422" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I422" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J422" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K422" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L422" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M422" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N422" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O422" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P422" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B423" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C423" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D423" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E423" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F423" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G423" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H423" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I423" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J423" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K423" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L423" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M423" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N423" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O423" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P423" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B424" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C424" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D424" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E424" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F424" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G424" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H424" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I424" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J424" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K424" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L424" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M424" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N424" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O424" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P424" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B425" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C425" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D425" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E425" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F425" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G425" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H425" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I425" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J425" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K425" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L425" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M425" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N425" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O425" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P425" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B426" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C426" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D426" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E426" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F426" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G426" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H426" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I426" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J426" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K426" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L426" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M426" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N426" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O426" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P426" s="19" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B427" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C427" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D427" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E427" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F427" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G427" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H427" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I427" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J427" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K427" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L427" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M427" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N427" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O427" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P427" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B428" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C428" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D428" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E428" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F428" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="G428" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H428" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I428" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J428" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K428" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L428" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M428" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N428" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O428" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P428" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B429" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C429" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D429" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E429" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F429" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G429" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H429" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I429" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J429" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K429" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L429" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M429" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N429" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O429" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P429" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B430" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C430" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D430" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E430" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F430" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G430" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H430" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I430" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J430" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K430" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L430" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M430" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N430" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O430" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P430" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B431" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C431" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D431" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E431" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F431" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G431" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H431" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I431" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J431" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K431" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L431" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M431" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N431" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O431" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P431" s="23" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4"/>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1296</v>
+        <v>1307</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P431"/>
+  <dimension ref="A1:P473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -26720,6 +26720,2526 @@
         <v>14.04</v>
       </c>
       <c r="P431" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B432" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C432" s="8" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D432" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E432" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F432" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G432" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H432" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I432" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J432" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K432" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L432" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M432" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N432" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O432" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P432" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B433" s="11" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C433" s="11" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D433" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E433" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F433" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G433" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H433" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I433" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J433" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K433" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L433" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M433" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N433" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O433" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P433" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B434" s="8" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C434" s="8" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D434" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E434" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F434" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G434" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H434" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I434" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J434" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K434" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L434" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M434" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N434" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O434" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P434" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B435" s="11" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C435" s="11" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D435" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E435" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F435" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G435" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H435" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I435" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J435" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K435" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L435" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M435" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N435" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O435" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P435" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B436" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C436" s="8" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D436" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E436" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F436" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G436" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H436" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I436" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J436" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K436" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L436" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M436" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N436" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O436" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P436" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B437" s="11" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C437" s="11" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D437" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E437" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F437" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G437" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H437" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I437" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J437" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K437" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L437" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M437" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N437" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O437" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P437" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B438" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C438" s="8" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D438" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E438" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F438" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G438" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H438" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I438" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J438" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K438" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L438" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M438" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N438" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O438" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P438" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B439" s="11" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C439" s="11" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D439" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E439" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F439" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G439" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H439" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I439" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J439" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K439" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L439" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M439" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N439" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O439" s="23" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="P439" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B440" s="8" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C440" s="8" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D440" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E440" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F440" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G440" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H440" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I440" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J440" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K440" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L440" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M440" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N440" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O440" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P440" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B441" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C441" s="11" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D441" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E441" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F441" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G441" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H441" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I441" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J441" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K441" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L441" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M441" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N441" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O441" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P441" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B442" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C442" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D442" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E442" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F442" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G442" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H442" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I442" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J442" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K442" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L442" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M442" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N442" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O442" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P442" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B443" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C443" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D443" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E443" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F443" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G443" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H443" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I443" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J443" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K443" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L443" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M443" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N443" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O443" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P443" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B444" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C444" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D444" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E444" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F444" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="G444" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H444" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I444" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J444" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K444" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L444" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M444" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N444" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O444" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P444" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B445" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C445" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D445" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E445" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F445" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G445" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H445" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I445" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J445" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K445" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L445" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M445" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N445" s="30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O445" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P445" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B446" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C446" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D446" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E446" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F446" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G446" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H446" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I446" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J446" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K446" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L446" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M446" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N446" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O446" s="19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P446" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B447" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C447" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D447" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E447" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F447" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G447" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H447" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I447" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J447" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K447" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L447" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M447" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N447" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O447" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P447" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B448" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C448" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D448" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E448" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F448" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G448" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="H448" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I448" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J448" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K448" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L448" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M448" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N448" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O448" s="19" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P448" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B449" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C449" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D449" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E449" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F449" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G449" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H449" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I449" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J449" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K449" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L449" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M449" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N449" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O449" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P449" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B450" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C450" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D450" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E450" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F450" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G450" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H450" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I450" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J450" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K450" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L450" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M450" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N450" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O450" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P450" s="19" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B451" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C451" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D451" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E451" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F451" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="G451" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H451" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I451" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J451" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K451" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L451" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M451" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N451" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O451" s="23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P451" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B452" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C452" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D452" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E452" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F452" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G452" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H452" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I452" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J452" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K452" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L452" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M452" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N452" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O452" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P452" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B453" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C453" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D453" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E453" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F453" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="G453" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H453" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I453" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J453" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K453" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L453" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M453" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N453" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O453" s="23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P453" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B454" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C454" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D454" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E454" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F454" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G454" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H454" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I454" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J454" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K454" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L454" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M454" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N454" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O454" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P454" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B455" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C455" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D455" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E455" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F455" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G455" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H455" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I455" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J455" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K455" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L455" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M455" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N455" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O455" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P455" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B456" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C456" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D456" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E456" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F456" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G456" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H456" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I456" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J456" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K456" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L456" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M456" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N456" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O456" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P456" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B457" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C457" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D457" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E457" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F457" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G457" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H457" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I457" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J457" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K457" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L457" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M457" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N457" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O457" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P457" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B458" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C458" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D458" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E458" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F458" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G458" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H458" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I458" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J458" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K458" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L458" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M458" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N458" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O458" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P458" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B459" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C459" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D459" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E459" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F459" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G459" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H459" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I459" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J459" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K459" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L459" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M459" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N459" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O459" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P459" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B460" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C460" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D460" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E460" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F460" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G460" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H460" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I460" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J460" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K460" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L460" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M460" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N460" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O460" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P460" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B461" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C461" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D461" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E461" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F461" s="21" t="n">
+        <v>77</v>
+      </c>
+      <c r="G461" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H461" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I461" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J461" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K461" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L461" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M461" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N461" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O461" s="23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P461" s="23" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B462" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C462" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D462" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E462" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F462" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G462" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H462" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I462" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J462" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K462" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L462" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M462" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N462" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O462" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P462" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B463" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C463" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D463" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E463" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F463" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G463" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H463" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I463" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J463" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K463" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L463" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M463" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N463" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O463" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P463" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B464" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C464" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D464" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E464" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F464" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G464" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H464" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I464" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J464" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K464" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L464" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M464" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N464" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O464" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P464" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B465" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C465" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D465" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E465" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F465" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G465" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H465" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I465" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J465" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K465" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L465" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M465" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N465" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O465" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P465" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B466" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C466" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D466" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E466" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F466" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G466" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H466" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I466" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J466" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K466" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L466" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M466" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N466" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O466" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P466" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B467" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C467" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D467" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E467" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F467" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G467" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H467" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I467" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J467" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K467" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L467" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M467" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N467" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O467" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P467" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B468" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C468" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D468" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E468" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F468" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G468" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H468" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I468" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J468" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K468" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L468" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M468" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N468" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O468" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P468" s="19" t="n">
+        <v>27.27</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B469" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C469" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D469" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E469" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F469" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G469" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H469" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I469" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J469" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K469" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L469" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M469" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N469" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O469" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P469" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B470" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C470" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D470" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E470" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F470" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="G470" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H470" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I470" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J470" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K470" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L470" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M470" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N470" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O470" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P470" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B471" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C471" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D471" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E471" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F471" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G471" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H471" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I471" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J471" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K471" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L471" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M471" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N471" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O471" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P471" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B472" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C472" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D472" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E472" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F472" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G472" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H472" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I472" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J472" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K472" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L472" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M472" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N472" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O472" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P472" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B473" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C473" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D473" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E473" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F473" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G473" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H473" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I473" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J473" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K473" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L473" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M473" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N473" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O473" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P473" s="23" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1307</v>
+        <v>1471</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="B14" s="27" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P473"/>
+  <dimension ref="A1:P515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -29243,6 +29243,2526 @@
         <v>26.67</v>
       </c>
     </row>
+    <row r="474">
+      <c r="A474" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B474" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C474" s="8" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D474" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E474" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F474" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G474" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H474" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I474" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J474" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K474" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L474" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M474" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N474" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O474" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P474" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B475" s="11" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C475" s="11" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D475" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E475" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F475" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G475" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H475" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I475" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J475" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K475" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L475" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M475" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N475" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O475" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P475" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B476" s="8" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C476" s="8" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D476" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E476" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F476" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G476" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H476" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I476" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J476" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K476" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L476" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M476" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N476" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O476" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P476" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B477" s="11" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C477" s="11" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D477" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E477" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F477" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G477" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H477" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I477" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J477" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K477" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L477" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M477" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N477" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O477" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P477" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B478" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C478" s="8" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D478" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E478" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F478" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G478" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H478" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I478" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J478" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K478" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L478" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M478" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N478" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O478" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P478" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B479" s="11" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C479" s="11" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D479" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E479" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F479" s="21" t="n">
+        <v>49</v>
+      </c>
+      <c r="G479" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H479" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I479" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J479" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K479" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L479" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M479" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N479" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O479" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P479" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B480" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C480" s="8" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D480" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E480" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F480" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G480" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H480" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I480" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J480" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K480" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L480" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M480" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N480" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O480" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P480" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B481" s="11" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C481" s="11" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D481" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E481" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F481" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G481" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H481" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I481" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J481" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K481" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L481" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M481" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N481" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O481" s="23" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P481" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B482" s="8" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C482" s="8" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D482" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E482" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F482" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G482" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H482" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I482" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J482" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K482" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L482" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M482" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N482" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O482" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P482" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B483" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C483" s="11" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D483" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E483" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F483" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G483" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H483" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I483" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J483" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K483" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L483" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M483" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N483" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O483" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P483" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B484" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C484" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D484" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E484" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F484" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G484" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H484" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I484" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J484" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K484" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L484" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M484" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N484" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O484" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P484" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B485" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C485" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D485" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E485" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F485" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G485" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H485" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I485" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J485" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K485" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L485" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M485" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N485" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O485" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P485" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B486" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C486" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D486" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E486" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F486" s="17" t="n">
+        <v>93</v>
+      </c>
+      <c r="G486" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H486" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I486" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J486" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K486" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L486" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M486" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N486" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O486" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P486" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B487" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C487" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D487" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E487" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F487" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G487" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H487" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I487" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J487" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K487" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L487" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M487" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N487" s="30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O487" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P487" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B488" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C488" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D488" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E488" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F488" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G488" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H488" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I488" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J488" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K488" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L488" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M488" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N488" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O488" s="19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P488" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B489" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C489" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D489" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E489" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F489" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G489" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H489" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I489" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J489" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K489" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L489" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M489" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N489" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O489" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P489" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B490" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C490" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D490" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E490" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F490" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G490" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H490" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I490" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J490" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K490" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L490" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M490" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N490" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O490" s="19" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P490" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B491" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C491" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D491" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E491" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F491" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G491" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H491" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I491" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J491" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K491" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L491" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M491" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N491" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O491" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P491" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B492" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C492" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D492" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E492" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F492" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G492" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H492" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I492" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J492" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K492" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L492" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M492" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N492" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O492" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P492" s="19" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B493" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C493" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D493" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E493" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F493" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="G493" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H493" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I493" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J493" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K493" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L493" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M493" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N493" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O493" s="23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P493" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B494" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C494" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D494" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E494" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F494" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G494" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H494" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I494" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J494" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K494" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L494" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M494" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N494" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O494" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P494" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B495" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C495" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D495" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E495" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F495" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="G495" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H495" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I495" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J495" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K495" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L495" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M495" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N495" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O495" s="23" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P495" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B496" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C496" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D496" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E496" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F496" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G496" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H496" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I496" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J496" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K496" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L496" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M496" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N496" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O496" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P496" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B497" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C497" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D497" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E497" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F497" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G497" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H497" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I497" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J497" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K497" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L497" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M497" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N497" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O497" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P497" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B498" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C498" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D498" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E498" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F498" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G498" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H498" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I498" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J498" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K498" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L498" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M498" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N498" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O498" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P498" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B499" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C499" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D499" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E499" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F499" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G499" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H499" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I499" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J499" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K499" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L499" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M499" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N499" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O499" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P499" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B500" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C500" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D500" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E500" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F500" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G500" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H500" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I500" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J500" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K500" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L500" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M500" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N500" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O500" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P500" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B501" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C501" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D501" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E501" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F501" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G501" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H501" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I501" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J501" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K501" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L501" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M501" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N501" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O501" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P501" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B502" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C502" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D502" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E502" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F502" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G502" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H502" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I502" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J502" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K502" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L502" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M502" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N502" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O502" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P502" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B503" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C503" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D503" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E503" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F503" s="21" t="n">
+        <v>79</v>
+      </c>
+      <c r="G503" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H503" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I503" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J503" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K503" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L503" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M503" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N503" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O503" s="23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P503" s="23" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B504" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C504" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D504" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E504" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F504" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G504" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H504" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I504" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J504" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K504" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L504" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M504" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N504" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O504" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P504" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B505" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C505" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D505" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E505" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F505" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G505" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H505" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I505" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J505" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K505" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L505" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M505" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N505" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O505" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P505" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B506" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C506" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D506" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E506" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F506" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G506" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H506" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I506" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J506" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K506" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L506" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M506" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N506" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O506" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P506" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B507" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C507" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D507" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E507" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F507" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G507" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H507" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I507" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J507" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K507" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L507" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M507" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N507" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O507" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P507" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B508" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C508" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D508" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E508" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F508" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G508" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H508" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I508" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J508" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K508" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L508" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M508" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N508" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O508" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P508" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B509" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C509" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D509" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E509" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F509" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G509" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H509" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I509" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J509" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K509" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L509" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M509" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N509" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O509" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P509" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B510" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C510" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D510" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E510" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F510" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G510" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H510" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I510" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J510" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K510" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L510" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M510" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N510" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O510" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P510" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B511" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C511" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D511" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E511" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F511" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G511" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H511" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I511" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J511" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K511" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L511" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M511" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N511" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O511" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P511" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B512" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C512" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D512" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E512" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F512" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="G512" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H512" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I512" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J512" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K512" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L512" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M512" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N512" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O512" s="19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P512" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B513" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C513" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D513" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E513" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F513" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G513" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H513" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I513" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J513" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K513" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L513" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M513" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N513" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O513" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P513" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B514" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C514" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D514" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E514" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F514" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G514" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H514" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I514" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J514" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K514" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L514" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M514" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N514" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O514" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P514" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B515" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C515" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D515" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E515" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F515" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G515" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H515" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I515" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J515" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K515" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L515" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M515" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N515" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O515" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P515" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29255,7 +31775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -30206,6 +32726,34 @@
         <v>0</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30218,7 +32766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -30659,6 +33207,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="C34" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P515"/>
+  <dimension ref="A1:P557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -31760,6 +31760,2526 @@
         <v>14.04</v>
       </c>
       <c r="P515" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B516" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C516" s="8" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D516" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E516" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F516" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G516" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H516" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I516" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J516" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K516" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L516" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M516" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N516" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O516" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P516" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B517" s="11" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C517" s="11" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D517" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E517" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F517" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G517" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H517" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I517" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J517" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K517" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L517" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M517" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N517" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O517" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P517" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B518" s="8" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C518" s="8" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D518" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E518" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F518" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G518" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H518" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I518" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J518" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K518" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L518" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M518" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N518" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O518" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P518" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B519" s="11" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C519" s="11" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D519" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E519" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F519" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G519" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H519" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I519" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J519" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K519" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L519" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M519" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N519" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O519" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P519" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B520" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C520" s="8" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D520" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E520" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F520" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G520" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H520" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I520" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J520" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K520" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L520" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M520" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N520" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O520" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P520" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B521" s="11" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C521" s="11" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D521" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E521" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F521" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G521" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H521" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I521" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J521" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K521" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L521" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M521" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N521" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O521" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P521" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B522" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C522" s="8" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D522" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E522" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F522" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G522" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H522" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I522" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J522" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K522" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L522" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M522" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N522" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O522" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P522" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B523" s="11" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C523" s="11" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D523" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E523" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F523" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G523" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H523" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I523" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J523" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K523" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L523" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M523" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N523" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O523" s="23" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P523" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B524" s="8" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C524" s="8" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D524" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E524" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F524" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G524" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H524" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I524" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J524" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K524" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L524" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M524" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N524" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O524" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P524" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B525" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C525" s="11" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D525" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E525" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F525" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G525" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H525" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I525" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J525" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K525" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L525" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M525" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N525" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O525" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P525" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B526" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C526" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D526" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E526" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F526" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G526" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H526" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I526" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J526" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K526" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L526" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M526" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N526" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O526" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P526" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B527" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C527" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D527" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E527" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F527" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G527" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H527" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I527" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J527" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K527" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L527" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M527" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N527" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O527" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P527" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B528" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C528" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D528" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E528" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F528" s="17" t="n">
+        <v>94</v>
+      </c>
+      <c r="G528" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H528" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I528" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J528" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K528" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L528" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M528" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N528" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O528" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P528" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B529" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C529" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D529" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E529" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F529" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G529" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H529" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I529" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J529" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K529" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L529" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M529" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N529" s="30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O529" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P529" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B530" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C530" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D530" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E530" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F530" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G530" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H530" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I530" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J530" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K530" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L530" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M530" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N530" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O530" s="19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P530" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B531" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C531" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D531" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E531" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F531" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G531" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H531" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I531" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J531" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K531" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L531" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M531" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N531" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O531" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P531" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B532" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C532" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D532" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E532" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F532" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G532" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H532" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I532" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J532" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K532" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L532" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M532" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N532" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O532" s="19" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P532" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B533" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C533" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D533" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E533" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F533" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G533" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H533" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I533" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J533" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K533" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L533" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M533" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N533" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O533" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P533" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B534" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C534" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D534" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E534" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F534" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G534" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H534" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I534" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J534" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K534" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L534" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M534" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N534" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O534" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P534" s="19" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B535" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C535" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D535" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E535" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F535" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="G535" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H535" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I535" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J535" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K535" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L535" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M535" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N535" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O535" s="23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P535" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B536" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C536" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D536" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E536" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F536" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G536" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H536" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I536" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J536" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K536" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L536" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M536" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N536" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O536" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P536" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B537" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C537" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D537" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E537" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F537" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="G537" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H537" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I537" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J537" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K537" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L537" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M537" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N537" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O537" s="23" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P537" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B538" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C538" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D538" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E538" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F538" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G538" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H538" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I538" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J538" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K538" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L538" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M538" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N538" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O538" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P538" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B539" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C539" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D539" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E539" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F539" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G539" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H539" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I539" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J539" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K539" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L539" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M539" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N539" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O539" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P539" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B540" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C540" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D540" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E540" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F540" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G540" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H540" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I540" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J540" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K540" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L540" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M540" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N540" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O540" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P540" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B541" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C541" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D541" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E541" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F541" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G541" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H541" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I541" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J541" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K541" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L541" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M541" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N541" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O541" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P541" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B542" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C542" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D542" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E542" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F542" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G542" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H542" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I542" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J542" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K542" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L542" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M542" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N542" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O542" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P542" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B543" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C543" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D543" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E543" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F543" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G543" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H543" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I543" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J543" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K543" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L543" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M543" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N543" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O543" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P543" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B544" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C544" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D544" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E544" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F544" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G544" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H544" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I544" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J544" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K544" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L544" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M544" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N544" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O544" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P544" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B545" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C545" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D545" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E545" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F545" s="21" t="n">
+        <v>79</v>
+      </c>
+      <c r="G545" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H545" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I545" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J545" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K545" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L545" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M545" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N545" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O545" s="23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P545" s="23" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B546" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C546" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D546" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E546" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F546" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G546" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H546" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I546" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J546" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K546" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L546" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M546" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N546" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O546" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P546" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B547" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C547" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D547" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E547" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F547" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G547" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H547" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I547" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J547" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K547" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L547" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M547" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N547" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O547" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P547" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B548" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C548" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D548" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E548" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F548" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G548" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H548" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I548" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J548" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K548" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L548" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M548" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N548" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O548" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P548" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B549" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C549" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D549" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E549" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F549" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G549" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H549" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I549" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J549" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K549" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L549" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M549" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N549" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O549" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P549" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B550" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C550" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D550" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E550" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F550" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G550" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H550" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I550" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J550" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K550" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L550" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M550" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N550" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O550" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P550" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B551" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C551" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D551" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E551" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F551" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G551" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H551" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I551" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J551" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K551" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L551" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M551" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N551" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O551" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P551" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B552" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C552" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D552" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E552" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F552" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G552" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H552" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I552" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J552" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K552" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L552" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M552" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N552" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O552" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P552" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B553" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C553" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D553" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E553" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F553" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G553" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H553" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I553" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J553" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K553" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L553" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M553" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N553" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O553" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P553" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B554" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C554" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D554" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E554" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F554" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="G554" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H554" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I554" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J554" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K554" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L554" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M554" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N554" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O554" s="19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P554" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B555" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C555" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D555" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E555" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F555" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G555" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H555" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I555" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J555" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K555" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L555" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M555" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N555" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O555" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P555" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B556" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C556" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D556" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E556" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F556" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G556" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H556" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I556" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J556" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K556" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L556" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M556" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N556" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O556" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P556" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B557" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C557" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D557" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E557" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F557" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G557" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H557" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I557" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J557" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K557" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L557" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M557" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N557" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O557" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P557" s="23" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P557"/>
+  <dimension ref="A1:P599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -34280,6 +34280,2526 @@
         <v>14.04</v>
       </c>
       <c r="P557" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B558" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C558" s="8" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D558" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E558" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F558" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G558" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H558" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I558" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J558" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K558" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L558" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M558" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N558" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O558" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P558" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B559" s="11" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C559" s="11" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D559" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E559" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F559" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="G559" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H559" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I559" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J559" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K559" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L559" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M559" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N559" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O559" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P559" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B560" s="8" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C560" s="8" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D560" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E560" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F560" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G560" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H560" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I560" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J560" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K560" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L560" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M560" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N560" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O560" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P560" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B561" s="11" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C561" s="11" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D561" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E561" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F561" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G561" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H561" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I561" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J561" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K561" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L561" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M561" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N561" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O561" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P561" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B562" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C562" s="8" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D562" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E562" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F562" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G562" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H562" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I562" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J562" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K562" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L562" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M562" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N562" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O562" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P562" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B563" s="11" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C563" s="11" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D563" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E563" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F563" s="21" t="n">
+        <v>51</v>
+      </c>
+      <c r="G563" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H563" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I563" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J563" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K563" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L563" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M563" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N563" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O563" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P563" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B564" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C564" s="8" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D564" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E564" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F564" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G564" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H564" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I564" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J564" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K564" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L564" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M564" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N564" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O564" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P564" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B565" s="11" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C565" s="11" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D565" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E565" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F565" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G565" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H565" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I565" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J565" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K565" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L565" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M565" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N565" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O565" s="23" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P565" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B566" s="8" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C566" s="8" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D566" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E566" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F566" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G566" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H566" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I566" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J566" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K566" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L566" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M566" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N566" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O566" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P566" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B567" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C567" s="11" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D567" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E567" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F567" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G567" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H567" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I567" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J567" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K567" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L567" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M567" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N567" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O567" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P567" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B568" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C568" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D568" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E568" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F568" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G568" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H568" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I568" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J568" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K568" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L568" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M568" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N568" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O568" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P568" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B569" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C569" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D569" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E569" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F569" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G569" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H569" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I569" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J569" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K569" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L569" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M569" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N569" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O569" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P569" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B570" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C570" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D570" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E570" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F570" s="17" t="n">
+        <v>94</v>
+      </c>
+      <c r="G570" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H570" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I570" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J570" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K570" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L570" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M570" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N570" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O570" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P570" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B571" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C571" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D571" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E571" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F571" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G571" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H571" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I571" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J571" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K571" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L571" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M571" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N571" s="30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O571" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P571" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B572" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C572" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D572" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E572" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F572" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G572" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H572" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I572" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J572" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K572" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L572" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M572" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N572" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O572" s="19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P572" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B573" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C573" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D573" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E573" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F573" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G573" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H573" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I573" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J573" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K573" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L573" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M573" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N573" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O573" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P573" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B574" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C574" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D574" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E574" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F574" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G574" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H574" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I574" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J574" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K574" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L574" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M574" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N574" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O574" s="19" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P574" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B575" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C575" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D575" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E575" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F575" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G575" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H575" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I575" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J575" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K575" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L575" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M575" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N575" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O575" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P575" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B576" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C576" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D576" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E576" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F576" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G576" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H576" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I576" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J576" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K576" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L576" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M576" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N576" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O576" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P576" s="19" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B577" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C577" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D577" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E577" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F577" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="G577" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H577" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I577" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J577" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K577" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L577" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M577" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N577" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O577" s="23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P577" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B578" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C578" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D578" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E578" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F578" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G578" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H578" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I578" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J578" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K578" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L578" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M578" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N578" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O578" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P578" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B579" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C579" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D579" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E579" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F579" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="G579" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H579" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I579" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J579" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K579" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L579" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M579" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N579" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O579" s="23" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P579" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B580" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C580" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D580" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E580" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F580" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G580" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H580" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I580" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J580" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K580" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L580" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M580" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N580" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O580" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P580" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B581" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C581" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D581" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E581" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F581" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G581" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H581" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I581" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J581" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K581" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L581" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M581" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N581" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O581" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P581" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B582" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C582" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D582" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E582" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F582" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G582" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H582" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I582" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J582" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K582" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L582" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M582" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N582" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O582" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P582" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B583" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C583" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D583" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E583" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F583" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G583" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H583" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I583" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J583" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K583" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L583" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M583" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N583" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O583" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P583" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B584" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C584" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D584" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E584" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F584" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G584" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H584" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I584" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J584" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K584" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L584" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M584" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N584" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O584" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P584" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B585" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C585" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D585" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E585" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F585" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G585" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H585" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I585" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J585" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K585" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L585" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M585" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N585" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O585" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P585" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B586" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C586" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D586" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E586" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F586" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G586" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H586" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I586" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J586" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K586" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L586" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M586" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N586" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O586" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P586" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B587" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C587" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D587" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E587" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F587" s="21" t="n">
+        <v>79</v>
+      </c>
+      <c r="G587" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H587" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I587" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J587" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K587" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L587" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M587" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N587" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O587" s="23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P587" s="23" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B588" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C588" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D588" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E588" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F588" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G588" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H588" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I588" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J588" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K588" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L588" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M588" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N588" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O588" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P588" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B589" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C589" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D589" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E589" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F589" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G589" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H589" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I589" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J589" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K589" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L589" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M589" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N589" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O589" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P589" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B590" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C590" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D590" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E590" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F590" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G590" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H590" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I590" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J590" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K590" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L590" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M590" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N590" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O590" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P590" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B591" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C591" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D591" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E591" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F591" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G591" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H591" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I591" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J591" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K591" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L591" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M591" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N591" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O591" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P591" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B592" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C592" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D592" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E592" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F592" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G592" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H592" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I592" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J592" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K592" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L592" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M592" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N592" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O592" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P592" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B593" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C593" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D593" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E593" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F593" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G593" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H593" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I593" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J593" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K593" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L593" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M593" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N593" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O593" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P593" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B594" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C594" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D594" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E594" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F594" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G594" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H594" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I594" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J594" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K594" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L594" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M594" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N594" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O594" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P594" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B595" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C595" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D595" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E595" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F595" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G595" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H595" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I595" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J595" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K595" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L595" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M595" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N595" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O595" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P595" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B596" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C596" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D596" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E596" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F596" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="G596" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H596" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I596" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J596" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K596" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L596" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M596" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N596" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O596" s="19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P596" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B597" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C597" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D597" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E597" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F597" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G597" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H597" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I597" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J597" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K597" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L597" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M597" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N597" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O597" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P597" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B598" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C598" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D598" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E598" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F598" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G598" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H598" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I598" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J598" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K598" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L598" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M598" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N598" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O598" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P598" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B599" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C599" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D599" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E599" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F599" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G599" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H599" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I599" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J599" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K599" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L599" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M599" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N599" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O599" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P599" s="23" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1475</v>
+        <v>1501</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P599"/>
+  <dimension ref="A1:P641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -36803,6 +36803,2526 @@
         <v>26.67</v>
       </c>
     </row>
+    <row r="600">
+      <c r="A600" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B600" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C600" s="8" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D600" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E600" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F600" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G600" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H600" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I600" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J600" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K600" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L600" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M600" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N600" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O600" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P600" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B601" s="11" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C601" s="11" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D601" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E601" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F601" s="21" t="n">
+        <v>67</v>
+      </c>
+      <c r="G601" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H601" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I601" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J601" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K601" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L601" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M601" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N601" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O601" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P601" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B602" s="8" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C602" s="8" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D602" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E602" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F602" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G602" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H602" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I602" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J602" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K602" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L602" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M602" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N602" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O602" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P602" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B603" s="11" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C603" s="11" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D603" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E603" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F603" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G603" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H603" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I603" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J603" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K603" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L603" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M603" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N603" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O603" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P603" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B604" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C604" s="8" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D604" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E604" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F604" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G604" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H604" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I604" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J604" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K604" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L604" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M604" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N604" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O604" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P604" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B605" s="11" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C605" s="11" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D605" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E605" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F605" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="G605" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H605" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I605" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J605" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K605" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L605" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M605" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N605" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O605" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P605" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B606" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C606" s="8" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D606" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E606" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F606" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G606" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H606" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I606" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J606" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K606" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L606" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M606" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N606" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O606" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P606" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B607" s="11" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C607" s="11" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D607" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E607" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F607" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G607" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H607" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I607" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J607" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K607" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L607" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M607" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N607" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O607" s="23" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P607" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B608" s="8" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C608" s="8" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D608" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E608" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F608" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G608" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H608" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I608" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J608" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K608" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L608" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M608" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N608" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O608" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P608" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B609" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C609" s="11" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D609" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E609" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F609" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G609" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H609" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I609" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J609" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K609" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L609" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M609" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N609" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O609" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P609" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B610" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C610" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D610" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E610" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F610" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G610" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H610" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I610" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J610" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K610" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L610" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M610" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N610" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O610" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P610" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B611" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C611" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D611" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E611" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F611" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G611" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H611" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I611" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J611" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K611" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L611" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M611" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N611" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O611" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P611" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B612" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C612" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D612" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E612" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F612" s="17" t="n">
+        <v>98</v>
+      </c>
+      <c r="G612" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H612" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I612" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J612" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K612" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L612" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M612" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N612" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O612" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P612" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B613" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C613" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D613" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E613" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F613" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G613" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H613" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I613" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J613" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K613" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L613" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M613" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N613" s="30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O613" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P613" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B614" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C614" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D614" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E614" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F614" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G614" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H614" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I614" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J614" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K614" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L614" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M614" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N614" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O614" s="19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P614" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B615" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C615" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D615" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E615" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F615" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G615" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H615" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I615" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J615" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K615" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L615" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M615" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N615" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O615" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P615" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B616" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C616" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D616" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E616" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F616" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G616" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H616" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I616" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J616" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K616" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L616" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M616" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N616" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O616" s="19" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="P616" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B617" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C617" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D617" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E617" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F617" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G617" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H617" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I617" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J617" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K617" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L617" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M617" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N617" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O617" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P617" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B618" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C618" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D618" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E618" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F618" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G618" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H618" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I618" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J618" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K618" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L618" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M618" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N618" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O618" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P618" s="19" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B619" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C619" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D619" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E619" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F619" s="21" t="n">
+        <v>76</v>
+      </c>
+      <c r="G619" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H619" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I619" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J619" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K619" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L619" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M619" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N619" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O619" s="23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P619" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B620" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C620" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D620" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E620" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F620" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G620" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H620" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I620" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J620" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K620" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L620" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M620" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N620" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O620" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P620" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B621" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C621" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D621" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E621" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F621" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G621" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H621" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I621" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J621" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K621" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L621" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M621" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N621" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O621" s="23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="P621" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B622" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C622" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D622" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E622" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F622" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G622" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H622" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I622" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J622" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K622" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L622" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M622" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N622" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O622" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P622" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B623" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C623" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D623" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E623" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F623" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G623" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H623" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I623" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J623" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K623" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L623" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M623" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N623" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O623" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P623" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B624" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C624" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D624" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E624" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F624" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G624" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H624" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I624" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J624" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K624" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L624" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M624" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N624" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O624" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P624" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B625" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C625" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D625" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E625" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F625" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G625" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H625" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I625" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J625" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K625" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L625" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M625" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N625" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O625" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P625" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B626" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C626" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D626" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E626" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F626" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G626" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H626" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I626" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J626" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K626" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L626" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M626" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N626" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O626" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P626" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B627" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C627" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D627" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E627" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F627" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G627" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H627" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I627" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J627" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K627" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L627" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M627" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N627" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O627" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P627" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B628" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C628" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D628" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E628" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F628" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G628" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H628" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I628" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J628" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K628" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L628" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M628" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N628" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O628" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P628" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B629" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C629" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D629" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E629" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F629" s="21" t="n">
+        <v>85</v>
+      </c>
+      <c r="G629" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H629" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I629" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J629" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K629" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L629" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M629" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N629" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O629" s="23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P629" s="23" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B630" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C630" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D630" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E630" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F630" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G630" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H630" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I630" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J630" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K630" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L630" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M630" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N630" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O630" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P630" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B631" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C631" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D631" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E631" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F631" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G631" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H631" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I631" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J631" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K631" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L631" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M631" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N631" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O631" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P631" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B632" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C632" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D632" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E632" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F632" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G632" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H632" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I632" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J632" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K632" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L632" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M632" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N632" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O632" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P632" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B633" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C633" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D633" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E633" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F633" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G633" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H633" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I633" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J633" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K633" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L633" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M633" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N633" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O633" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P633" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B634" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C634" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D634" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E634" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F634" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G634" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H634" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I634" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J634" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K634" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L634" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M634" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N634" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O634" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P634" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B635" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C635" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D635" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E635" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F635" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G635" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H635" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I635" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J635" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K635" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L635" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M635" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N635" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O635" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P635" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B636" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C636" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D636" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E636" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F636" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G636" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H636" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I636" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J636" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K636" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L636" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M636" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N636" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O636" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P636" s="19" t="n">
+        <v>23.08</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B637" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C637" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D637" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E637" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F637" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G637" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H637" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I637" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J637" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K637" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L637" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M637" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N637" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O637" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P637" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B638" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C638" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D638" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E638" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F638" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="G638" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H638" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I638" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J638" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K638" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L638" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M638" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N638" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O638" s="19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P638" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B639" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C639" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D639" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E639" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F639" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G639" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H639" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I639" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J639" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K639" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L639" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M639" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N639" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O639" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P639" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B640" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C640" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D640" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E640" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F640" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G640" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H640" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I640" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J640" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K640" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L640" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M640" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N640" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O640" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P640" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B641" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C641" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D641" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E641" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F641" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G641" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H641" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I641" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J641" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K641" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L641" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M641" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N641" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O641" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P641" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -36815,7 +39335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -37794,6 +40314,34 @@
         <v>0</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -37806,7 +40354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -38260,6 +40808,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="C35" s="33" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P641"/>
+  <dimension ref="A1:P683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -39320,6 +39320,2526 @@
         <v>14.04</v>
       </c>
       <c r="P641" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B642" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C642" s="8" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D642" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E642" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F642" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G642" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H642" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I642" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J642" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K642" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L642" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M642" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N642" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O642" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P642" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B643" s="11" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C643" s="11" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D643" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E643" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F643" s="21" t="n">
+        <v>67</v>
+      </c>
+      <c r="G643" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H643" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I643" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J643" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K643" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L643" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M643" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N643" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O643" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P643" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B644" s="8" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C644" s="8" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D644" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E644" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F644" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G644" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H644" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I644" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J644" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K644" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L644" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M644" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N644" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O644" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P644" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B645" s="11" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C645" s="11" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D645" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E645" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F645" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G645" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H645" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I645" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J645" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K645" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L645" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M645" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N645" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O645" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P645" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B646" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C646" s="8" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D646" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E646" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F646" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G646" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H646" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I646" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J646" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K646" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L646" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M646" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N646" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O646" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P646" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B647" s="11" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C647" s="11" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D647" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E647" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F647" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="G647" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H647" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I647" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J647" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K647" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L647" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M647" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N647" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O647" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P647" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B648" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C648" s="8" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D648" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E648" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F648" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G648" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H648" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I648" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J648" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K648" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L648" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M648" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N648" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O648" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P648" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B649" s="11" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C649" s="11" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D649" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E649" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F649" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G649" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H649" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I649" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J649" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K649" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L649" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M649" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N649" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O649" s="23" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P649" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B650" s="8" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C650" s="8" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D650" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E650" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F650" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G650" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H650" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I650" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J650" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K650" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L650" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M650" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N650" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O650" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P650" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B651" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C651" s="11" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D651" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E651" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F651" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G651" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H651" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I651" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J651" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K651" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L651" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M651" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N651" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O651" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P651" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B652" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C652" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D652" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E652" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F652" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G652" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H652" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I652" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J652" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K652" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L652" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M652" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N652" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O652" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P652" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B653" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C653" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D653" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E653" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F653" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G653" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H653" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I653" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J653" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K653" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L653" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M653" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N653" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O653" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P653" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B654" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C654" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D654" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E654" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F654" s="17" t="n">
+        <v>99</v>
+      </c>
+      <c r="G654" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H654" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I654" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J654" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K654" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L654" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M654" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N654" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O654" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P654" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B655" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C655" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D655" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E655" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F655" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G655" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H655" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I655" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J655" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K655" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L655" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M655" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N655" s="30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O655" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P655" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B656" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C656" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D656" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E656" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F656" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G656" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H656" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I656" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J656" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K656" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L656" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M656" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N656" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O656" s="19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P656" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B657" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C657" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D657" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E657" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F657" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G657" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H657" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I657" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J657" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K657" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L657" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M657" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N657" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O657" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P657" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B658" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C658" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D658" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E658" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F658" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G658" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H658" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I658" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J658" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K658" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L658" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M658" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N658" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O658" s="19" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="P658" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B659" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C659" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D659" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E659" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F659" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G659" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H659" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I659" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J659" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K659" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L659" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M659" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N659" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O659" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P659" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B660" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C660" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D660" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E660" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F660" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G660" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H660" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I660" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J660" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K660" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L660" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M660" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N660" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O660" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P660" s="19" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B661" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C661" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D661" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E661" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F661" s="21" t="n">
+        <v>76</v>
+      </c>
+      <c r="G661" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H661" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I661" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J661" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K661" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L661" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M661" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N661" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O661" s="23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P661" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B662" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C662" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D662" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E662" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F662" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G662" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H662" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I662" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J662" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K662" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L662" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M662" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N662" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O662" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P662" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B663" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C663" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D663" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E663" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F663" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="G663" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H663" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I663" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J663" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K663" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L663" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M663" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N663" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O663" s="23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="P663" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B664" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C664" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D664" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E664" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F664" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G664" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H664" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I664" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J664" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K664" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L664" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M664" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N664" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O664" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P664" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B665" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C665" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D665" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E665" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F665" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G665" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H665" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I665" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J665" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K665" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L665" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M665" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N665" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O665" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P665" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B666" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C666" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D666" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E666" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F666" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G666" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H666" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I666" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J666" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K666" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L666" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M666" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N666" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O666" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P666" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B667" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C667" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D667" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E667" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F667" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G667" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H667" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I667" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J667" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K667" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L667" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M667" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N667" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O667" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P667" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B668" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C668" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D668" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E668" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F668" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G668" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H668" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I668" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J668" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K668" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L668" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M668" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N668" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O668" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P668" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B669" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C669" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D669" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E669" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F669" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G669" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H669" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I669" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J669" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K669" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L669" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M669" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N669" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O669" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P669" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B670" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C670" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D670" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E670" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F670" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G670" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H670" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I670" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J670" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K670" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L670" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M670" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N670" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O670" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P670" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B671" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C671" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D671" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E671" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F671" s="21" t="n">
+        <v>87</v>
+      </c>
+      <c r="G671" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H671" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I671" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J671" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K671" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L671" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M671" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N671" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O671" s="23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P671" s="23" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B672" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C672" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D672" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E672" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F672" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G672" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H672" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I672" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J672" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K672" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L672" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M672" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N672" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O672" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P672" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B673" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C673" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D673" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E673" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F673" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G673" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H673" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I673" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J673" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K673" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L673" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M673" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N673" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O673" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P673" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B674" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C674" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D674" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E674" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F674" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G674" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H674" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I674" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J674" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K674" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L674" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M674" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N674" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O674" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P674" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B675" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C675" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D675" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E675" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F675" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G675" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H675" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I675" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J675" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K675" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L675" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M675" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N675" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O675" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P675" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B676" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C676" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D676" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E676" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F676" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G676" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H676" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I676" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J676" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K676" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L676" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M676" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N676" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O676" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P676" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B677" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C677" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D677" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E677" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F677" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G677" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H677" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I677" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J677" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K677" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L677" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M677" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N677" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O677" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P677" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B678" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C678" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D678" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E678" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F678" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G678" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H678" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I678" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J678" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K678" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L678" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M678" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N678" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O678" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P678" s="19" t="n">
+        <v>23.08</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B679" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C679" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D679" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E679" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F679" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G679" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H679" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I679" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J679" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K679" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L679" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M679" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N679" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O679" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P679" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B680" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C680" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D680" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E680" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F680" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="G680" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H680" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I680" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J680" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K680" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L680" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M680" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N680" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O680" s="19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P680" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B681" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C681" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D681" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E681" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F681" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G681" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H681" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I681" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J681" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K681" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L681" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M681" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N681" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O681" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P681" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B682" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C682" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D682" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E682" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F682" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G682" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H682" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I682" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J682" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K682" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L682" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M682" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N682" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O682" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P682" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B683" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C683" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D683" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E683" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F683" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G683" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H683" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I683" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J683" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K683" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L683" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M683" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N683" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O683" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P683" s="23" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P683"/>
+  <dimension ref="A1:P725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -41840,6 +41840,2526 @@
         <v>14.04</v>
       </c>
       <c r="P683" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B684" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C684" s="8" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D684" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E684" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F684" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G684" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H684" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I684" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J684" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K684" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L684" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M684" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N684" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O684" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P684" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B685" s="11" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C685" s="11" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D685" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E685" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F685" s="21" t="n">
+        <v>68</v>
+      </c>
+      <c r="G685" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H685" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I685" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J685" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K685" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L685" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M685" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N685" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O685" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P685" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B686" s="8" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C686" s="8" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D686" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E686" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F686" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G686" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H686" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I686" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J686" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K686" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L686" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M686" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N686" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O686" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P686" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B687" s="11" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C687" s="11" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D687" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E687" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F687" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G687" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H687" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I687" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J687" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K687" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L687" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M687" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N687" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O687" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P687" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B688" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C688" s="8" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D688" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E688" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F688" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G688" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H688" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I688" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J688" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K688" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L688" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M688" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N688" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O688" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P688" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B689" s="11" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C689" s="11" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D689" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E689" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F689" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="G689" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H689" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I689" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J689" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K689" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L689" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M689" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N689" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O689" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P689" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B690" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C690" s="8" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D690" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E690" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F690" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G690" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H690" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I690" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J690" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K690" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L690" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M690" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N690" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O690" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P690" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B691" s="11" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C691" s="11" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D691" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E691" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F691" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G691" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H691" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I691" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J691" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K691" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L691" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M691" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N691" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O691" s="23" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P691" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B692" s="8" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C692" s="8" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D692" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E692" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F692" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G692" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H692" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I692" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J692" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K692" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L692" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M692" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N692" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O692" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P692" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B693" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C693" s="11" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D693" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E693" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F693" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G693" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H693" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I693" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J693" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K693" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L693" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M693" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N693" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O693" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P693" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B694" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C694" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D694" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E694" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F694" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G694" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H694" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I694" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J694" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K694" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L694" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M694" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N694" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O694" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P694" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B695" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C695" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D695" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E695" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F695" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G695" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H695" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I695" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J695" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K695" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L695" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M695" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N695" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O695" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P695" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B696" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C696" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D696" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E696" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F696" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="G696" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H696" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I696" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J696" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K696" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L696" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M696" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N696" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O696" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P696" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B697" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C697" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D697" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E697" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F697" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G697" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H697" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I697" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J697" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K697" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L697" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M697" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N697" s="30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O697" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P697" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B698" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C698" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D698" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E698" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F698" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G698" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H698" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I698" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J698" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K698" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L698" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M698" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N698" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O698" s="19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P698" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B699" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C699" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D699" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E699" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F699" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G699" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H699" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I699" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J699" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K699" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L699" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M699" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N699" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O699" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P699" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B700" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C700" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D700" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E700" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F700" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G700" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H700" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I700" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J700" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K700" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L700" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M700" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N700" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O700" s="19" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="P700" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B701" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C701" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D701" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E701" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F701" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G701" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H701" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I701" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J701" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K701" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L701" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M701" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N701" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O701" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P701" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B702" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C702" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D702" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E702" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F702" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G702" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H702" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I702" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J702" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K702" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L702" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M702" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N702" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O702" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P702" s="19" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B703" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C703" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D703" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E703" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F703" s="21" t="n">
+        <v>76</v>
+      </c>
+      <c r="G703" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H703" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I703" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J703" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K703" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L703" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M703" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N703" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O703" s="23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P703" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B704" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C704" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D704" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E704" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F704" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G704" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H704" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I704" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J704" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K704" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L704" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M704" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N704" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O704" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P704" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B705" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C705" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D705" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E705" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F705" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="G705" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H705" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I705" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J705" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K705" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L705" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M705" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N705" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O705" s="23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="P705" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B706" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C706" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D706" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E706" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F706" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G706" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H706" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I706" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J706" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K706" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L706" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M706" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N706" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O706" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P706" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B707" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C707" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D707" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E707" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F707" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G707" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H707" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I707" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J707" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K707" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L707" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M707" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N707" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O707" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P707" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B708" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C708" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D708" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E708" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F708" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G708" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H708" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I708" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J708" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K708" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L708" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M708" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N708" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O708" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P708" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B709" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C709" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D709" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E709" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F709" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G709" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H709" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I709" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J709" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K709" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L709" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M709" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N709" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O709" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P709" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B710" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C710" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D710" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E710" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F710" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G710" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H710" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I710" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J710" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K710" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L710" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M710" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N710" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O710" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P710" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B711" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C711" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D711" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E711" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F711" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G711" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H711" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I711" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J711" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K711" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L711" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M711" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N711" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O711" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P711" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B712" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C712" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D712" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E712" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F712" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G712" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H712" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I712" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J712" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K712" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L712" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M712" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N712" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O712" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P712" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B713" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C713" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D713" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E713" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F713" s="21" t="n">
+        <v>87</v>
+      </c>
+      <c r="G713" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H713" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I713" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J713" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K713" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L713" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M713" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N713" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O713" s="23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P713" s="23" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B714" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C714" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D714" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E714" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F714" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G714" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H714" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I714" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J714" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K714" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L714" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M714" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N714" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O714" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P714" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B715" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C715" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D715" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E715" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F715" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G715" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H715" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I715" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J715" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K715" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L715" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M715" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N715" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O715" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P715" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B716" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C716" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D716" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E716" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F716" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G716" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H716" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I716" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J716" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K716" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L716" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M716" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N716" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O716" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P716" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B717" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C717" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D717" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E717" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F717" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G717" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H717" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I717" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J717" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K717" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L717" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M717" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N717" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O717" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P717" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B718" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C718" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D718" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E718" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F718" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G718" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H718" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I718" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J718" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K718" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L718" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M718" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N718" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O718" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P718" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B719" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C719" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D719" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E719" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F719" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G719" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H719" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I719" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J719" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K719" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L719" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M719" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N719" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O719" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P719" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B720" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C720" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D720" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E720" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F720" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G720" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H720" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I720" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J720" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K720" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L720" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M720" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N720" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O720" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P720" s="19" t="n">
+        <v>23.08</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B721" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C721" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D721" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E721" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F721" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G721" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H721" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I721" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J721" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K721" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L721" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M721" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N721" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O721" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P721" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B722" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C722" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D722" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E722" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F722" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="G722" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H722" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I722" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J722" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K722" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L722" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M722" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N722" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O722" s="19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P722" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B723" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C723" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D723" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E723" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F723" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G723" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H723" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I723" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J723" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K723" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L723" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M723" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N723" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O723" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P723" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B724" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C724" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D724" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E724" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F724" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G724" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H724" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I724" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J724" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K724" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L724" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M724" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N724" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O724" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P724" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B725" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C725" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D725" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E725" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F725" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G725" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H725" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I725" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J725" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K725" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L725" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M725" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N725" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O725" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P725" s="23" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1507</v>
+        <v>1558</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P725"/>
+  <dimension ref="A1:P767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -44363,6 +44363,2526 @@
         <v>26.67</v>
       </c>
     </row>
+    <row r="726">
+      <c r="A726" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B726" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C726" s="8" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D726" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E726" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F726" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G726" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H726" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I726" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J726" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K726" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L726" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M726" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N726" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O726" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P726" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B727" s="11" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C727" s="11" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D727" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E727" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F727" s="21" t="n">
+        <v>72</v>
+      </c>
+      <c r="G727" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H727" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I727" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J727" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K727" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L727" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M727" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N727" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O727" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P727" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B728" s="8" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C728" s="8" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D728" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E728" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F728" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G728" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H728" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I728" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J728" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K728" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L728" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M728" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N728" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O728" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P728" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B729" s="11" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C729" s="11" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D729" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E729" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F729" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G729" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H729" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I729" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J729" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K729" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L729" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M729" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N729" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O729" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P729" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B730" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C730" s="8" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D730" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E730" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F730" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G730" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H730" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I730" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J730" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K730" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L730" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M730" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N730" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O730" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P730" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B731" s="11" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C731" s="11" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D731" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E731" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F731" s="21" t="n">
+        <v>63</v>
+      </c>
+      <c r="G731" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H731" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I731" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J731" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K731" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L731" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M731" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N731" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O731" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P731" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B732" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C732" s="8" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D732" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E732" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F732" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G732" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H732" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I732" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J732" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K732" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L732" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M732" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N732" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O732" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P732" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B733" s="11" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C733" s="11" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D733" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E733" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F733" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G733" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H733" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I733" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J733" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K733" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L733" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M733" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N733" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O733" s="23" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P733" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B734" s="8" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C734" s="8" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D734" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E734" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F734" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G734" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H734" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I734" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J734" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K734" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L734" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M734" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N734" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O734" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P734" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B735" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C735" s="11" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D735" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E735" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F735" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G735" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H735" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I735" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J735" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K735" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L735" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M735" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N735" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O735" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P735" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B736" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C736" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D736" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E736" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F736" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G736" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H736" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I736" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J736" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K736" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L736" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M736" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N736" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O736" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P736" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B737" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C737" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D737" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E737" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F737" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G737" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H737" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I737" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J737" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K737" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L737" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M737" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N737" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O737" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P737" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B738" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C738" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D738" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E738" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F738" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="G738" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H738" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I738" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J738" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K738" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L738" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M738" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N738" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O738" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P738" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B739" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C739" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D739" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E739" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F739" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G739" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H739" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I739" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J739" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K739" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L739" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M739" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N739" s="30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O739" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P739" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B740" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C740" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D740" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E740" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F740" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G740" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H740" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I740" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J740" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K740" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L740" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M740" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N740" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O740" s="19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P740" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B741" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C741" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D741" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E741" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F741" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G741" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H741" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I741" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J741" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K741" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L741" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M741" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N741" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O741" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P741" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B742" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C742" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D742" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E742" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F742" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G742" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H742" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I742" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J742" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K742" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L742" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M742" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N742" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O742" s="19" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="P742" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B743" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C743" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D743" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E743" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F743" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G743" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H743" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I743" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J743" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K743" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L743" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M743" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N743" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O743" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P743" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B744" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C744" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D744" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E744" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F744" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G744" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H744" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I744" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J744" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K744" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L744" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M744" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N744" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O744" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P744" s="19" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B745" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C745" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D745" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E745" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F745" s="21" t="n">
+        <v>76</v>
+      </c>
+      <c r="G745" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H745" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I745" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J745" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K745" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L745" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M745" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N745" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O745" s="23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P745" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B746" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C746" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D746" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E746" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F746" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G746" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H746" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I746" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J746" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K746" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L746" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M746" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N746" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O746" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P746" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B747" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C747" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D747" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E747" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F747" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G747" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H747" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I747" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J747" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K747" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L747" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M747" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N747" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O747" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="P747" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B748" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C748" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D748" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E748" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F748" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G748" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H748" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I748" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J748" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K748" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L748" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M748" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N748" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O748" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P748" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B749" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C749" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D749" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E749" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F749" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G749" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H749" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I749" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J749" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K749" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L749" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M749" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N749" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O749" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P749" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B750" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C750" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D750" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E750" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F750" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G750" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H750" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I750" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J750" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K750" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L750" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M750" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N750" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O750" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P750" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B751" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C751" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D751" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E751" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F751" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G751" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H751" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I751" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J751" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K751" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L751" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M751" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N751" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O751" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P751" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B752" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C752" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D752" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E752" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F752" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G752" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H752" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I752" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J752" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K752" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L752" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M752" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N752" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O752" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P752" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B753" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C753" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D753" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E753" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F753" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G753" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H753" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I753" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J753" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K753" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L753" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M753" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N753" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O753" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P753" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B754" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C754" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D754" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E754" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F754" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G754" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H754" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I754" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J754" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K754" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L754" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M754" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N754" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O754" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P754" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B755" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C755" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D755" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E755" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F755" s="21" t="n">
+        <v>99</v>
+      </c>
+      <c r="G755" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H755" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I755" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J755" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K755" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L755" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M755" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N755" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O755" s="23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P755" s="23" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B756" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C756" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D756" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E756" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F756" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G756" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H756" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I756" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J756" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K756" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L756" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M756" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N756" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O756" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P756" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B757" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C757" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D757" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E757" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F757" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G757" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H757" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I757" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J757" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K757" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L757" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M757" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N757" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O757" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P757" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B758" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C758" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D758" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E758" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F758" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G758" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H758" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I758" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J758" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K758" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L758" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M758" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N758" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O758" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P758" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B759" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C759" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D759" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E759" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F759" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G759" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H759" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I759" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J759" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K759" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L759" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M759" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N759" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O759" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P759" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B760" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C760" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D760" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E760" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F760" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G760" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H760" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I760" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J760" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K760" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L760" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M760" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N760" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O760" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P760" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B761" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C761" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D761" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E761" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F761" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G761" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H761" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I761" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J761" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K761" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L761" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M761" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N761" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O761" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P761" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B762" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C762" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D762" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E762" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F762" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G762" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H762" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I762" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J762" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K762" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L762" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M762" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N762" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O762" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P762" s="19" t="n">
+        <v>29.41</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B763" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C763" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D763" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E763" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F763" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G763" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H763" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I763" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J763" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K763" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L763" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M763" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N763" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O763" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P763" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B764" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C764" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D764" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E764" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F764" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="G764" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H764" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I764" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J764" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K764" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L764" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M764" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N764" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O764" s="19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P764" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B765" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C765" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D765" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E765" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F765" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G765" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H765" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I765" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J765" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K765" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L765" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M765" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N765" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O765" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P765" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B766" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C766" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D766" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E766" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F766" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G766" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H766" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I766" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J766" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K766" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L766" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M766" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N766" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O766" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P766" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B767" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C767" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D767" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E767" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F767" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G767" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H767" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I767" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J767" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K767" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L767" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M767" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N767" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O767" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P767" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -44375,7 +46895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -45382,6 +47902,34 @@
         <v>0</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -45394,7 +47942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -45861,6 +48409,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="C36" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P767"/>
+  <dimension ref="A1:P809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -46880,6 +46880,2526 @@
         <v>14.04</v>
       </c>
       <c r="P767" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B768" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C768" s="8" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D768" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E768" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F768" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G768" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H768" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I768" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J768" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K768" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L768" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M768" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N768" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O768" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P768" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B769" s="11" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C769" s="11" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D769" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E769" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F769" s="21" t="n">
+        <v>72</v>
+      </c>
+      <c r="G769" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H769" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I769" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J769" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K769" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L769" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M769" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N769" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O769" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P769" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B770" s="8" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C770" s="8" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D770" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E770" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F770" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G770" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H770" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I770" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J770" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K770" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L770" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M770" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N770" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O770" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P770" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B771" s="11" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C771" s="11" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D771" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E771" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F771" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G771" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H771" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I771" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J771" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K771" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L771" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M771" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N771" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O771" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P771" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B772" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C772" s="8" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D772" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E772" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F772" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G772" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H772" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I772" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J772" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K772" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L772" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M772" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N772" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O772" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P772" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B773" s="11" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C773" s="11" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D773" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E773" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F773" s="21" t="n">
+        <v>64</v>
+      </c>
+      <c r="G773" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H773" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I773" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J773" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K773" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L773" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M773" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N773" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O773" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P773" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B774" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C774" s="8" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D774" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E774" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F774" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G774" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H774" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I774" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J774" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K774" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L774" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M774" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N774" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O774" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P774" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B775" s="11" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C775" s="11" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D775" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E775" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F775" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G775" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H775" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I775" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J775" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K775" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L775" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M775" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N775" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O775" s="23" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P775" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B776" s="8" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C776" s="8" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D776" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E776" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F776" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G776" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H776" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I776" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J776" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K776" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L776" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M776" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N776" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O776" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P776" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B777" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C777" s="11" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D777" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E777" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F777" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G777" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H777" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I777" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J777" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K777" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L777" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M777" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N777" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O777" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P777" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B778" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C778" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D778" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E778" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F778" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G778" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H778" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I778" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J778" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K778" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L778" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M778" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N778" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O778" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P778" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B779" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C779" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D779" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E779" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F779" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G779" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H779" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I779" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J779" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K779" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L779" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M779" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N779" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O779" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P779" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B780" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C780" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D780" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E780" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F780" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="G780" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H780" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I780" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J780" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K780" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L780" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M780" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N780" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O780" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P780" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B781" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C781" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D781" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E781" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F781" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G781" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H781" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I781" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J781" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K781" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L781" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M781" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N781" s="30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O781" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P781" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B782" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C782" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D782" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E782" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F782" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G782" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H782" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I782" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J782" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K782" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L782" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M782" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N782" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O782" s="19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P782" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B783" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C783" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D783" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E783" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F783" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G783" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H783" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I783" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J783" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K783" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L783" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M783" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N783" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O783" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P783" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B784" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C784" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D784" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E784" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F784" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G784" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H784" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I784" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J784" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K784" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L784" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M784" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N784" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O784" s="19" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="P784" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B785" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C785" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D785" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E785" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F785" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G785" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H785" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I785" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J785" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K785" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L785" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M785" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N785" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O785" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P785" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B786" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C786" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D786" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E786" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F786" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G786" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H786" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I786" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J786" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K786" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L786" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M786" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N786" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O786" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P786" s="19" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B787" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C787" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D787" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E787" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F787" s="21" t="n">
+        <v>76</v>
+      </c>
+      <c r="G787" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H787" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I787" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J787" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K787" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L787" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M787" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N787" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O787" s="23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P787" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B788" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C788" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D788" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E788" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F788" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G788" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H788" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I788" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J788" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K788" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L788" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M788" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N788" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O788" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P788" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B789" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C789" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D789" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E789" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F789" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G789" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H789" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I789" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J789" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K789" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L789" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M789" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N789" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O789" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="P789" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B790" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C790" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D790" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E790" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F790" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G790" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H790" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I790" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J790" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K790" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L790" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M790" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N790" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O790" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P790" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B791" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C791" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D791" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E791" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F791" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G791" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H791" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I791" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J791" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K791" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L791" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M791" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N791" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O791" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P791" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B792" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C792" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D792" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E792" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F792" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G792" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H792" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I792" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J792" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K792" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L792" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M792" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N792" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O792" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P792" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B793" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C793" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D793" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E793" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F793" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G793" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H793" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I793" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J793" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K793" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L793" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M793" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N793" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O793" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P793" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B794" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C794" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D794" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E794" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F794" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G794" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H794" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I794" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J794" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K794" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L794" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M794" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N794" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O794" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P794" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B795" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C795" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D795" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E795" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F795" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G795" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H795" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I795" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J795" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K795" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L795" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M795" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N795" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O795" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P795" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B796" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C796" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D796" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E796" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F796" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G796" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H796" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I796" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J796" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K796" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L796" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M796" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N796" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O796" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P796" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B797" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C797" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D797" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E797" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F797" s="21" t="n">
+        <v>99</v>
+      </c>
+      <c r="G797" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H797" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I797" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J797" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K797" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L797" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M797" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N797" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O797" s="23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P797" s="23" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B798" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C798" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D798" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E798" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F798" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G798" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H798" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I798" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J798" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K798" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L798" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M798" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N798" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O798" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P798" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B799" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C799" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D799" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E799" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F799" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G799" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H799" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I799" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J799" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K799" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L799" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M799" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N799" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O799" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P799" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B800" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C800" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D800" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E800" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F800" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G800" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H800" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I800" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J800" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K800" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L800" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M800" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N800" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O800" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P800" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B801" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C801" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D801" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E801" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F801" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G801" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H801" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I801" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J801" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K801" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L801" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M801" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N801" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O801" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P801" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B802" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C802" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D802" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E802" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F802" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G802" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H802" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I802" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J802" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K802" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L802" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M802" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N802" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O802" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P802" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B803" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C803" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D803" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E803" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F803" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G803" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H803" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I803" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J803" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K803" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L803" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M803" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N803" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O803" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P803" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B804" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C804" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D804" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E804" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F804" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G804" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H804" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I804" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J804" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K804" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L804" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M804" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N804" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O804" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P804" s="19" t="n">
+        <v>29.41</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B805" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C805" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D805" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E805" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F805" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G805" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H805" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I805" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J805" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K805" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L805" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M805" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N805" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O805" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P805" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B806" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C806" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D806" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E806" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F806" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="G806" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H806" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I806" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J806" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K806" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L806" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M806" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N806" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O806" s="19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P806" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B807" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C807" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D807" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E807" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F807" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G807" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H807" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I807" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J807" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K807" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L807" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M807" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N807" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O807" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P807" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B808" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C808" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D808" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E808" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F808" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G808" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H808" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I808" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J808" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K808" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L808" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M808" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N808" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O808" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P808" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B809" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C809" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D809" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E809" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F809" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G809" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H809" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I809" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J809" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K809" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L809" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M809" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N809" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O809" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P809" s="23" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1559</v>
+        <v>1569</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P809"/>
+  <dimension ref="A1:P851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -49400,6 +49400,2526 @@
         <v>14.04</v>
       </c>
       <c r="P809" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B810" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C810" s="8" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D810" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E810" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F810" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G810" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H810" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I810" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J810" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K810" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L810" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M810" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N810" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O810" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P810" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B811" s="11" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C811" s="11" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D811" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E811" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F811" s="21" t="n">
+        <v>73</v>
+      </c>
+      <c r="G811" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H811" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I811" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J811" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K811" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L811" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M811" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N811" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O811" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P811" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B812" s="8" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C812" s="8" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D812" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E812" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F812" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G812" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H812" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I812" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J812" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K812" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L812" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M812" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N812" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O812" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P812" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B813" s="11" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C813" s="11" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D813" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E813" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F813" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G813" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H813" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I813" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J813" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K813" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L813" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M813" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N813" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O813" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P813" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B814" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C814" s="8" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D814" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E814" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F814" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G814" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H814" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I814" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J814" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K814" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L814" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M814" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N814" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O814" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P814" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B815" s="11" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C815" s="11" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D815" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E815" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F815" s="21" t="n">
+        <v>65</v>
+      </c>
+      <c r="G815" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H815" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I815" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J815" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K815" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L815" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M815" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N815" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O815" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P815" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B816" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C816" s="8" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D816" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E816" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F816" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G816" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H816" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I816" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J816" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K816" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L816" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M816" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N816" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O816" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P816" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B817" s="11" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C817" s="11" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D817" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E817" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F817" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G817" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H817" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I817" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J817" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K817" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L817" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M817" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N817" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O817" s="23" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P817" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B818" s="8" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C818" s="8" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D818" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E818" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F818" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G818" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H818" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I818" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J818" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K818" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L818" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M818" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N818" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O818" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P818" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B819" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C819" s="11" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D819" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E819" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F819" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G819" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H819" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I819" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J819" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K819" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L819" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M819" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N819" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O819" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P819" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B820" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C820" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D820" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E820" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F820" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G820" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H820" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I820" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J820" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K820" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L820" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M820" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N820" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O820" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P820" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B821" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C821" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D821" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E821" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F821" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G821" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H821" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I821" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J821" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K821" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L821" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M821" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N821" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O821" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P821" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B822" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C822" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D822" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E822" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F822" s="17" t="n">
+        <v>126</v>
+      </c>
+      <c r="G822" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H822" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I822" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J822" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K822" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L822" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M822" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N822" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O822" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P822" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B823" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C823" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D823" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E823" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F823" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G823" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H823" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I823" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J823" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K823" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L823" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M823" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N823" s="30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O823" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P823" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B824" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C824" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D824" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E824" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F824" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G824" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H824" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I824" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J824" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K824" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L824" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M824" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N824" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O824" s="19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P824" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B825" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C825" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D825" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E825" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F825" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G825" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H825" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I825" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J825" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K825" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L825" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M825" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N825" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O825" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P825" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B826" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C826" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D826" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E826" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F826" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G826" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H826" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I826" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J826" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K826" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L826" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M826" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N826" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O826" s="19" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="P826" s="19" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B827" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C827" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D827" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E827" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F827" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G827" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H827" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I827" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J827" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K827" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L827" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M827" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N827" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O827" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P827" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B828" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C828" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D828" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E828" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F828" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G828" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H828" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I828" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J828" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K828" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L828" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M828" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N828" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O828" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P828" s="19" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B829" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C829" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D829" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E829" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F829" s="21" t="n">
+        <v>76</v>
+      </c>
+      <c r="G829" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H829" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I829" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J829" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K829" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L829" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M829" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N829" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O829" s="23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P829" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B830" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C830" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D830" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E830" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F830" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G830" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H830" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I830" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J830" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K830" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L830" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M830" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N830" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O830" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P830" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B831" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C831" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D831" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E831" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F831" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G831" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H831" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I831" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J831" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K831" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L831" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M831" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N831" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O831" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="P831" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B832" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C832" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D832" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E832" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F832" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G832" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H832" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I832" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J832" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K832" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L832" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M832" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N832" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O832" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P832" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B833" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C833" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D833" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E833" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F833" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G833" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H833" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I833" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J833" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K833" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L833" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M833" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N833" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O833" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P833" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B834" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C834" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D834" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E834" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F834" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G834" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H834" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I834" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J834" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K834" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L834" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M834" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N834" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O834" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P834" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B835" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C835" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D835" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E835" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F835" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G835" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H835" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I835" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J835" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K835" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L835" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M835" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N835" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O835" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P835" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B836" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C836" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D836" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E836" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F836" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G836" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H836" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I836" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J836" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K836" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L836" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M836" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N836" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O836" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P836" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B837" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C837" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D837" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E837" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F837" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G837" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H837" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I837" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J837" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K837" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L837" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M837" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N837" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O837" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P837" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B838" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C838" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D838" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E838" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F838" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G838" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H838" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I838" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J838" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K838" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L838" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M838" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N838" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O838" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P838" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B839" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C839" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D839" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E839" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F839" s="21" t="n">
+        <v>101</v>
+      </c>
+      <c r="G839" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H839" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I839" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J839" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K839" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L839" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M839" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N839" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O839" s="23" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P839" s="23" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B840" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C840" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D840" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E840" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F840" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G840" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H840" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I840" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J840" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K840" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L840" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M840" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N840" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O840" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P840" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B841" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C841" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D841" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E841" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F841" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G841" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H841" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I841" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J841" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K841" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L841" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M841" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N841" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O841" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P841" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B842" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C842" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D842" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E842" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F842" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G842" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H842" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I842" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J842" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K842" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L842" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M842" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N842" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O842" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P842" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B843" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C843" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D843" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E843" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F843" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G843" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H843" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I843" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J843" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K843" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L843" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M843" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N843" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O843" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P843" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B844" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C844" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D844" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E844" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F844" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G844" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H844" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I844" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J844" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K844" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L844" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M844" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N844" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O844" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P844" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B845" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C845" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D845" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E845" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F845" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G845" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H845" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I845" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J845" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K845" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L845" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M845" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N845" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O845" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P845" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B846" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C846" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D846" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E846" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F846" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G846" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="H846" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I846" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J846" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K846" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L846" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M846" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N846" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O846" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P846" s="19" t="n">
+        <v>29.41</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B847" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C847" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D847" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E847" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F847" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G847" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H847" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I847" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J847" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K847" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L847" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M847" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N847" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O847" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P847" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B848" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C848" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D848" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E848" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F848" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="G848" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H848" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I848" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J848" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K848" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L848" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M848" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N848" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O848" s="19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P848" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B849" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C849" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D849" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E849" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F849" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G849" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H849" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I849" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J849" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K849" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L849" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M849" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N849" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O849" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P849" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B850" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C850" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D850" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E850" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F850" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G850" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H850" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I850" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J850" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K850" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L850" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M850" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N850" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O850" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P850" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B851" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C851" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D851" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E851" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F851" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G851" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H851" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I851" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J851" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K851" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L851" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M851" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N851" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O851" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P851" s="23" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1569</v>
+        <v>1604</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="B14" s="27" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P851"/>
+  <dimension ref="A1:P893"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -51923,6 +51923,2526 @@
         <v>26.67</v>
       </c>
     </row>
+    <row r="852">
+      <c r="A852" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B852" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C852" s="8" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D852" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E852" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F852" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G852" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H852" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I852" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J852" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K852" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L852" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M852" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N852" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O852" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P852" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B853" s="11" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C853" s="11" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D853" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E853" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F853" s="21" t="n">
+        <v>79</v>
+      </c>
+      <c r="G853" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H853" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I853" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J853" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K853" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L853" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M853" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N853" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O853" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P853" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B854" s="8" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C854" s="8" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D854" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E854" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F854" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G854" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H854" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I854" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J854" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K854" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L854" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M854" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N854" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O854" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P854" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B855" s="11" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C855" s="11" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D855" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E855" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F855" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G855" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H855" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I855" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J855" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K855" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L855" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M855" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N855" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O855" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P855" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B856" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C856" s="8" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D856" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E856" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F856" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G856" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H856" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I856" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J856" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K856" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L856" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M856" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N856" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O856" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P856" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B857" s="11" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C857" s="11" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D857" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E857" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F857" s="21" t="n">
+        <v>72</v>
+      </c>
+      <c r="G857" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H857" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I857" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J857" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K857" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L857" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M857" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N857" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O857" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P857" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B858" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C858" s="8" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D858" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E858" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F858" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G858" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H858" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I858" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J858" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K858" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L858" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M858" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N858" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O858" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P858" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B859" s="11" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C859" s="11" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D859" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E859" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F859" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G859" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H859" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I859" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J859" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K859" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L859" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M859" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N859" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O859" s="23" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P859" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B860" s="8" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C860" s="8" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D860" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E860" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F860" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G860" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H860" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I860" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J860" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K860" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L860" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M860" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N860" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O860" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P860" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B861" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C861" s="11" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D861" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E861" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F861" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G861" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H861" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I861" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J861" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K861" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L861" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M861" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N861" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O861" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P861" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B862" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C862" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D862" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E862" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F862" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G862" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H862" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I862" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J862" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K862" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L862" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M862" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N862" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O862" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P862" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B863" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C863" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D863" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E863" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F863" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G863" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H863" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I863" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J863" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K863" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L863" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M863" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N863" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O863" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P863" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B864" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C864" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D864" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E864" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F864" s="17" t="n">
+        <v>132</v>
+      </c>
+      <c r="G864" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H864" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I864" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J864" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K864" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L864" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M864" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N864" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O864" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P864" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B865" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C865" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D865" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E865" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F865" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G865" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H865" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I865" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J865" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K865" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L865" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M865" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N865" s="30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O865" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P865" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B866" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C866" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D866" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E866" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F866" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G866" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H866" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I866" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J866" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K866" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L866" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M866" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N866" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O866" s="19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P866" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B867" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C867" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D867" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E867" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F867" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G867" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H867" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I867" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J867" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K867" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L867" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M867" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N867" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O867" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P867" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B868" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C868" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D868" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E868" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F868" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G868" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H868" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="I868" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="J868" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K868" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L868" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M868" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N868" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O868" s="19" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="P868" s="19" t="n">
+        <v>77.78</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B869" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C869" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D869" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E869" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F869" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="G869" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H869" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I869" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J869" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K869" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L869" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M869" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N869" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O869" s="23" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P869" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B870" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C870" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D870" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E870" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F870" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G870" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H870" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I870" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J870" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K870" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L870" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M870" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N870" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O870" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P870" s="19" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B871" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C871" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D871" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E871" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F871" s="21" t="n">
+        <v>76</v>
+      </c>
+      <c r="G871" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H871" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I871" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J871" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K871" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L871" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M871" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N871" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O871" s="23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P871" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B872" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C872" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D872" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E872" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F872" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G872" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H872" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I872" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J872" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K872" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L872" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M872" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N872" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O872" s="19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P872" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B873" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C873" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D873" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E873" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F873" s="21" t="n">
+        <v>51</v>
+      </c>
+      <c r="G873" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H873" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I873" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J873" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K873" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L873" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M873" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N873" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O873" s="23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P873" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B874" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C874" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D874" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E874" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F874" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G874" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H874" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I874" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J874" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K874" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L874" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M874" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N874" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O874" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P874" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B875" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C875" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D875" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E875" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F875" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G875" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H875" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I875" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J875" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K875" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L875" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M875" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N875" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O875" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P875" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B876" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C876" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D876" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E876" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F876" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G876" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H876" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I876" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J876" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K876" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L876" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M876" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N876" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O876" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P876" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B877" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C877" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D877" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E877" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F877" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G877" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H877" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I877" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J877" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K877" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L877" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M877" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N877" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O877" s="23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P877" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B878" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C878" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D878" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E878" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F878" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G878" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H878" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I878" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J878" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K878" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L878" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M878" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N878" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O878" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P878" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B879" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C879" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D879" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E879" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F879" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G879" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H879" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I879" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J879" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K879" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L879" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M879" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N879" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O879" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P879" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B880" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C880" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D880" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E880" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F880" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G880" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H880" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I880" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J880" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K880" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L880" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M880" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N880" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O880" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P880" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B881" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C881" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D881" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E881" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F881" s="21" t="n">
+        <v>114</v>
+      </c>
+      <c r="G881" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H881" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I881" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J881" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K881" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L881" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M881" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N881" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O881" s="23" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P881" s="23" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B882" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C882" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D882" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E882" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F882" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G882" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H882" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I882" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J882" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K882" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L882" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M882" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N882" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O882" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P882" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B883" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C883" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D883" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E883" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F883" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G883" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H883" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I883" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J883" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K883" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L883" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M883" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N883" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O883" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P883" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B884" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C884" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D884" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E884" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F884" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G884" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H884" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I884" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J884" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K884" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L884" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M884" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N884" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O884" s="19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P884" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B885" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C885" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D885" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E885" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F885" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G885" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H885" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I885" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J885" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K885" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L885" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M885" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N885" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O885" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P885" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B886" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C886" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D886" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E886" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F886" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="G886" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H886" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I886" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J886" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K886" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L886" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M886" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N886" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O886" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P886" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B887" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C887" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D887" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E887" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F887" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G887" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H887" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I887" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J887" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K887" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L887" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M887" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N887" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O887" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P887" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B888" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C888" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D888" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E888" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F888" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G888" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="H888" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I888" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J888" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K888" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L888" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M888" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N888" s="29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O888" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P888" s="19" t="n">
+        <v>27.78</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B889" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C889" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D889" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E889" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F889" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G889" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H889" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I889" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J889" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K889" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L889" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M889" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N889" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O889" s="23" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P889" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B890" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C890" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D890" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E890" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F890" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="G890" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H890" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I890" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J890" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K890" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L890" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M890" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N890" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O890" s="19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P890" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B891" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C891" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D891" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E891" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F891" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G891" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H891" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I891" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J891" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K891" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L891" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M891" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N891" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O891" s="23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P891" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B892" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C892" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D892" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E892" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F892" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G892" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H892" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I892" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J892" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K892" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L892" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M892" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N892" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O892" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P892" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B893" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C893" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D893" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E893" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F893" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G893" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H893" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I893" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J893" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K893" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L893" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M893" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N893" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O893" s="23" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P893" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -51935,7 +54455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -52970,6 +55490,34 @@
         <v>0</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="C37" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D37" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -52982,7 +55530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -53462,6 +56010,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="C37" s="33" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4"/>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1604</v>
+        <v>1618</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P893"/>
+  <dimension ref="A1:P938"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -54440,6 +54440,2706 @@
         <v>14.04</v>
       </c>
       <c r="P893" s="23" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B894" s="8" t="inlineStr">
+        <is>
+          <t>Как заставить нейросеть писать твоим голосом</t>
+        </is>
+      </c>
+      <c r="C894" s="8" t="inlineStr">
+        <is>
+          <t>6a0319609e1e6a5143cf59f2</t>
+        </is>
+      </c>
+      <c r="D894" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E894" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F894" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G894" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H894" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I894" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J894" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K894" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L894" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M894" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N894" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O894" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P894" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B895" s="11" t="inlineStr">
+        <is>
+          <t>Система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C895" s="11" t="inlineStr">
+        <is>
+          <t>6a0316e9f7cd3124ebb7e2e5</t>
+        </is>
+      </c>
+      <c r="D895" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E895" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F895" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G895" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H895" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I895" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J895" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K895" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L895" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M895" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N895" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O895" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P895" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B896" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети</t>
+        </is>
+      </c>
+      <c r="C896" s="8" t="inlineStr">
+        <is>
+          <t>6a03133bbb2ab60cfd65824b</t>
+        </is>
+      </c>
+      <c r="D896" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E896" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F896" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G896" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H896" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I896" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J896" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K896" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L896" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M896" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N896" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O896" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P896" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B897" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C897" s="11" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D897" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E897" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F897" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G897" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H897" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I897" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J897" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K897" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L897" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M897" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N897" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O897" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P897" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B898" s="8" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C898" s="8" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D898" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E898" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F898" s="17" t="n">
+        <v>81</v>
+      </c>
+      <c r="G898" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H898" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I898" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J898" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K898" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L898" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M898" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N898" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O898" s="19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P898" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B899" s="11" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C899" s="11" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D899" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E899" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F899" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G899" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H899" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I899" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J899" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K899" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L899" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M899" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N899" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O899" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P899" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B900" s="8" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C900" s="8" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D900" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E900" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F900" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G900" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H900" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I900" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J900" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K900" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L900" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M900" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N900" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O900" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P900" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B901" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C901" s="11" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D901" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E901" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F901" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G901" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H901" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I901" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J901" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K901" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L901" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M901" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N901" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O901" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P901" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B902" s="8" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C902" s="8" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D902" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E902" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F902" s="17" t="n">
+        <v>73</v>
+      </c>
+      <c r="G902" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H902" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I902" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J902" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K902" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L902" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M902" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N902" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O902" s="19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P902" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B903" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C903" s="11" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D903" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E903" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F903" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G903" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H903" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I903" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J903" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K903" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L903" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M903" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N903" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O903" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P903" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B904" s="8" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C904" s="8" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D904" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E904" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F904" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G904" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H904" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I904" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J904" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K904" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L904" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M904" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N904" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O904" s="19" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P904" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B905" s="11" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C905" s="11" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D905" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E905" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F905" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G905" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H905" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I905" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J905" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K905" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L905" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M905" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N905" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O905" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P905" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B906" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C906" s="8" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D906" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E906" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F906" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G906" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H906" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I906" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J906" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K906" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L906" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M906" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N906" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O906" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P906" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B907" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C907" s="11" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D907" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E907" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F907" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G907" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H907" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I907" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J907" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K907" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L907" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M907" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N907" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O907" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P907" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B908" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C908" s="8" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D908" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E908" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F908" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G908" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H908" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I908" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J908" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K908" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L908" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M908" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N908" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O908" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P908" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B909" s="11" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C909" s="11" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D909" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E909" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F909" s="21" t="n">
+        <v>132</v>
+      </c>
+      <c r="G909" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H909" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I909" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J909" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K909" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L909" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M909" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N909" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O909" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P909" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B910" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C910" s="8" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D910" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E910" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F910" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G910" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H910" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I910" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J910" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K910" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L910" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M910" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N910" s="29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O910" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P910" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B911" s="11" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C911" s="11" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D911" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E911" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F911" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="G911" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H911" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I911" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J911" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K911" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L911" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M911" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N911" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O911" s="23" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P911" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B912" s="8" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C912" s="8" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D912" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E912" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F912" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G912" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H912" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I912" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J912" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K912" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L912" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M912" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N912" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O912" s="19" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P912" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B913" s="11" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C913" s="11" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D913" s="20" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E913" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F913" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G913" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="H913" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I913" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="J913" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K913" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L913" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M913" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N913" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O913" s="23" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="P913" s="23" t="n">
+        <v>77.78</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B914" s="8" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C914" s="8" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D914" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E914" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F914" s="17" t="n">
+        <v>105</v>
+      </c>
+      <c r="G914" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H914" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I914" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J914" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K914" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L914" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M914" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N914" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O914" s="19" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P914" s="19" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B915" s="11" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C915" s="11" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D915" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E915" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F915" s="21" t="n">
+        <v>84</v>
+      </c>
+      <c r="G915" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H915" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I915" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J915" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K915" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L915" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M915" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N915" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O915" s="23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P915" s="23" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B916" s="8" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C916" s="8" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D916" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E916" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F916" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="G916" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H916" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I916" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J916" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K916" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L916" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M916" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N916" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O916" s="19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P916" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B917" s="11" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C917" s="11" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D917" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E917" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F917" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="G917" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H917" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I917" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J917" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K917" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L917" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M917" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N917" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O917" s="23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P917" s="23" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B918" s="8" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C918" s="8" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D918" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E918" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F918" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="G918" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H918" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I918" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J918" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K918" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L918" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M918" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N918" s="29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O918" s="19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P918" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B919" s="11" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C919" s="11" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D919" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E919" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F919" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="G919" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H919" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I919" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J919" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K919" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L919" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M919" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N919" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O919" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P919" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B920" s="8" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C920" s="8" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D920" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E920" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F920" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="G920" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H920" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I920" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J920" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K920" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L920" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M920" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N920" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O920" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P920" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B921" s="11" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C921" s="11" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D921" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E921" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F921" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="G921" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H921" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I921" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J921" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K921" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L921" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M921" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N921" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O921" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P921" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B922" s="8" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C922" s="8" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D922" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E922" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F922" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="G922" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H922" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I922" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J922" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K922" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L922" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M922" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N922" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O922" s="19" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P922" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B923" s="11" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C923" s="11" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D923" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E923" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F923" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G923" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H923" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I923" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J923" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K923" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L923" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M923" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N923" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O923" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P923" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B924" s="8" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C924" s="8" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D924" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E924" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F924" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G924" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H924" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I924" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J924" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K924" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L924" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M924" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N924" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O924" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P924" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B925" s="11" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C925" s="11" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D925" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E925" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F925" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="G925" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H925" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I925" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J925" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K925" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L925" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M925" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N925" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O925" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P925" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B926" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C926" s="8" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D926" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E926" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F926" s="17" t="n">
+        <v>115</v>
+      </c>
+      <c r="G926" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H926" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I926" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J926" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K926" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L926" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M926" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N926" s="29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O926" s="19" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="P926" s="19" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B927" s="11" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C927" s="11" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D927" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E927" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F927" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G927" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H927" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I927" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J927" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K927" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L927" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M927" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N927" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O927" s="23" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P927" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B928" s="8" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C928" s="8" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D928" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E928" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F928" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="G928" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H928" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I928" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J928" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K928" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L928" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M928" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N928" s="29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O928" s="19" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P928" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B929" s="11" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C929" s="11" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D929" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E929" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F929" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G929" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H929" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I929" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J929" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K929" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L929" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M929" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N929" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O929" s="23" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P929" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B930" s="8" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C930" s="8" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D930" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E930" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F930" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="G930" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H930" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I930" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J930" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K930" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L930" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M930" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N930" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O930" s="19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P930" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B931" s="11" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C931" s="11" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D931" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E931" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F931" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G931" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H931" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I931" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J931" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K931" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L931" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M931" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N931" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O931" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P931" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B932" s="8" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C932" s="8" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D932" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E932" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F932" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G932" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H932" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I932" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J932" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K932" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L932" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M932" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N932" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O932" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P932" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B933" s="11" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C933" s="11" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D933" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E933" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F933" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G933" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="H933" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I933" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J933" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K933" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L933" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M933" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N933" s="30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O933" s="23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P933" s="23" t="n">
+        <v>27.78</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B934" s="8" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C934" s="8" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D934" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E934" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F934" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G934" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H934" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I934" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J934" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K934" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L934" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M934" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N934" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O934" s="19" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P934" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B935" s="11" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C935" s="11" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D935" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E935" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F935" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="G935" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H935" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I935" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J935" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K935" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L935" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M935" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N935" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O935" s="23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P935" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B936" s="8" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C936" s="8" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D936" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E936" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F936" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G936" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H936" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I936" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J936" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K936" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L936" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M936" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N936" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O936" s="19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P936" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B937" s="11" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C937" s="11" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D937" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E937" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F937" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="G937" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H937" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I937" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J937" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K937" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L937" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M937" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N937" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O937" s="23" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P937" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B938" s="8" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C938" s="8" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D938" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E938" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F938" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G938" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H938" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I938" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J938" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K938" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L938" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M938" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N938" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O938" s="19" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P938" s="19" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P938"/>
+  <dimension ref="A1:P983"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -57140,6 +57140,2706 @@
         <v>14.04</v>
       </c>
       <c r="P938" s="19" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B939" s="8" t="inlineStr">
+        <is>
+          <t>Как заставить нейросеть писать твоим голосом</t>
+        </is>
+      </c>
+      <c r="C939" s="8" t="inlineStr">
+        <is>
+          <t>6a0319609e1e6a5143cf59f2</t>
+        </is>
+      </c>
+      <c r="D939" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E939" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F939" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G939" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H939" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I939" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J939" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K939" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L939" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M939" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N939" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O939" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P939" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B940" s="11" t="inlineStr">
+        <is>
+          <t>Система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C940" s="11" t="inlineStr">
+        <is>
+          <t>6a0316e9f7cd3124ebb7e2e5</t>
+        </is>
+      </c>
+      <c r="D940" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E940" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F940" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G940" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H940" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I940" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J940" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K940" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L940" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M940" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N940" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O940" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P940" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B941" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети</t>
+        </is>
+      </c>
+      <c r="C941" s="8" t="inlineStr">
+        <is>
+          <t>6a03133bbb2ab60cfd65824b</t>
+        </is>
+      </c>
+      <c r="D941" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E941" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F941" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G941" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H941" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I941" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J941" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K941" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L941" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M941" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N941" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O941" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P941" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B942" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C942" s="11" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D942" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E942" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F942" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G942" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H942" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I942" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J942" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K942" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L942" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M942" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N942" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O942" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P942" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B943" s="8" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C943" s="8" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D943" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E943" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F943" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G943" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H943" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I943" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J943" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K943" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L943" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M943" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N943" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O943" s="19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P943" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B944" s="11" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C944" s="11" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D944" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E944" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F944" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G944" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H944" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I944" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J944" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K944" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L944" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M944" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N944" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O944" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P944" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B945" s="8" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C945" s="8" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D945" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E945" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F945" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G945" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H945" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I945" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J945" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K945" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L945" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M945" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N945" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O945" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P945" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B946" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C946" s="11" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D946" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E946" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F946" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G946" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H946" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I946" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J946" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K946" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L946" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M946" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N946" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O946" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P946" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B947" s="8" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C947" s="8" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D947" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E947" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F947" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="G947" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H947" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I947" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J947" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K947" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L947" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M947" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N947" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O947" s="19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P947" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B948" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C948" s="11" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D948" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E948" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F948" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G948" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H948" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I948" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J948" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K948" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L948" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M948" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N948" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O948" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P948" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B949" s="8" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C949" s="8" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D949" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E949" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F949" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G949" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H949" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I949" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J949" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K949" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L949" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M949" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N949" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O949" s="19" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="P949" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B950" s="11" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C950" s="11" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D950" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E950" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F950" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G950" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H950" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I950" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J950" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K950" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L950" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M950" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N950" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O950" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P950" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B951" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C951" s="8" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D951" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E951" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F951" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G951" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H951" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I951" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J951" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K951" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L951" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M951" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N951" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O951" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P951" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B952" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C952" s="11" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D952" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E952" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F952" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G952" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H952" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I952" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J952" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K952" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L952" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M952" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N952" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O952" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P952" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B953" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C953" s="8" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D953" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E953" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F953" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G953" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H953" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I953" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J953" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K953" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L953" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M953" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N953" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O953" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P953" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B954" s="11" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C954" s="11" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D954" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E954" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F954" s="21" t="n">
+        <v>132</v>
+      </c>
+      <c r="G954" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H954" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I954" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J954" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K954" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L954" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M954" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N954" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O954" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P954" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B955" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C955" s="8" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D955" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E955" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F955" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G955" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H955" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I955" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J955" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K955" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L955" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M955" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N955" s="29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O955" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P955" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B956" s="11" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C956" s="11" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D956" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E956" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F956" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="G956" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H956" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I956" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J956" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K956" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L956" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M956" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N956" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O956" s="23" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P956" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B957" s="8" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C957" s="8" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D957" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E957" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F957" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G957" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H957" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I957" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J957" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K957" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L957" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M957" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N957" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O957" s="19" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P957" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B958" s="11" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C958" s="11" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D958" s="20" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E958" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F958" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G958" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="H958" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I958" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="J958" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K958" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L958" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M958" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N958" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O958" s="23" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="P958" s="23" t="n">
+        <v>77.78</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B959" s="8" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C959" s="8" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D959" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E959" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F959" s="17" t="n">
+        <v>105</v>
+      </c>
+      <c r="G959" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H959" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I959" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J959" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K959" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L959" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M959" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N959" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O959" s="19" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P959" s="19" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B960" s="11" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C960" s="11" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D960" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E960" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F960" s="21" t="n">
+        <v>84</v>
+      </c>
+      <c r="G960" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H960" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I960" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J960" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K960" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L960" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M960" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N960" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O960" s="23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P960" s="23" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B961" s="8" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C961" s="8" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D961" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E961" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F961" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="G961" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H961" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I961" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J961" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K961" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L961" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M961" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N961" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O961" s="19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P961" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B962" s="11" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C962" s="11" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D962" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E962" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F962" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="G962" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H962" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I962" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J962" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K962" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L962" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M962" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N962" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O962" s="23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P962" s="23" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B963" s="8" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C963" s="8" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D963" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E963" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F963" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="G963" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H963" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I963" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J963" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K963" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L963" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M963" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N963" s="29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O963" s="19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P963" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B964" s="11" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C964" s="11" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D964" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E964" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F964" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="G964" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H964" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I964" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J964" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K964" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L964" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M964" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N964" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O964" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P964" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B965" s="8" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C965" s="8" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D965" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E965" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F965" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="G965" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H965" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I965" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J965" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K965" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L965" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M965" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N965" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O965" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P965" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B966" s="11" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C966" s="11" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D966" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E966" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F966" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="G966" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H966" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I966" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J966" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K966" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L966" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M966" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N966" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O966" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P966" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B967" s="8" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C967" s="8" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D967" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E967" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F967" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="G967" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H967" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I967" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J967" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K967" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L967" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M967" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N967" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O967" s="19" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P967" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B968" s="11" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C968" s="11" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D968" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E968" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F968" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G968" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H968" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I968" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J968" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K968" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L968" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M968" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N968" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O968" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P968" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B969" s="8" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C969" s="8" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D969" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E969" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F969" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G969" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H969" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I969" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J969" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K969" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L969" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M969" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N969" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O969" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P969" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B970" s="11" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C970" s="11" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D970" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E970" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F970" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="G970" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H970" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I970" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J970" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K970" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L970" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M970" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N970" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O970" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P970" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B971" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C971" s="8" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D971" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E971" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F971" s="17" t="n">
+        <v>115</v>
+      </c>
+      <c r="G971" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H971" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I971" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J971" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K971" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L971" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M971" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N971" s="29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O971" s="19" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="P971" s="19" t="n">
+        <v>41.67</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B972" s="11" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C972" s="11" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D972" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E972" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F972" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G972" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H972" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I972" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J972" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K972" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L972" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M972" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N972" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O972" s="23" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P972" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B973" s="8" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C973" s="8" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D973" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E973" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F973" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="G973" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H973" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I973" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J973" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K973" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L973" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M973" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N973" s="29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O973" s="19" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P973" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B974" s="11" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C974" s="11" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D974" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E974" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F974" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G974" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H974" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I974" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J974" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K974" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L974" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M974" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N974" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O974" s="23" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P974" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B975" s="8" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C975" s="8" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D975" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E975" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F975" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="G975" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H975" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I975" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J975" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K975" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L975" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M975" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N975" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O975" s="19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P975" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B976" s="11" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C976" s="11" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D976" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E976" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F976" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G976" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H976" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I976" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J976" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K976" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L976" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M976" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N976" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O976" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P976" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B977" s="8" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C977" s="8" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D977" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E977" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F977" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G977" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H977" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I977" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J977" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K977" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L977" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M977" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N977" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O977" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P977" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B978" s="11" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C978" s="11" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D978" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E978" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F978" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G978" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="H978" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I978" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J978" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K978" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L978" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M978" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N978" s="30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O978" s="23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P978" s="23" t="n">
+        <v>27.78</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B979" s="8" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C979" s="8" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D979" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E979" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F979" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G979" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H979" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I979" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J979" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K979" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L979" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M979" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N979" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O979" s="19" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P979" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B980" s="11" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C980" s="11" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D980" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E980" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F980" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="G980" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H980" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I980" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J980" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K980" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L980" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M980" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N980" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O980" s="23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P980" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B981" s="8" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C981" s="8" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D981" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E981" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F981" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G981" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H981" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I981" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J981" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K981" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L981" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M981" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N981" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O981" s="19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P981" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B982" s="11" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C982" s="11" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D982" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E982" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F982" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="G982" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H982" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I982" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J982" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K982" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L982" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M982" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N982" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O982" s="23" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P982" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B983" s="8" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C983" s="8" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D983" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E983" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F983" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G983" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H983" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I983" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J983" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K983" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L983" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M983" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N983" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O983" s="19" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P983" s="19" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1622</v>
+        <v>1644</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P983"/>
+  <dimension ref="A1:P1028"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -59843,6 +59843,2706 @@
         <v>26.67</v>
       </c>
     </row>
+    <row r="984">
+      <c r="A984" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B984" s="8" t="inlineStr">
+        <is>
+          <t>Как заставить нейросеть писать твоим голосом</t>
+        </is>
+      </c>
+      <c r="C984" s="8" t="inlineStr">
+        <is>
+          <t>6a0319609e1e6a5143cf59f2</t>
+        </is>
+      </c>
+      <c r="D984" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E984" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F984" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G984" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H984" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I984" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J984" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K984" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L984" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M984" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N984" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O984" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P984" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B985" s="11" t="inlineStr">
+        <is>
+          <t>Система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C985" s="11" t="inlineStr">
+        <is>
+          <t>6a0316e9f7cd3124ebb7e2e5</t>
+        </is>
+      </c>
+      <c r="D985" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E985" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F985" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G985" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H985" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I985" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J985" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K985" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L985" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M985" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N985" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O985" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P985" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B986" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети</t>
+        </is>
+      </c>
+      <c r="C986" s="8" t="inlineStr">
+        <is>
+          <t>6a03133bbb2ab60cfd65824b</t>
+        </is>
+      </c>
+      <c r="D986" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E986" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F986" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G986" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H986" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I986" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J986" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K986" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L986" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M986" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N986" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O986" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P986" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B987" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C987" s="11" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D987" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E987" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F987" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G987" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H987" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I987" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J987" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K987" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L987" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M987" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N987" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O987" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P987" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B988" s="8" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C988" s="8" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D988" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E988" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F988" s="17" t="n">
+        <v>91</v>
+      </c>
+      <c r="G988" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H988" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I988" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J988" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K988" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L988" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M988" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N988" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O988" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P988" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B989" s="11" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C989" s="11" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D989" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E989" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F989" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G989" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H989" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I989" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J989" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K989" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L989" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M989" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N989" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O989" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P989" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B990" s="8" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C990" s="8" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D990" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E990" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F990" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G990" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H990" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I990" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J990" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K990" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L990" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M990" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N990" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O990" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P990" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B991" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C991" s="11" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D991" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E991" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F991" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G991" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H991" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I991" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J991" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K991" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L991" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M991" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N991" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O991" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P991" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B992" s="8" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C992" s="8" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D992" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E992" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F992" s="17" t="n">
+        <v>79</v>
+      </c>
+      <c r="G992" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H992" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I992" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J992" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K992" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L992" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M992" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N992" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O992" s="19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P992" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B993" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C993" s="11" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D993" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E993" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F993" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G993" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H993" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I993" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J993" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K993" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L993" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M993" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N993" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O993" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P993" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B994" s="8" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C994" s="8" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D994" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E994" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F994" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G994" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H994" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I994" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J994" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K994" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L994" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M994" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N994" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O994" s="19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P994" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B995" s="11" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C995" s="11" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D995" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E995" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F995" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G995" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H995" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I995" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J995" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K995" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L995" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M995" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N995" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O995" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P995" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B996" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C996" s="8" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D996" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E996" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F996" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G996" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H996" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I996" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J996" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K996" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L996" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M996" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N996" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O996" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P996" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B997" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C997" s="11" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D997" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E997" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F997" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G997" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H997" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I997" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J997" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K997" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L997" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M997" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N997" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O997" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P997" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B998" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C998" s="8" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D998" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E998" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F998" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G998" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H998" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I998" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J998" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K998" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L998" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M998" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N998" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O998" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P998" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B999" s="11" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C999" s="11" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D999" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E999" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F999" s="21" t="n">
+        <v>131</v>
+      </c>
+      <c r="G999" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H999" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I999" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J999" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K999" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L999" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M999" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N999" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O999" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P999" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1000" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1000" s="8" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D1000" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1000" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F1000" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1000" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1000" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1000" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1000" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1000" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1000" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1000" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1000" s="29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O1000" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1000" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1001" s="11" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C1001" s="11" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D1001" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1001" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F1001" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1001" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1001" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1001" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1001" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1001" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1001" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1001" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1001" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1001" s="23" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P1001" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1002" s="8" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C1002" s="8" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D1002" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1002" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1002" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1002" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1002" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1002" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1002" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1002" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1002" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1002" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1002" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1002" s="19" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P1002" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1003" s="11" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C1003" s="11" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D1003" s="20" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E1003" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1003" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1003" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1003" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1003" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="J1003" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1003" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1003" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1003" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1003" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1003" s="23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P1003" s="23" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1004" s="8" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C1004" s="8" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D1004" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1004" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F1004" s="17" t="n">
+        <v>105</v>
+      </c>
+      <c r="G1004" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1004" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1004" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1004" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1004" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1004" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1004" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1004" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1004" s="19" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P1004" s="19" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1005" s="11" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C1005" s="11" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D1005" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1005" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F1005" s="21" t="n">
+        <v>84</v>
+      </c>
+      <c r="G1005" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1005" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1005" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1005" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1005" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1005" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1005" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1005" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1005" s="23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P1005" s="23" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1006" s="8" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C1006" s="8" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D1006" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1006" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F1006" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="G1006" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1006" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1006" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1006" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1006" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1006" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1006" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1006" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O1006" s="19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P1006" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1007" s="11" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C1007" s="11" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D1007" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1007" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1007" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1007" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1007" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1007" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1007" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1007" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1007" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1007" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1007" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1007" s="23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P1007" s="23" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1008" s="8" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C1008" s="8" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D1008" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1008" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1008" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1008" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1008" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1008" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1008" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1008" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1008" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1008" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1008" s="29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O1008" s="19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P1008" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1009" s="11" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C1009" s="11" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D1009" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1009" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1009" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1009" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1009" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1009" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1009" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1009" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1009" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1009" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1009" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1009" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1009" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1010" s="8" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C1010" s="8" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D1010" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1010" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1010" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1010" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1010" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1010" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1010" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1010" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1010" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1010" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1010" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1010" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1010" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1011" s="11" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1011" s="11" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D1011" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1011" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1011" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="G1011" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1011" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1011" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1011" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1011" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1011" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1011" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1011" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1011" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1011" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1012" s="8" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C1012" s="8" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D1012" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1012" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1012" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="G1012" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1012" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1012" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1012" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1012" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1012" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1012" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1012" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1012" s="19" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P1012" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1013" s="11" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C1013" s="11" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D1013" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1013" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1013" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1013" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1013" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1013" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1013" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1013" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1013" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1013" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1013" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1013" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1013" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1014" s="8" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1014" s="8" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D1014" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1014" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1014" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G1014" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1014" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1014" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1014" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1014" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1014" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1014" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1014" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1014" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1014" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1015" s="11" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C1015" s="11" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D1015" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1015" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1015" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="G1015" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1015" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1015" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1015" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1015" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1015" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1015" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1015" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1015" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1015" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1016" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C1016" s="8" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D1016" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1016" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1016" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="G1016" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1016" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1016" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1016" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1016" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1016" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1016" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1016" s="29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O1016" s="19" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P1016" s="19" t="n">
+        <v>38.46</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1017" s="11" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C1017" s="11" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D1017" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1017" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F1017" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1017" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1017" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1017" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1017" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1017" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1017" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1017" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1017" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O1017" s="23" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P1017" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1018" s="8" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C1018" s="8" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D1018" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1018" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1018" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="G1018" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1018" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1018" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1018" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1018" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1018" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1018" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1018" s="29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O1018" s="19" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P1018" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1019" s="11" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C1019" s="11" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D1019" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1019" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1019" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1019" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1019" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1019" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1019" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1019" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1019" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1019" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1019" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1019" s="23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P1019" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1020" s="8" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C1020" s="8" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D1020" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1020" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1020" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1020" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1020" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1020" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1020" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1020" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1020" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1020" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1020" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1020" s="19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P1020" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1021" s="11" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C1021" s="11" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D1021" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1021" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1021" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1021" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1021" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1021" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1021" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1021" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1021" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1021" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1021" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1021" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1021" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1022" s="8" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C1022" s="8" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D1022" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1022" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1022" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1022" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1022" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1022" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1022" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1022" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1022" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1022" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1022" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1022" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1022" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1023" s="11" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C1023" s="11" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D1023" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1023" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1023" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1023" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1023" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1023" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1023" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1023" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1023" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1023" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1023" s="30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O1023" s="23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P1023" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1024" s="8" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C1024" s="8" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D1024" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1024" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F1024" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1024" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1024" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1024" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1024" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1024" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1024" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1024" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1024" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O1024" s="19" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P1024" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1025" s="11" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C1025" s="11" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D1025" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1025" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F1025" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="G1025" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1025" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1025" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1025" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1025" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1025" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1025" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1025" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O1025" s="23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P1025" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1026" s="8" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C1026" s="8" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D1026" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1026" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1026" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1026" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1026" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1026" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1026" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1026" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1026" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1026" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1026" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1026" s="19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P1026" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1027" s="11" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C1027" s="11" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D1027" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1027" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1027" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1027" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1027" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1027" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1027" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1027" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1027" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1027" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1027" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1027" s="23" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P1027" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1028" s="8" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C1028" s="8" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D1028" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1028" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F1028" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G1028" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1028" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1028" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1028" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1028" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1028" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1028" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1028" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O1028" s="19" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P1028" s="19" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -59855,7 +62555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -60918,6 +63618,34 @@
         <v>0</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -60930,7 +63658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -61423,6 +64151,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="C38" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4"/>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1028"/>
+  <dimension ref="A1:P1075"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -62540,6 +62540,2826 @@
         <v>14.04</v>
       </c>
       <c r="P1028" s="19" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1029" s="8" t="inlineStr">
+        <is>
+          <t>ИИ снова написал «не то». Дело не в промпте</t>
+        </is>
+      </c>
+      <c r="C1029" s="8" t="inlineStr">
+        <is>
+          <t>6a045fb61b306979e41e249a</t>
+        </is>
+      </c>
+      <c r="D1029" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1029" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1029" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1029" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1029" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1029" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1029" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1029" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1029" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1029" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1029" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1029" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1029" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1030" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент для анализа аудитории: почему он бьёт точнее любого опроса</t>
+        </is>
+      </c>
+      <c r="C1030" s="11" t="inlineStr">
+        <is>
+          <t>6a04552f109a6c68d8b08a43</t>
+        </is>
+      </c>
+      <c r="D1030" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1030" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1030" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1030" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1030" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1030" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1030" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1030" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1030" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1030" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1030" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1030" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1030" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1031" s="8" t="inlineStr">
+        <is>
+          <t>Как заставить нейросеть писать твоим голосом</t>
+        </is>
+      </c>
+      <c r="C1031" s="8" t="inlineStr">
+        <is>
+          <t>6a0319609e1e6a5143cf59f2</t>
+        </is>
+      </c>
+      <c r="D1031" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1031" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1031" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1031" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1031" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1031" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1031" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1031" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1031" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1031" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1031" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1031" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1031" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1032" s="11" t="inlineStr">
+        <is>
+          <t>Система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1032" s="11" t="inlineStr">
+        <is>
+          <t>6a0316e9f7cd3124ebb7e2e5</t>
+        </is>
+      </c>
+      <c r="D1032" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1032" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1032" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1032" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1032" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1032" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1032" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1032" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1032" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1032" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1032" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1032" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1032" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1033" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети</t>
+        </is>
+      </c>
+      <c r="C1033" s="8" t="inlineStr">
+        <is>
+          <t>6a03133bbb2ab60cfd65824b</t>
+        </is>
+      </c>
+      <c r="D1033" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1033" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1033" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1033" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1033" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1033" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1033" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1033" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1033" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1033" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1033" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1033" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1033" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1034" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C1034" s="11" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D1034" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1034" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1034" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1034" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1034" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1034" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1034" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1034" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1034" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1034" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1034" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1034" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1034" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1035" s="8" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1035" s="8" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D1035" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1035" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1035" s="17" t="n">
+        <v>91</v>
+      </c>
+      <c r="G1035" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1035" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1035" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1035" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1035" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1035" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1035" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1035" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1035" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P1035" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1036" s="11" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C1036" s="11" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D1036" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1036" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1036" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1036" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1036" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1036" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1036" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1036" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1036" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1036" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1036" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1036" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1036" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1037" s="8" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C1037" s="8" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D1037" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1037" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1037" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1037" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1037" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1037" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1037" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1037" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1037" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1037" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1037" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1037" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1037" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1038" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1038" s="11" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D1038" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1038" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1038" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1038" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1038" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1038" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1038" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1038" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1038" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1038" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1038" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1038" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1038" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1039" s="8" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C1039" s="8" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D1039" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1039" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1039" s="17" t="n">
+        <v>79</v>
+      </c>
+      <c r="G1039" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1039" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1039" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1039" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1039" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1039" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1039" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1039" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1039" s="19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P1039" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1040" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C1040" s="11" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D1040" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1040" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1040" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1040" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1040" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1040" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1040" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1040" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1040" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1040" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1040" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1040" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1040" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1041" s="8" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C1041" s="8" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D1041" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1041" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1041" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1041" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1041" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1041" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1041" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1041" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1041" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1041" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1041" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1041" s="19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P1041" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1042" s="11" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C1042" s="11" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D1042" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1042" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1042" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1042" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1042" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1042" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1042" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1042" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1042" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1042" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1042" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1042" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1042" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1043" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C1043" s="8" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D1043" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1043" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1043" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1043" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1043" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1043" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1043" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1043" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1043" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1043" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1043" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1043" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1043" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1044" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C1044" s="11" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D1044" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1044" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1044" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1044" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1044" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1044" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1044" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1044" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1044" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1044" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1044" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1044" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1044" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1045" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C1045" s="8" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D1045" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1045" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1045" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1045" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1045" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1045" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1045" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1045" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1045" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1045" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1045" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O1045" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1045" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1046" s="11" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C1046" s="11" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D1046" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1046" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F1046" s="21" t="n">
+        <v>131</v>
+      </c>
+      <c r="G1046" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1046" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1046" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1046" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1046" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1046" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1046" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1046" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1046" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1046" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1047" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1047" s="8" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D1047" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1047" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F1047" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1047" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1047" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1047" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1047" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1047" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1047" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1047" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1047" s="29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O1047" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1047" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1048" s="11" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C1048" s="11" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D1048" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1048" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F1048" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1048" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1048" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1048" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1048" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1048" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1048" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1048" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1048" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1048" s="23" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P1048" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1049" s="8" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C1049" s="8" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D1049" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1049" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1049" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1049" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1049" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1049" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1049" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1049" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1049" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1049" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1049" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1049" s="19" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P1049" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1050" s="11" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C1050" s="11" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D1050" s="20" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E1050" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1050" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1050" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1050" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1050" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="J1050" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1050" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1050" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1050" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1050" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1050" s="23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P1050" s="23" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1051" s="8" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C1051" s="8" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D1051" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1051" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F1051" s="17" t="n">
+        <v>105</v>
+      </c>
+      <c r="G1051" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1051" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1051" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1051" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1051" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1051" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1051" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1051" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1051" s="19" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="P1051" s="19" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1052" s="11" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C1052" s="11" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D1052" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1052" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F1052" s="21" t="n">
+        <v>84</v>
+      </c>
+      <c r="G1052" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1052" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1052" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1052" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1052" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1052" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1052" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1052" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1052" s="23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P1052" s="23" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1053" s="8" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C1053" s="8" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D1053" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1053" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F1053" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="G1053" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1053" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1053" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1053" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1053" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1053" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1053" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1053" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O1053" s="19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P1053" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1054" s="11" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C1054" s="11" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D1054" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1054" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1054" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1054" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1054" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1054" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1054" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1054" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1054" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1054" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1054" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1054" s="23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="P1054" s="23" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1055" s="8" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C1055" s="8" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D1055" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1055" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1055" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1055" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1055" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1055" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1055" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1055" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1055" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1055" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1055" s="29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O1055" s="19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P1055" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1056" s="11" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C1056" s="11" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D1056" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1056" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1056" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1056" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1056" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1056" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1056" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1056" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1056" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1056" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1056" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1056" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1056" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1057" s="8" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C1057" s="8" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D1057" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1057" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1057" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1057" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1057" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1057" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1057" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1057" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1057" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1057" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1057" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1057" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1057" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1058" s="11" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1058" s="11" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D1058" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1058" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1058" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="G1058" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1058" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1058" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1058" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1058" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1058" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1058" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1058" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1058" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1058" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1059" s="8" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C1059" s="8" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D1059" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1059" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1059" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="G1059" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1059" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1059" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1059" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1059" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1059" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1059" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1059" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1059" s="19" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="P1059" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1060" s="11" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C1060" s="11" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D1060" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1060" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1060" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1060" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1060" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1060" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1060" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1060" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1060" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1060" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1060" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1060" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1060" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1061" s="8" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1061" s="8" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D1061" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1061" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1061" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G1061" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1061" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1061" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1061" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1061" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1061" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1061" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1061" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1061" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1061" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1062" s="11" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C1062" s="11" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D1062" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1062" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1062" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="G1062" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1062" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1062" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1062" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1062" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1062" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1062" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1062" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1062" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1062" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1063" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C1063" s="8" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D1063" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1063" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1063" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="G1063" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1063" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1063" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1063" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1063" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1063" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1063" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1063" s="29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O1063" s="19" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="P1063" s="19" t="n">
+        <v>38.46</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1064" s="11" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C1064" s="11" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D1064" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1064" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F1064" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1064" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1064" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1064" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1064" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1064" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1064" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1064" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1064" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O1064" s="23" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P1064" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1065" s="8" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C1065" s="8" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D1065" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1065" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1065" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="G1065" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1065" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1065" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1065" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1065" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1065" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1065" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1065" s="29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O1065" s="19" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P1065" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1066" s="11" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C1066" s="11" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D1066" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1066" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1066" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1066" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1066" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1066" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1066" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1066" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1066" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1066" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1066" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1066" s="23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P1066" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1067" s="8" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C1067" s="8" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D1067" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1067" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1067" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1067" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1067" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1067" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1067" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1067" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1067" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1067" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1067" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1067" s="19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P1067" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1068" s="11" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C1068" s="11" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D1068" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1068" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1068" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1068" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1068" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1068" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1068" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1068" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1068" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1068" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1068" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1068" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1068" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1069" s="8" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C1069" s="8" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D1069" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1069" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1069" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1069" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1069" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1069" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1069" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1069" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1069" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1069" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1069" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1069" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1069" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1070" s="11" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C1070" s="11" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D1070" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1070" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1070" s="21" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1070" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1070" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1070" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1070" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1070" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1070" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1070" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1070" s="30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O1070" s="23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P1070" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1071" s="8" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C1071" s="8" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D1071" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1071" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F1071" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1071" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1071" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1071" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1071" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1071" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1071" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1071" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1071" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O1071" s="19" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="P1071" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1072" s="11" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C1072" s="11" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D1072" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1072" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F1072" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="G1072" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1072" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1072" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1072" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1072" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1072" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1072" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1072" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O1072" s="23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P1072" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1073" s="8" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C1073" s="8" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D1073" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1073" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1073" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1073" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1073" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1073" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1073" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1073" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1073" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1073" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1073" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1073" s="19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P1073" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1074" s="11" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C1074" s="11" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D1074" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1074" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1074" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1074" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1074" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1074" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1074" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1074" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1074" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1074" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1074" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1074" s="23" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P1074" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1075" s="8" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C1075" s="8" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D1075" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1075" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F1075" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G1075" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1075" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1075" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1075" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1075" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1075" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1075" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1075" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O1075" s="19" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="P1075" s="19" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4"/>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1644</v>
+        <v>1700</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1075"/>
+  <dimension ref="A1:P1125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -65360,6 +65360,3006 @@
         <v>14.04</v>
       </c>
       <c r="P1075" s="19" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1076" s="8" t="inlineStr">
+        <is>
+          <t>Что такое цепочка агентов и зачем она нужна маркетологу</t>
+        </is>
+      </c>
+      <c r="C1076" s="8" t="inlineStr">
+        <is>
+          <t>6a046691a62f4604067b7c83</t>
+        </is>
+      </c>
+      <c r="D1076" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1076" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1076" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1076" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1076" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1076" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1076" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1076" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1076" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1076" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1076" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1076" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1076" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1077" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинг в одиночку: 6 ИИ-агентов вместо отдела из пяти человек</t>
+        </is>
+      </c>
+      <c r="C1077" s="11" t="inlineStr">
+        <is>
+          <t>6a04635ea62f46040676a741</t>
+        </is>
+      </c>
+      <c r="D1077" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1077" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1077" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1077" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1077" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1077" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1077" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1077" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1077" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1077" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1077" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1077" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1077" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1078" s="8" t="inlineStr">
+        <is>
+          <t>ИИ снова написал «не то». Дело не в промпте</t>
+        </is>
+      </c>
+      <c r="C1078" s="8" t="inlineStr">
+        <is>
+          <t>6a045fb61b306979e41e249a</t>
+        </is>
+      </c>
+      <c r="D1078" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1078" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1078" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1078" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1078" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1078" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1078" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1078" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1078" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1078" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1078" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1078" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1078" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1079" s="11" t="inlineStr">
+        <is>
+          <t>Контент-план на месяц за 20 минут. Без воды и страданий над пустой табличкой</t>
+        </is>
+      </c>
+      <c r="C1079" s="11" t="inlineStr">
+        <is>
+          <t>6a045b2229363d25f247f1c2</t>
+        </is>
+      </c>
+      <c r="D1079" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1079" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1079" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1079" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1079" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1079" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1079" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1079" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1079" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1079" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1079" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1079" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1079" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1080" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агент для анализа аудитории: почему он бьёт точнее любого опроса</t>
+        </is>
+      </c>
+      <c r="C1080" s="8" t="inlineStr">
+        <is>
+          <t>6a04552f109a6c68d8b08a43</t>
+        </is>
+      </c>
+      <c r="D1080" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1080" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1080" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1080" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1080" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1080" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1080" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1080" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1080" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1080" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1080" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1080" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1080" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1081" s="11" t="inlineStr">
+        <is>
+          <t>Как заставить нейросеть писать твоим голосом</t>
+        </is>
+      </c>
+      <c r="C1081" s="11" t="inlineStr">
+        <is>
+          <t>6a0319609e1e6a5143cf59f2</t>
+        </is>
+      </c>
+      <c r="D1081" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1081" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1081" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1081" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1081" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1081" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1081" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1081" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1081" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1081" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1081" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1081" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1081" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1082" s="8" t="inlineStr">
+        <is>
+          <t>Система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1082" s="8" t="inlineStr">
+        <is>
+          <t>6a0316e9f7cd3124ebb7e2e5</t>
+        </is>
+      </c>
+      <c r="D1082" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1082" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1082" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1082" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1082" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1082" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1082" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1082" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1082" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1082" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1082" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1082" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1082" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1083" s="11" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети</t>
+        </is>
+      </c>
+      <c r="C1083" s="11" t="inlineStr">
+        <is>
+          <t>6a03133bbb2ab60cfd65824b</t>
+        </is>
+      </c>
+      <c r="D1083" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1083" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1083" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1083" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1083" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1083" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1083" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1083" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1083" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1083" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1083" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1083" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1083" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1084" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C1084" s="8" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D1084" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1084" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1084" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1084" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1084" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1084" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1084" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1084" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1084" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1084" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1084" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1084" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1084" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1085" s="11" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1085" s="11" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D1085" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1085" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1085" s="21" t="n">
+        <v>93</v>
+      </c>
+      <c r="G1085" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1085" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1085" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1085" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1085" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1085" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1085" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1085" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1085" s="23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P1085" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1086" s="8" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C1086" s="8" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D1086" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1086" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1086" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="G1086" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1086" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1086" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1086" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1086" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1086" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1086" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1086" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1086" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1086" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1087" s="11" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C1087" s="11" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D1087" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1087" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1087" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1087" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1087" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1087" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1087" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1087" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1087" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1087" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1087" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1087" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1087" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1088" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1088" s="8" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D1088" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1088" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1088" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1088" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1088" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1088" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1088" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1088" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1088" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1088" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1088" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1088" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1088" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1089" s="11" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C1089" s="11" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D1089" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1089" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1089" s="21" t="n">
+        <v>81</v>
+      </c>
+      <c r="G1089" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1089" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1089" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1089" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1089" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1089" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1089" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1089" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1089" s="23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P1089" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1090" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C1090" s="8" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D1090" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1090" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1090" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1090" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1090" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1090" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1090" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1090" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1090" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1090" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1090" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1090" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1090" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1091" s="11" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C1091" s="11" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D1091" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1091" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1091" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1091" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1091" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1091" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1091" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1091" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1091" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1091" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1091" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1091" s="23" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P1091" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1092" s="8" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C1092" s="8" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D1092" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1092" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1092" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1092" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1092" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1092" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1092" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1092" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1092" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1092" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1092" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1092" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1092" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1093" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C1093" s="11" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D1093" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1093" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1093" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1093" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1093" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1093" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1093" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1093" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1093" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1093" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1093" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1093" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1093" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1094" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C1094" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D1094" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1094" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1094" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1094" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1094" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1094" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1094" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1094" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1094" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1094" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1094" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1094" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1094" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1095" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C1095" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D1095" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1095" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1095" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1095" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1095" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1095" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1095" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1095" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1095" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1095" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1095" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O1095" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1095" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1096" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C1096" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D1096" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1096" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F1096" s="17" t="n">
+        <v>132</v>
+      </c>
+      <c r="G1096" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1096" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1096" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1096" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1096" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1096" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1096" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1096" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1096" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1096" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1097" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1097" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D1097" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1097" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F1097" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1097" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1097" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1097" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1097" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1097" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1097" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1097" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1097" s="30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O1097" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1097" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1098" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C1098" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D1098" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1098" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F1098" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1098" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1098" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1098" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1098" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1098" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1098" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1098" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1098" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1098" s="19" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P1098" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1099" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C1099" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D1099" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1099" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1099" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1099" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1099" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1099" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1099" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1099" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1099" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1099" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1099" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1099" s="23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P1099" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1100" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C1100" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D1100" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E1100" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1100" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="G1100" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1100" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1100" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J1100" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1100" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1100" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1100" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1100" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1100" s="19" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="P1100" s="19" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1101" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C1101" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D1101" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1101" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F1101" s="21" t="n">
+        <v>106</v>
+      </c>
+      <c r="G1101" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1101" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1101" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1101" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1101" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1101" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1101" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1101" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1101" s="23" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="P1101" s="23" t="n">
+        <v>7.14</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1102" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C1102" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D1102" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1102" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F1102" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="G1102" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1102" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1102" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1102" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1102" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1102" s="19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P1102" s="19" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1103" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C1103" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D1103" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1103" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F1103" s="21" t="n">
+        <v>77</v>
+      </c>
+      <c r="G1103" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1103" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1103" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1103" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1103" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1103" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1103" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1103" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O1103" s="23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P1103" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1104" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C1104" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D1104" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1104" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1104" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1104" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1104" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1104" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1104" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1104" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1104" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1104" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1104" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1104" s="19" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="P1104" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1105" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C1105" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D1105" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1105" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1105" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="G1105" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1105" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1105" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1105" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1105" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O1105" s="23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P1105" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1106" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C1106" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D1106" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1106" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1106" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1106" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1106" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1106" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1106" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1106" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1107" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C1107" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D1107" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1107" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1107" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1107" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1107" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1107" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1107" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1107" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1108" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1108" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D1108" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1108" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1108" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1108" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1108" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1108" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1108" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1108" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1108" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1108" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1108" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1108" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1108" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1109" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C1109" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D1109" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1109" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1109" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1109" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1109" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1109" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1109" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1109" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1109" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1109" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1109" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1109" s="23" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="P1109" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1110" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C1110" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D1110" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1110" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1110" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1110" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1110" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1110" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1110" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1110" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1111" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1111" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D1111" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1111" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1111" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1111" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1111" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1111" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1111" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1111" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1112" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C1112" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D1112" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1112" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1112" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="G1112" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1112" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1112" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1112" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1112" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1112" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1112" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1112" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1112" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1112" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1113" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C1113" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D1113" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1113" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1113" s="21" t="n">
+        <v>122</v>
+      </c>
+      <c r="G1113" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1113" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1113" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1113" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1113" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1113" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1113" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1113" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O1113" s="23" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="P1113" s="23" t="n">
+        <v>38.46</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1114" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C1114" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D1114" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1114" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F1114" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1114" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1114" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1114" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1114" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1114" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1114" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1114" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1114" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O1114" s="19" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="P1114" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1115" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C1115" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D1115" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1115" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1115" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1115" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1115" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1115" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1115" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1115" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1115" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1115" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1115" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O1115" s="23" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="P1115" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1116" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C1116" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D1116" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1116" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1116" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="G1116" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1116" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1116" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1116" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1116" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1116" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1116" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1116" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1116" s="19" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="P1116" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1117" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C1117" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D1117" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1117" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1117" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1117" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1117" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1117" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1117" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1117" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1117" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1117" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1117" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1117" s="23" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="P1117" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1118" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C1118" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D1118" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1118" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1118" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1118" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1118" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1118" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1118" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1118" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1118" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1118" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1118" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1118" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1118" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1119" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C1119" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D1119" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1119" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1119" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1119" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1119" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1119" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1119" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1119" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1119" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1119" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1119" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1119" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1119" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1120" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C1120" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D1120" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1120" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1120" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G1120" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1120" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1120" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1120" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1120" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1120" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1120" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1120" s="29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O1120" s="19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P1120" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1121" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C1121" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D1121" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1121" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F1121" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="G1121" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1121" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1121" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1121" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1121" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O1121" s="23" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="P1121" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1122" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C1122" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D1122" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1122" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F1122" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="G1122" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1122" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1122" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1122" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1122" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1122" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1122" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1122" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O1122" s="19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P1122" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1123" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C1123" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D1123" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1123" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1123" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1123" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1123" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1123" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1123" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1123" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1123" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1123" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1123" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1123" s="23" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P1123" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1124" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C1124" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D1124" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1124" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1124" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1124" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1124" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1124" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1124" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1124" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1124" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1124" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1124" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1124" s="19" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="P1124" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1125" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C1125" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D1125" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1125" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F1125" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1125" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1125" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1125" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1125" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1125" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1125" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1125" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1125" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O1125" s="23" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="P1125" s="23" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4"/>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1700</v>
+        <v>1726</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1125"/>
+  <dimension ref="A1:P1178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -68363,6 +68363,3186 @@
         <v>26.67</v>
       </c>
     </row>
+    <row r="1126">
+      <c r="A1126" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1126" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ под нишу: один шаблон – три бизнеса</t>
+        </is>
+      </c>
+      <c r="C1126" s="8" t="inlineStr">
+        <is>
+          <t>6a05a22bbc6f8902a0667228</t>
+        </is>
+      </c>
+      <c r="D1126" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1126" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1126" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1126" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1126" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1126" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1127" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT для бизнеса: почему платная подписка не решает проблему сама по себе</t>
+        </is>
+      </c>
+      <c r="C1127" s="11" t="inlineStr">
+        <is>
+          <t>6a059b14a62f460406a8ba98</t>
+        </is>
+      </c>
+      <c r="D1127" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1127" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1127" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1127" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1127" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1127" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1127" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1127" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1127" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1127" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1127" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1127" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1127" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1128" s="8" t="inlineStr">
+        <is>
+          <t>3 признака, что вы используете ИИ неэффективно (и как это исправить)</t>
+        </is>
+      </c>
+      <c r="C1128" s="8" t="inlineStr">
+        <is>
+          <t>6a05933c4c0cb314940868ee</t>
+        </is>
+      </c>
+      <c r="D1128" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1128" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1128" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1128" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1128" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1128" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1128" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1128" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1128" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1128" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1128" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1128" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="P1128" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1129" s="11" t="inlineStr">
+        <is>
+          <t>Что такое цепочка агентов и зачем она нужна маркетологу</t>
+        </is>
+      </c>
+      <c r="C1129" s="11" t="inlineStr">
+        <is>
+          <t>6a046691a62f4604067b7c83</t>
+        </is>
+      </c>
+      <c r="D1129" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1129" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1129" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1129" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1129" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1129" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1129" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1129" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1129" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1129" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1129" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1129" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1129" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1130" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг в одиночку: 6 ИИ-агентов вместо отдела из пяти человек</t>
+        </is>
+      </c>
+      <c r="C1130" s="8" t="inlineStr">
+        <is>
+          <t>6a04635ea62f46040676a741</t>
+        </is>
+      </c>
+      <c r="D1130" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1130" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1130" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1130" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1130" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1130" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1130" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1130" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1130" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1130" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1130" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1130" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1130" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1131" s="11" t="inlineStr">
+        <is>
+          <t>ИИ снова написал «не то». Дело не в промпте</t>
+        </is>
+      </c>
+      <c r="C1131" s="11" t="inlineStr">
+        <is>
+          <t>6a045fb61b306979e41e249a</t>
+        </is>
+      </c>
+      <c r="D1131" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1131" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1131" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1131" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1131" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1131" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1131" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1131" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1132" s="8" t="inlineStr">
+        <is>
+          <t>Контент-план на месяц за 20 минут. Без воды и страданий над пустой табличкой</t>
+        </is>
+      </c>
+      <c r="C1132" s="8" t="inlineStr">
+        <is>
+          <t>6a045b2229363d25f247f1c2</t>
+        </is>
+      </c>
+      <c r="D1132" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1132" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1132" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1132" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1132" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1132" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1132" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1132" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1132" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1132" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1132" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1132" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1132" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1133" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент для анализа аудитории: почему он бьёт точнее любого опроса</t>
+        </is>
+      </c>
+      <c r="C1133" s="11" t="inlineStr">
+        <is>
+          <t>6a04552f109a6c68d8b08a43</t>
+        </is>
+      </c>
+      <c r="D1133" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1133" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1133" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1133" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1133" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1133" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1133" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1133" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1133" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1133" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1133" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1133" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1133" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1134" s="8" t="inlineStr">
+        <is>
+          <t>Как заставить нейросеть писать твоим голосом</t>
+        </is>
+      </c>
+      <c r="C1134" s="8" t="inlineStr">
+        <is>
+          <t>6a0319609e1e6a5143cf59f2</t>
+        </is>
+      </c>
+      <c r="D1134" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1134" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1134" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1134" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1134" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1134" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1134" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1134" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1134" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1134" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1134" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1134" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1134" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1135" s="11" t="inlineStr">
+        <is>
+          <t>Система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1135" s="11" t="inlineStr">
+        <is>
+          <t>6a0316e9f7cd3124ebb7e2e5</t>
+        </is>
+      </c>
+      <c r="D1135" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1135" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1135" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1135" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1135" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1135" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1135" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1135" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1135" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1135" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1135" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1135" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1135" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1136" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети</t>
+        </is>
+      </c>
+      <c r="C1136" s="8" t="inlineStr">
+        <is>
+          <t>6a03133bbb2ab60cfd65824b</t>
+        </is>
+      </c>
+      <c r="D1136" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1136" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1136" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1136" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1136" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1136" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1136" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1136" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1136" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1136" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1136" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1136" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1136" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1137" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C1137" s="11" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D1137" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1137" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1137" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1137" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1137" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1137" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1137" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1137" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1137" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1137" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1137" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1137" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1137" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1138" s="8" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1138" s="8" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D1138" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1138" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1138" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="G1138" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1138" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1138" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1138" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1138" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1138" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1138" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1138" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1138" s="19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P1138" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1139" s="11" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C1139" s="11" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D1139" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1139" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1139" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="G1139" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1139" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1139" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1139" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1139" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1139" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1139" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1139" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1139" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1139" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1140" s="8" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C1140" s="8" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D1140" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1140" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1140" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1140" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1140" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1140" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1140" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1140" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1140" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1140" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1140" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1140" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1140" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1141" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1141" s="11" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D1141" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1141" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1141" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1141" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1141" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1141" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1141" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1141" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1141" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1141" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1141" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1141" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1141" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1142" s="8" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C1142" s="8" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D1142" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1142" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1142" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1142" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1142" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1142" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1142" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1142" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1142" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1142" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1142" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1142" s="19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P1142" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1143" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C1143" s="11" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D1143" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1143" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1143" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1143" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1143" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1143" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1143" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1143" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1143" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1143" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1143" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1143" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1143" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1144" s="8" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C1144" s="8" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D1144" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1144" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1144" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1144" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1144" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1144" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1144" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1144" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1144" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1144" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1144" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1144" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P1144" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1145" s="11" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C1145" s="11" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D1145" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1145" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1145" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1145" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1145" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1145" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1145" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1145" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1145" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1145" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1145" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1145" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1145" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1146" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C1146" s="8" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D1146" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1146" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1146" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1146" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1146" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1146" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1146" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1146" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1146" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1146" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1146" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1146" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1146" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1147" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C1147" s="11" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D1147" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1147" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1147" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1147" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1147" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1147" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1147" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1147" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1147" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1147" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1147" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1147" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1147" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1148" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C1148" s="8" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D1148" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1148" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1148" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1148" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1148" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1148" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1148" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1148" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1148" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1148" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1148" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O1148" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1148" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1149" s="11" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C1149" s="11" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D1149" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1149" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F1149" s="21" t="n">
+        <v>132</v>
+      </c>
+      <c r="G1149" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1149" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1149" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1149" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1149" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1149" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1149" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1149" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1149" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1149" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1150" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1150" s="8" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D1150" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1150" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F1150" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1150" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1150" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1150" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1150" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1150" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1150" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1150" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1150" s="29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O1150" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1150" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1151" s="11" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C1151" s="11" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D1151" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1151" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F1151" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1151" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1151" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1151" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1151" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1151" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1151" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1151" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1151" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1151" s="23" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P1151" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1152" s="8" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C1152" s="8" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D1152" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1152" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1152" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1152" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1152" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1152" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1152" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1152" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1152" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1152" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1152" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1152" s="19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P1152" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1153" s="11" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C1153" s="11" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D1153" s="20" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E1153" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1153" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G1153" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1153" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1153" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="J1153" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1153" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1153" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1153" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1153" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1153" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P1153" s="23" t="n">
+        <v>63.64</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1154" s="8" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C1154" s="8" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D1154" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1154" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F1154" s="17" t="n">
+        <v>106</v>
+      </c>
+      <c r="G1154" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1154" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1154" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1154" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1154" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1154" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1154" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1154" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1154" s="19" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="P1154" s="19" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1155" s="11" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C1155" s="11" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D1155" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1155" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F1155" s="21" t="n">
+        <v>85</v>
+      </c>
+      <c r="G1155" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1155" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1155" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1155" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1155" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1155" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1155" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1155" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1155" s="23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P1155" s="23" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1156" s="8" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C1156" s="8" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D1156" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1156" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F1156" s="17" t="n">
+        <v>77</v>
+      </c>
+      <c r="G1156" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1156" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1156" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1156" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1156" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1156" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1156" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1156" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O1156" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P1156" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1157" s="11" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C1157" s="11" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D1157" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1157" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1157" s="21" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1157" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1157" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1157" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1157" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1157" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1157" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1157" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1157" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1157" s="23" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="P1157" s="23" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1158" s="8" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C1158" s="8" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D1158" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1158" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1158" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="G1158" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1158" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1158" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1158" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1158" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1158" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1158" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1158" s="29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O1158" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P1158" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1159" s="11" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C1159" s="11" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D1159" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1159" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1159" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1159" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1159" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1159" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1159" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1159" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1159" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1159" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1159" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1159" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1159" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1160" s="8" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C1160" s="8" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D1160" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1160" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1160" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1160" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1160" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1160" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1160" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1160" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1160" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1160" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1160" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1160" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1160" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1161" s="11" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1161" s="11" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D1161" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1161" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1161" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1161" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1161" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1161" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1161" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1161" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1161" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1161" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1161" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1161" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1161" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1162" s="8" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C1162" s="8" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D1162" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1162" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1162" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1162" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1162" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1162" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1162" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1162" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1162" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1162" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1162" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1162" s="19" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="P1162" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1163" s="11" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C1163" s="11" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D1163" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1163" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1163" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1163" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1163" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1163" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1163" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1163" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1163" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1163" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1163" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1163" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1163" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1164" s="8" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1164" s="8" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D1164" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1164" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1164" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1164" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1164" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1164" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1164" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1164" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1164" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1164" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1164" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1164" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1164" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1165" s="11" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C1165" s="11" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D1165" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1165" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1165" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G1165" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1165" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1165" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1165" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1165" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1165" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1165" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1165" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1165" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1165" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1166" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C1166" s="8" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D1166" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1166" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1166" s="17" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1166" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1166" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1166" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1166" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1166" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1166" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1166" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1166" s="29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O1166" s="19" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="P1166" s="19" t="n">
+        <v>38.46</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1167" s="11" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C1167" s="11" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D1167" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1167" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F1167" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1167" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1167" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1167" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1167" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1167" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1167" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1167" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1167" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O1167" s="23" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="P1167" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1168" s="8" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C1168" s="8" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D1168" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1168" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1168" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1168" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1168" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1168" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1168" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1168" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1168" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1168" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1168" s="29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O1168" s="19" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="P1168" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1169" s="11" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C1169" s="11" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D1169" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1169" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1169" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1169" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1169" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1169" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1169" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1169" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1169" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1169" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1169" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1169" s="23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P1169" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1170" s="8" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C1170" s="8" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D1170" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1170" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1170" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1170" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1170" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1170" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1170" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1170" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1170" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1170" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1170" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1170" s="19" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="P1170" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1171" s="11" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C1171" s="11" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D1171" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1171" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1171" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1171" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1171" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1171" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1171" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1171" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1171" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1171" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1171" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1171" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1171" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1172" s="8" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C1172" s="8" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D1172" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1172" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1172" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1172" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1172" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1172" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1172" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1172" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1172" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1172" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1172" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1172" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1172" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1173" s="11" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C1173" s="11" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D1173" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1173" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1173" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="G1173" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1173" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1173" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J1173" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1173" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1173" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1173" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1173" s="30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O1173" s="23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P1173" s="23" t="n">
+        <v>26.09</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1174" s="8" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C1174" s="8" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D1174" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1174" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F1174" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G1174" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1174" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1174" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1174" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1174" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1174" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1174" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1174" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O1174" s="19" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="P1174" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1175" s="11" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C1175" s="11" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D1175" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1175" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F1175" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G1175" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1175" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1175" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1175" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1175" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1175" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1175" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1175" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O1175" s="23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P1175" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1176" s="8" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C1176" s="8" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D1176" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1176" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1176" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1176" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1176" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1176" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1176" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1176" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1176" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1176" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1176" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1176" s="19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P1176" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1177" s="11" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C1177" s="11" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D1177" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1177" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1177" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1177" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1177" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1177" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1177" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1177" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1177" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1177" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1177" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1177" s="23" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="P1177" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1178" s="8" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C1178" s="8" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D1178" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1178" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F1178" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1178" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1178" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1178" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1178" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1178" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1178" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1178" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1178" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O1178" s="19" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="P1178" s="19" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -68375,7 +71555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -69466,6 +72646,34 @@
         <v>0</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C39" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="D39" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -69478,7 +72686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -69984,6 +73192,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="C39" s="33" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1178"/>
+  <dimension ref="A1:P1231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -71540,6 +71540,3186 @@
         <v>13.79</v>
       </c>
       <c r="P1178" s="19" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1179" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ под нишу: один шаблон – три бизнеса</t>
+        </is>
+      </c>
+      <c r="C1179" s="8" t="inlineStr">
+        <is>
+          <t>6a05a22bbc6f8902a0667228</t>
+        </is>
+      </c>
+      <c r="D1179" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1179" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1179" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1179" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1179" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1179" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1179" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1179" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1179" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1179" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1179" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1179" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1179" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1180" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT для бизнеса: почему платная подписка не решает проблему сама по себе</t>
+        </is>
+      </c>
+      <c r="C1180" s="11" t="inlineStr">
+        <is>
+          <t>6a059b14a62f460406a8ba98</t>
+        </is>
+      </c>
+      <c r="D1180" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1180" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1180" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1180" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1180" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1180" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1180" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1180" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1180" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1180" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1180" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1180" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1180" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1181" s="8" t="inlineStr">
+        <is>
+          <t>3 признака, что вы используете ИИ неэффективно (и как это исправить)</t>
+        </is>
+      </c>
+      <c r="C1181" s="8" t="inlineStr">
+        <is>
+          <t>6a05933c4c0cb314940868ee</t>
+        </is>
+      </c>
+      <c r="D1181" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1181" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1181" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1181" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1181" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1181" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1181" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1181" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1181" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1181" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1181" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1181" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="P1181" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1182" s="11" t="inlineStr">
+        <is>
+          <t>Что такое цепочка агентов и зачем она нужна маркетологу</t>
+        </is>
+      </c>
+      <c r="C1182" s="11" t="inlineStr">
+        <is>
+          <t>6a046691a62f4604067b7c83</t>
+        </is>
+      </c>
+      <c r="D1182" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1182" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1182" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1182" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1182" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1182" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1182" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1182" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1182" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1182" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1182" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1182" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1182" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1183" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг в одиночку: 6 ИИ-агентов вместо отдела из пяти человек</t>
+        </is>
+      </c>
+      <c r="C1183" s="8" t="inlineStr">
+        <is>
+          <t>6a04635ea62f46040676a741</t>
+        </is>
+      </c>
+      <c r="D1183" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1183" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1183" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1183" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1183" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1183" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1183" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1183" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1183" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1183" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1183" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1183" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1183" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1184" s="11" t="inlineStr">
+        <is>
+          <t>ИИ снова написал «не то». Дело не в промпте</t>
+        </is>
+      </c>
+      <c r="C1184" s="11" t="inlineStr">
+        <is>
+          <t>6a045fb61b306979e41e249a</t>
+        </is>
+      </c>
+      <c r="D1184" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1184" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1184" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1184" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1184" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1184" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1184" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1184" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1184" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1184" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1184" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1184" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1184" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1185" s="8" t="inlineStr">
+        <is>
+          <t>Контент-план на месяц за 20 минут. Без воды и страданий над пустой табличкой</t>
+        </is>
+      </c>
+      <c r="C1185" s="8" t="inlineStr">
+        <is>
+          <t>6a045b2229363d25f247f1c2</t>
+        </is>
+      </c>
+      <c r="D1185" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1185" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1185" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1185" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1185" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1185" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1185" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1185" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1185" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1185" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1185" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1185" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1185" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1186" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент для анализа аудитории: почему он бьёт точнее любого опроса</t>
+        </is>
+      </c>
+      <c r="C1186" s="11" t="inlineStr">
+        <is>
+          <t>6a04552f109a6c68d8b08a43</t>
+        </is>
+      </c>
+      <c r="D1186" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1186" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1186" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1186" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1186" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1186" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1186" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1186" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1186" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1186" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1186" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1186" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1186" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1187" s="8" t="inlineStr">
+        <is>
+          <t>Как заставить нейросеть писать твоим голосом</t>
+        </is>
+      </c>
+      <c r="C1187" s="8" t="inlineStr">
+        <is>
+          <t>6a0319609e1e6a5143cf59f2</t>
+        </is>
+      </c>
+      <c r="D1187" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1187" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1187" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1187" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1187" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1187" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1187" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1187" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1187" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1187" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1187" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1187" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1187" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1188" s="11" t="inlineStr">
+        <is>
+          <t>Система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1188" s="11" t="inlineStr">
+        <is>
+          <t>6a0316e9f7cd3124ebb7e2e5</t>
+        </is>
+      </c>
+      <c r="D1188" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1188" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1188" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1188" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1188" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1188" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1188" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1188" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1188" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1188" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1188" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1188" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1188" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1189" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети</t>
+        </is>
+      </c>
+      <c r="C1189" s="8" t="inlineStr">
+        <is>
+          <t>6a03133bbb2ab60cfd65824b</t>
+        </is>
+      </c>
+      <c r="D1189" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1189" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1189" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1189" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1189" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1189" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1189" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1189" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1189" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1189" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1189" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1189" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1189" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1190" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C1190" s="11" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D1190" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1190" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1190" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1190" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1190" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1190" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1190" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1190" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1190" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1190" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1190" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1190" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1190" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1191" s="8" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1191" s="8" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D1191" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1191" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1191" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="G1191" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1191" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1191" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1191" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1191" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1191" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1191" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1191" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1191" s="19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P1191" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1192" s="11" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C1192" s="11" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D1192" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1192" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1192" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="G1192" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1192" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1192" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1192" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1192" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1192" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1192" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1192" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1192" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1192" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1193" s="8" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C1193" s="8" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D1193" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1193" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1193" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1193" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1193" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1193" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1193" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1193" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1193" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1193" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1193" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1193" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1193" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1194" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1194" s="11" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D1194" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1194" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1194" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1194" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1194" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1194" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1194" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1194" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1194" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1194" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1194" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1194" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1194" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1195" s="8" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C1195" s="8" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D1195" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1195" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1195" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1195" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1195" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1195" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1195" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1195" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1195" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1195" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1195" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1195" s="19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P1195" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1196" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C1196" s="11" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D1196" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1196" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1196" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1196" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1196" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1196" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1196" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1196" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1196" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1196" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1196" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1196" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1196" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1197" s="8" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C1197" s="8" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D1197" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1197" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1197" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1197" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1197" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1197" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1197" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1197" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1197" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1197" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1197" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1197" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P1197" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1198" s="11" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C1198" s="11" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D1198" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1198" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1198" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1198" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1198" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1198" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1198" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1198" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1198" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1198" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1198" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1198" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1198" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1199" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C1199" s="8" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D1199" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1199" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1199" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1199" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1199" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1199" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1199" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1199" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1199" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1199" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1199" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1199" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1199" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1200" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C1200" s="11" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D1200" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1200" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1200" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1200" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1200" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1200" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1200" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1200" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1200" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1200" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1200" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1200" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1200" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1201" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C1201" s="8" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D1201" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1201" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1201" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1201" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1201" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1201" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1201" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1201" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1201" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1201" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1201" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O1201" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1201" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1202" s="11" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C1202" s="11" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D1202" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1202" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F1202" s="21" t="n">
+        <v>132</v>
+      </c>
+      <c r="G1202" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1202" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1202" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1202" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1202" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1202" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1202" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1202" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1202" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1202" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1203" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1203" s="8" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D1203" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1203" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F1203" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1203" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1203" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1203" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1203" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1203" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1203" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1203" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1203" s="29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O1203" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1203" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1204" s="11" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C1204" s="11" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D1204" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1204" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F1204" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1204" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1204" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1204" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1204" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1204" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1204" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1204" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1204" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1204" s="23" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P1204" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1205" s="8" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C1205" s="8" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D1205" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1205" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1205" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1205" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1205" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1205" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1205" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1205" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1205" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1205" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1205" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1205" s="19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P1205" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1206" s="11" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C1206" s="11" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D1206" s="20" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E1206" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1206" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G1206" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1206" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1206" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="J1206" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1206" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1206" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1206" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1206" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1206" s="23" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P1206" s="23" t="n">
+        <v>63.64</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1207" s="8" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C1207" s="8" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D1207" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1207" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F1207" s="17" t="n">
+        <v>106</v>
+      </c>
+      <c r="G1207" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1207" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1207" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1207" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1207" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1207" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1207" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1207" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1207" s="19" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="P1207" s="19" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1208" s="11" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C1208" s="11" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D1208" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1208" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F1208" s="21" t="n">
+        <v>85</v>
+      </c>
+      <c r="G1208" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1208" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1208" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1208" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1208" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1208" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1208" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1208" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1208" s="23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P1208" s="23" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1209" s="8" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C1209" s="8" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D1209" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1209" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F1209" s="17" t="n">
+        <v>77</v>
+      </c>
+      <c r="G1209" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1209" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1209" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1209" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1209" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1209" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1209" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1209" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O1209" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P1209" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1210" s="11" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C1210" s="11" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D1210" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1210" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1210" s="21" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1210" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1210" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1210" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1210" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1210" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1210" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1210" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1210" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1210" s="23" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="P1210" s="23" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1211" s="8" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C1211" s="8" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D1211" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1211" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1211" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="G1211" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1211" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1211" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1211" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1211" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1211" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1211" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1211" s="29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O1211" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P1211" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1212" s="11" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C1212" s="11" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D1212" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1212" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1212" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1212" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1212" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1212" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1212" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1212" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1212" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1212" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1212" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1212" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1212" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1213" s="8" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C1213" s="8" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D1213" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1213" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1213" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1213" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1213" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1213" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1213" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1213" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1213" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1213" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1213" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1213" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1213" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1214" s="11" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1214" s="11" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D1214" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1214" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1214" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1214" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1214" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1214" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1214" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1214" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1214" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1214" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1214" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1214" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1214" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1215" s="8" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C1215" s="8" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D1215" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1215" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1215" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1215" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1215" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1215" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1215" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1215" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1215" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1215" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1215" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1215" s="19" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="P1215" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1216" s="11" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C1216" s="11" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D1216" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1216" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1216" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1216" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1216" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1216" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1216" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1216" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1216" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1216" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1216" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1216" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1216" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1217" s="8" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1217" s="8" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D1217" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1217" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1217" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1217" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1217" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1217" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1217" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1217" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1217" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1217" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1217" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1217" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1217" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1218" s="11" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C1218" s="11" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D1218" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1218" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1218" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G1218" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1218" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1218" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1218" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1218" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1218" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1218" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1218" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1218" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1218" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1219" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C1219" s="8" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D1219" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1219" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1219" s="17" t="n">
+        <v>123</v>
+      </c>
+      <c r="G1219" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1219" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1219" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1219" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1219" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1219" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1219" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1219" s="29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O1219" s="19" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="P1219" s="19" t="n">
+        <v>38.46</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1220" s="11" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C1220" s="11" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D1220" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1220" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F1220" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1220" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1220" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1220" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1220" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1220" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1220" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1220" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1220" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O1220" s="23" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="P1220" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1221" s="8" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C1221" s="8" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D1221" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1221" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1221" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1221" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1221" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1221" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1221" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1221" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1221" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1221" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1221" s="29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O1221" s="19" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="P1221" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1222" s="11" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C1222" s="11" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D1222" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1222" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1222" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1222" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1222" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1222" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1222" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1222" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1222" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1222" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1222" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1222" s="23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P1222" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1223" s="8" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C1223" s="8" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D1223" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1223" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1223" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1223" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1223" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1223" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1223" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1223" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1223" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1223" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1223" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1223" s="19" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="P1223" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1224" s="11" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C1224" s="11" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D1224" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1224" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1224" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1224" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1224" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1224" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1224" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1224" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1224" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1224" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1224" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1224" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1224" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1225" s="8" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C1225" s="8" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D1225" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1225" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1225" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1225" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1225" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1225" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1225" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1225" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1225" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1225" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1225" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1225" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1225" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1226" s="11" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C1226" s="11" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D1226" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1226" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1226" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="G1226" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1226" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1226" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J1226" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1226" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1226" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1226" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1226" s="30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O1226" s="23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P1226" s="23" t="n">
+        <v>26.09</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1227" s="8" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C1227" s="8" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D1227" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1227" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F1227" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="G1227" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1227" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1227" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1227" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1227" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1227" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1227" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1227" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O1227" s="19" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="P1227" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1228" s="11" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C1228" s="11" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D1228" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1228" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F1228" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="G1228" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1228" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1228" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1228" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1228" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1228" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1228" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1228" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O1228" s="23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P1228" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1229" s="8" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C1229" s="8" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D1229" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1229" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1229" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1229" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1229" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1229" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1229" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1229" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1229" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1229" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1229" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1229" s="19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P1229" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1230" s="11" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C1230" s="11" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D1230" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1230" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1230" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1230" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1230" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1230" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1230" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1230" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1230" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1230" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1230" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1230" s="23" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="P1230" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1231" s="8" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C1231" s="8" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D1231" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1231" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F1231" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1231" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1231" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1231" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1231" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1231" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1231" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1231" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1231" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O1231" s="19" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="P1231" s="19" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4"/>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1726</v>
+        <v>1779</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1231"/>
+  <dimension ref="A1:P1286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -74720,6 +74720,3306 @@
         <v>13.79</v>
       </c>
       <c r="P1231" s="19" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1232" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агенты уже работают. Вот как маркетологи экономят 10–15 часов в неделю</t>
+        </is>
+      </c>
+      <c r="C1232" s="8" t="inlineStr">
+        <is>
+          <t>6a05b121208c506aa806e020</t>
+        </is>
+      </c>
+      <c r="D1232" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1232" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1232" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1232" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1232" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1232" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1232" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1232" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1232" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1232" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1232" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1232" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1232" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1233" s="11" t="inlineStr">
+        <is>
+          <t>Почему я перестал нанимать копирайтера на рутину</t>
+        </is>
+      </c>
+      <c r="C1233" s="11" t="inlineStr">
+        <is>
+          <t>6a05a9223dcba176c302be56</t>
+        </is>
+      </c>
+      <c r="D1233" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1233" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1233" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1233" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1233" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1233" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1233" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1233" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1233" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1233" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1233" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1233" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1233" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1234" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ под нишу: один шаблон – три бизнеса</t>
+        </is>
+      </c>
+      <c r="C1234" s="8" t="inlineStr">
+        <is>
+          <t>6a05a22bbc6f8902a0667228</t>
+        </is>
+      </c>
+      <c r="D1234" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1234" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1234" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1234" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1234" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1234" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1234" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1234" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1234" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1234" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1234" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1234" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1234" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1235" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT для бизнеса: почему платная подписка не решает проблему сама по себе</t>
+        </is>
+      </c>
+      <c r="C1235" s="11" t="inlineStr">
+        <is>
+          <t>6a059b14a62f460406a8ba98</t>
+        </is>
+      </c>
+      <c r="D1235" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1235" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1235" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1235" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1235" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1235" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1235" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1235" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1235" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1235" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1235" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1235" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1235" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1236" s="8" t="inlineStr">
+        <is>
+          <t>3 признака, что вы используете ИИ неэффективно (и как это исправить)</t>
+        </is>
+      </c>
+      <c r="C1236" s="8" t="inlineStr">
+        <is>
+          <t>6a05933c4c0cb314940868ee</t>
+        </is>
+      </c>
+      <c r="D1236" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1236" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1236" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1236" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1236" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1236" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1236" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1236" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1236" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1236" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1236" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1236" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="P1236" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1237" s="11" t="inlineStr">
+        <is>
+          <t>Что такое цепочка агентов и зачем она нужна маркетологу</t>
+        </is>
+      </c>
+      <c r="C1237" s="11" t="inlineStr">
+        <is>
+          <t>6a046691a62f4604067b7c83</t>
+        </is>
+      </c>
+      <c r="D1237" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1237" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1237" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1237" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1237" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1237" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1237" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1237" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1237" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1237" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1237" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1237" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1237" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1238" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг в одиночку: 6 ИИ-агентов вместо отдела из пяти человек</t>
+        </is>
+      </c>
+      <c r="C1238" s="8" t="inlineStr">
+        <is>
+          <t>6a04635ea62f46040676a741</t>
+        </is>
+      </c>
+      <c r="D1238" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1238" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1238" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1238" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1238" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1238" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1238" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1238" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1238" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1238" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1238" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1238" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1238" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1239" s="11" t="inlineStr">
+        <is>
+          <t>ИИ снова написал «не то». Дело не в промпте</t>
+        </is>
+      </c>
+      <c r="C1239" s="11" t="inlineStr">
+        <is>
+          <t>6a045fb61b306979e41e249a</t>
+        </is>
+      </c>
+      <c r="D1239" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1239" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1239" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1239" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1239" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1239" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1239" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1239" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1239" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1239" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1239" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1239" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1239" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1240" s="8" t="inlineStr">
+        <is>
+          <t>Контент-план на месяц за 20 минут. Без воды и страданий над пустой табличкой</t>
+        </is>
+      </c>
+      <c r="C1240" s="8" t="inlineStr">
+        <is>
+          <t>6a045b2229363d25f247f1c2</t>
+        </is>
+      </c>
+      <c r="D1240" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1240" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1240" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1240" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1240" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1240" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1240" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1240" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1240" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1240" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1240" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1240" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1240" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1241" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент для анализа аудитории: почему он бьёт точнее любого опроса</t>
+        </is>
+      </c>
+      <c r="C1241" s="11" t="inlineStr">
+        <is>
+          <t>6a04552f109a6c68d8b08a43</t>
+        </is>
+      </c>
+      <c r="D1241" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1241" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1241" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1241" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1241" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1241" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1241" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1241" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1241" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1241" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1241" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1241" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1241" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1242" s="8" t="inlineStr">
+        <is>
+          <t>Как заставить нейросеть писать твоим голосом</t>
+        </is>
+      </c>
+      <c r="C1242" s="8" t="inlineStr">
+        <is>
+          <t>6a0319609e1e6a5143cf59f2</t>
+        </is>
+      </c>
+      <c r="D1242" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1242" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1242" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1242" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1242" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1242" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1242" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1242" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1242" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1242" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1242" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1242" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1242" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1243" s="11" t="inlineStr">
+        <is>
+          <t>Система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1243" s="11" t="inlineStr">
+        <is>
+          <t>6a0316e9f7cd3124ebb7e2e5</t>
+        </is>
+      </c>
+      <c r="D1243" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1243" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1243" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1243" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1243" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1243" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1243" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1243" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1243" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1243" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1243" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1243" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1243" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1244" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети</t>
+        </is>
+      </c>
+      <c r="C1244" s="8" t="inlineStr">
+        <is>
+          <t>6a03133bbb2ab60cfd65824b</t>
+        </is>
+      </c>
+      <c r="D1244" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1244" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1244" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1244" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1244" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1244" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1244" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1244" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1244" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1244" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1244" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1244" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1244" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1245" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C1245" s="11" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D1245" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1245" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1245" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1245" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1245" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1245" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1245" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1245" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1245" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1245" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1245" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1245" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1245" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1246" s="8" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1246" s="8" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D1246" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1246" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1246" s="17" t="n">
+        <v>97</v>
+      </c>
+      <c r="G1246" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1246" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1246" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1246" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1246" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1246" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1246" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1246" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1246" s="19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="P1246" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1247" s="11" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C1247" s="11" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D1247" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1247" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1247" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="G1247" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1247" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1247" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1247" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1247" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1247" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1247" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1247" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1247" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1247" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1248" s="8" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C1248" s="8" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D1248" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1248" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1248" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1248" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1248" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1248" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1248" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1248" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1248" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1248" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1248" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1248" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1248" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1249" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1249" s="11" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D1249" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1249" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1249" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1249" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1249" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1249" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1249" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1249" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1249" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1249" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1249" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1249" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1249" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1250" s="8" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C1250" s="8" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D1250" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1250" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1250" s="17" t="n">
+        <v>83</v>
+      </c>
+      <c r="G1250" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1250" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1250" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1250" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1250" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1250" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1250" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1250" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1250" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P1250" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1251" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C1251" s="11" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D1251" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1251" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1251" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1251" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1251" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1251" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1251" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1251" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1251" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1251" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1251" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1251" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1251" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1252" s="8" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C1252" s="8" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D1252" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1252" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1252" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1252" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1252" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1252" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1252" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1252" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1252" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1252" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1252" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1252" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="P1252" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1253" s="11" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C1253" s="11" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D1253" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1253" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1253" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1253" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1253" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1253" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1253" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1253" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1253" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1253" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1253" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1253" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1253" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1254" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C1254" s="8" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D1254" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1254" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1254" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1254" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1254" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1254" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1254" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1254" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1254" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1254" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1254" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1254" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1254" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1255" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C1255" s="11" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D1255" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1255" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1255" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1255" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1255" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1255" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1255" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1255" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1255" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1255" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1255" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1255" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1255" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1256" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C1256" s="8" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D1256" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1256" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1256" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1256" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1256" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1256" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1256" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1256" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1256" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1256" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1256" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O1256" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1256" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1257" s="11" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C1257" s="11" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D1257" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1257" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F1257" s="21" t="n">
+        <v>132</v>
+      </c>
+      <c r="G1257" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1257" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1257" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1257" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1257" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1257" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1257" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1257" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1257" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1257" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1258" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1258" s="8" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D1258" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1258" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F1258" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1258" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1258" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1258" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1258" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1258" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1258" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1258" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1258" s="29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O1258" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1258" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1259" s="11" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C1259" s="11" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D1259" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1259" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F1259" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1259" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1259" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1259" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1259" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1259" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1259" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1259" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1259" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1259" s="23" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P1259" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1260" s="8" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C1260" s="8" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D1260" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1260" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1260" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1260" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1260" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1260" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1260" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1260" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1260" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1260" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1260" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1260" s="19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P1260" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1261" s="11" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C1261" s="11" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D1261" s="20" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E1261" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1261" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1261" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1261" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1261" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="J1261" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1261" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1261" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1261" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1261" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1261" s="23" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="P1261" s="23" t="n">
+        <v>63.64</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1262" s="8" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C1262" s="8" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D1262" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1262" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F1262" s="17" t="n">
+        <v>106</v>
+      </c>
+      <c r="G1262" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1262" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1262" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1262" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1262" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1262" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1262" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1262" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1262" s="19" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="P1262" s="19" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1263" s="11" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C1263" s="11" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D1263" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1263" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F1263" s="21" t="n">
+        <v>85</v>
+      </c>
+      <c r="G1263" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1263" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1263" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1263" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1263" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1263" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1263" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1263" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1263" s="23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P1263" s="23" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1264" s="8" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C1264" s="8" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D1264" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1264" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F1264" s="17" t="n">
+        <v>77</v>
+      </c>
+      <c r="G1264" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1264" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1264" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1264" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1264" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1264" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1264" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1264" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O1264" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P1264" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1265" s="11" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C1265" s="11" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D1265" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1265" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1265" s="21" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1265" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1265" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1265" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1265" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1265" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1265" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1265" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1265" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1265" s="23" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="P1265" s="23" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1266" s="8" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C1266" s="8" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D1266" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1266" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1266" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="G1266" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1266" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1266" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1266" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1266" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1266" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1266" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1266" s="29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O1266" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P1266" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1267" s="11" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C1267" s="11" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D1267" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1267" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1267" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1267" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1267" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1267" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1267" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1267" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1267" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1267" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1267" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1267" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1267" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1268" s="8" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C1268" s="8" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D1268" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1268" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1268" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1268" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1268" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1268" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1268" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1268" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1268" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1268" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1268" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1268" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1268" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1269" s="11" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1269" s="11" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D1269" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1269" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1269" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1269" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1269" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1269" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1269" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1269" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1269" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1269" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1269" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1269" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1269" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1270" s="8" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C1270" s="8" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D1270" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1270" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1270" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G1270" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1270" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1270" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1270" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1270" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1270" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1270" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1270" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1270" s="19" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="P1270" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1271" s="11" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C1271" s="11" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D1271" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1271" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1271" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1271" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1271" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1271" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1271" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1271" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1271" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1271" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1271" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1271" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1271" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1272" s="8" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1272" s="8" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D1272" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1272" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1272" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1272" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1272" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1272" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1272" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1272" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1272" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1272" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1272" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1272" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1272" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1273" s="11" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C1273" s="11" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D1273" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1273" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1273" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1273" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1273" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1273" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1273" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1273" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1273" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1273" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1273" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1273" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1273" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1274" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C1274" s="8" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D1274" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1274" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1274" s="17" t="n">
+        <v>124</v>
+      </c>
+      <c r="G1274" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1274" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1274" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1274" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1274" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1274" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1274" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1274" s="29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O1274" s="19" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="P1274" s="19" t="n">
+        <v>38.46</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1275" s="11" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C1275" s="11" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D1275" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1275" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F1275" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1275" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1275" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1275" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1275" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1275" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1275" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1275" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1275" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O1275" s="23" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="P1275" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1276" s="8" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C1276" s="8" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D1276" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1276" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1276" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1276" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1276" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1276" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1276" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1276" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1276" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1276" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1276" s="29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O1276" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P1276" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1277" s="11" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C1277" s="11" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D1277" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1277" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1277" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="G1277" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1277" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1277" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1277" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1277" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1277" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1277" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1277" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1277" s="23" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="P1277" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1278" s="8" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C1278" s="8" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D1278" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1278" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1278" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1278" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1278" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1278" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1278" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1278" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1278" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1278" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1278" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1278" s="19" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="P1278" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1279" s="11" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C1279" s="11" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D1279" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1279" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1279" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1279" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1279" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1279" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1279" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1279" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1279" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1279" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1279" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1279" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1279" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1280" s="8" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C1280" s="8" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D1280" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1280" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1280" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1280" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1280" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1280" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1280" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1280" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1280" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1281" s="11" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C1281" s="11" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D1281" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1281" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1281" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1281" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="H1281" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1281" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J1281" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1281" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1281" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1281" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1281" s="30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O1281" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P1281" s="23" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1282" s="8" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C1282" s="8" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D1282" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1282" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F1282" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1282" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1282" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1282" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1282" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1282" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1282" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1282" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1282" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O1282" s="19" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="P1282" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1283" s="11" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C1283" s="11" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D1283" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1283" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F1283" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1283" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1283" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1283" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1283" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1283" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1283" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1283" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1283" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O1283" s="23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P1283" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1284" s="8" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C1284" s="8" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D1284" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1284" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1284" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1284" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1284" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1284" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1284" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1284" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1284" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1284" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1284" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1284" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P1284" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1285" s="11" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C1285" s="11" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D1285" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1285" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1285" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1285" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1285" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1285" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1285" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1285" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1285" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1285" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1285" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1285" s="23" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="P1285" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1286" s="8" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C1286" s="8" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D1286" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1286" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F1286" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1286" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1286" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1286" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1286" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1286" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1286" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1286" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1286" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O1286" s="19" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="P1286" s="19" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1779</v>
+        <v>1814</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1286"/>
+  <dimension ref="A1:P1341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -78023,6 +78023,3306 @@
         <v>26.67</v>
       </c>
     </row>
+    <row r="1287">
+      <c r="A1287" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1287" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агенты уже работают. Вот как маркетологи экономят 10–15 часов в неделю</t>
+        </is>
+      </c>
+      <c r="C1287" s="8" t="inlineStr">
+        <is>
+          <t>6a05b121208c506aa806e020</t>
+        </is>
+      </c>
+      <c r="D1287" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1287" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1287" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1287" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1287" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1287" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1287" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1287" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1287" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1287" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1287" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1287" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1287" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1288" s="11" t="inlineStr">
+        <is>
+          <t>Почему я перестал нанимать копирайтера на рутину</t>
+        </is>
+      </c>
+      <c r="C1288" s="11" t="inlineStr">
+        <is>
+          <t>6a05a9223dcba176c302be56</t>
+        </is>
+      </c>
+      <c r="D1288" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1288" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1288" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1288" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1288" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1288" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1288" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1288" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1288" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1288" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1288" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1288" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1288" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1289" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ под нишу: один шаблон – три бизнеса</t>
+        </is>
+      </c>
+      <c r="C1289" s="8" t="inlineStr">
+        <is>
+          <t>6a05a22bbc6f8902a0667228</t>
+        </is>
+      </c>
+      <c r="D1289" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1289" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1289" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1289" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1289" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1289" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1289" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1289" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1289" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1289" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1289" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1289" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1289" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1290" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT для бизнеса: почему платная подписка не решает проблему сама по себе</t>
+        </is>
+      </c>
+      <c r="C1290" s="11" t="inlineStr">
+        <is>
+          <t>6a059b14a62f460406a8ba98</t>
+        </is>
+      </c>
+      <c r="D1290" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1290" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1290" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1290" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1290" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1290" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1290" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1290" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1290" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1290" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1290" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1290" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1290" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1291" s="8" t="inlineStr">
+        <is>
+          <t>3 признака, что вы используете ИИ неэффективно (и как это исправить)</t>
+        </is>
+      </c>
+      <c r="C1291" s="8" t="inlineStr">
+        <is>
+          <t>6a05933c4c0cb314940868ee</t>
+        </is>
+      </c>
+      <c r="D1291" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1291" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1291" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="G1291" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1291" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1291" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1291" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1291" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1291" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1291" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1291" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1291" s="19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P1291" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1292" s="11" t="inlineStr">
+        <is>
+          <t>Что такое цепочка агентов и зачем она нужна маркетологу</t>
+        </is>
+      </c>
+      <c r="C1292" s="11" t="inlineStr">
+        <is>
+          <t>6a046691a62f4604067b7c83</t>
+        </is>
+      </c>
+      <c r="D1292" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1292" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1292" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1292" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1292" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1292" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1292" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1292" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1292" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1292" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1292" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1292" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1292" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1293" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг в одиночку: 6 ИИ-агентов вместо отдела из пяти человек</t>
+        </is>
+      </c>
+      <c r="C1293" s="8" t="inlineStr">
+        <is>
+          <t>6a04635ea62f46040676a741</t>
+        </is>
+      </c>
+      <c r="D1293" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1293" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1293" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1293" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1293" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1293" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1293" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1293" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1293" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1293" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1293" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1293" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1293" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1294" s="11" t="inlineStr">
+        <is>
+          <t>ИИ снова написал «не то». Дело не в промпте</t>
+        </is>
+      </c>
+      <c r="C1294" s="11" t="inlineStr">
+        <is>
+          <t>6a045fb61b306979e41e249a</t>
+        </is>
+      </c>
+      <c r="D1294" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1294" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1294" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1294" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1294" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1294" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1294" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1294" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1294" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1294" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1294" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1294" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1294" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1295" s="8" t="inlineStr">
+        <is>
+          <t>Контент-план на месяц за 20 минут. Без воды и страданий над пустой табличкой</t>
+        </is>
+      </c>
+      <c r="C1295" s="8" t="inlineStr">
+        <is>
+          <t>6a045b2229363d25f247f1c2</t>
+        </is>
+      </c>
+      <c r="D1295" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1295" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1295" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1295" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1295" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1295" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1295" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1295" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1295" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1295" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1295" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1295" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1295" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1296" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент для анализа аудитории: почему он бьёт точнее любого опроса</t>
+        </is>
+      </c>
+      <c r="C1296" s="11" t="inlineStr">
+        <is>
+          <t>6a04552f109a6c68d8b08a43</t>
+        </is>
+      </c>
+      <c r="D1296" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1296" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1296" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1296" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1296" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1296" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1296" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1296" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1296" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1296" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1296" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1296" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1296" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1297" s="8" t="inlineStr">
+        <is>
+          <t>Как заставить нейросеть писать твоим голосом</t>
+        </is>
+      </c>
+      <c r="C1297" s="8" t="inlineStr">
+        <is>
+          <t>6a0319609e1e6a5143cf59f2</t>
+        </is>
+      </c>
+      <c r="D1297" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1297" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1297" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1297" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1297" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1297" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1297" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1297" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1297" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1297" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1297" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1297" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1297" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1298" s="11" t="inlineStr">
+        <is>
+          <t>Система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1298" s="11" t="inlineStr">
+        <is>
+          <t>6a0316e9f7cd3124ebb7e2e5</t>
+        </is>
+      </c>
+      <c r="D1298" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1298" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1298" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1298" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1298" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1298" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1298" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1298" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1298" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1298" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1298" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1298" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1298" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1299" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети</t>
+        </is>
+      </c>
+      <c r="C1299" s="8" t="inlineStr">
+        <is>
+          <t>6a03133bbb2ab60cfd65824b</t>
+        </is>
+      </c>
+      <c r="D1299" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1299" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1299" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1299" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1299" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1299" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1299" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1299" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1299" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1299" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1299" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1299" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1299" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1300" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C1300" s="11" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D1300" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1300" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1300" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1300" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1300" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1300" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1300" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1300" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1300" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1300" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1300" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1300" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1300" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1301" s="8" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1301" s="8" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D1301" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1301" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1301" s="17" t="n">
+        <v>99</v>
+      </c>
+      <c r="G1301" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1301" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1301" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1301" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1301" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1301" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1301" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1301" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1301" s="19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P1301" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1302" s="11" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C1302" s="11" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D1302" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1302" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1302" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1302" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1302" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1302" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1302" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1302" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1302" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1302" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1302" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1302" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1302" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1303" s="8" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C1303" s="8" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D1303" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1303" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1303" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1303" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1303" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1303" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1303" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1303" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1303" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1303" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1303" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1303" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1303" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1304" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1304" s="11" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D1304" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1304" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1304" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1304" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1304" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1304" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1304" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1304" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1304" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1304" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1304" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1304" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1304" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1305" s="8" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C1305" s="8" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D1305" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1305" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1305" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G1305" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1305" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1305" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1305" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1305" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1305" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1305" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1305" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1305" s="19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P1305" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1306" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C1306" s="11" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D1306" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1306" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1306" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1306" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1306" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1306" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1306" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1306" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1306" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1306" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1306" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1306" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1306" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1307" s="8" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C1307" s="8" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D1307" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1307" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1307" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1307" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1307" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1307" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1307" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1307" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1307" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1307" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1307" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1307" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="P1307" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1308" s="11" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C1308" s="11" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D1308" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1308" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1308" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1308" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1308" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1308" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1308" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1308" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1308" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1308" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1308" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1308" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1308" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1309" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C1309" s="8" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D1309" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1309" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1309" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1309" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1309" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1309" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1309" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1309" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1309" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1309" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1309" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1309" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1309" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1310" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C1310" s="11" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D1310" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1310" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1310" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1310" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1310" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1310" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1310" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1310" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1310" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1310" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1310" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1310" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1310" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1311" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C1311" s="8" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D1311" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1311" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1311" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1311" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1311" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1311" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1311" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1311" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1311" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1311" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1311" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O1311" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1311" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1312" s="11" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C1312" s="11" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D1312" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1312" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F1312" s="21" t="n">
+        <v>132</v>
+      </c>
+      <c r="G1312" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1312" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1312" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1312" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1312" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1312" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1312" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1312" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1312" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1312" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1313" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1313" s="8" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D1313" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1313" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F1313" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1313" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1313" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1313" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1313" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1313" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1313" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1313" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1313" s="29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O1313" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1313" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1314" s="11" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C1314" s="11" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D1314" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1314" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F1314" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1314" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1314" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1314" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1314" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1314" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1314" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1314" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1314" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1314" s="23" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P1314" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1315" s="8" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C1315" s="8" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D1315" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1315" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1315" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1315" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1315" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1315" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1315" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1315" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1315" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1315" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1315" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1315" s="19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P1315" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1316" s="11" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C1316" s="11" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D1316" s="20" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E1316" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1316" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1316" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1316" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1316" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="J1316" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1316" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1316" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1316" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1316" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1316" s="23" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="P1316" s="23" t="n">
+        <v>63.64</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1317" s="8" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C1317" s="8" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D1317" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1317" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F1317" s="17" t="n">
+        <v>106</v>
+      </c>
+      <c r="G1317" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1317" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1317" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1317" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1317" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1317" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1317" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1317" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1317" s="19" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="P1317" s="19" t="n">
+        <v>7.14</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1318" s="11" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C1318" s="11" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D1318" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1318" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F1318" s="21" t="n">
+        <v>85</v>
+      </c>
+      <c r="G1318" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1318" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1318" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1318" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1318" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1318" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1318" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1318" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1318" s="23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P1318" s="23" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1319" s="8" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C1319" s="8" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D1319" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1319" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F1319" s="17" t="n">
+        <v>77</v>
+      </c>
+      <c r="G1319" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1319" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1319" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1319" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1319" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1319" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1319" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1319" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O1319" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P1319" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1320" s="11" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C1320" s="11" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D1320" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1320" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1320" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1320" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1320" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1320" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1320" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1320" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1320" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1320" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1320" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1320" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="P1320" s="23" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1321" s="8" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C1321" s="8" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D1321" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1321" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1321" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="G1321" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1321" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1321" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1321" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1321" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1321" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1321" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1321" s="29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O1321" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P1321" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1322" s="11" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C1322" s="11" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D1322" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1322" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1322" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1322" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1322" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1322" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1322" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1322" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1322" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1322" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1322" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1322" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1322" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1323" s="8" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C1323" s="8" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D1323" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1323" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1323" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1323" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1323" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1323" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1323" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1323" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1323" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1323" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1323" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1323" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1323" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1324" s="11" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1324" s="11" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D1324" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1324" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1324" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1324" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1324" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1324" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1324" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1324" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1324" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1324" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1324" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1324" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1324" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1325" s="8" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C1325" s="8" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D1325" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1325" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1325" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G1325" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1325" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1325" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1325" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1325" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1325" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1325" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1325" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1325" s="19" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="P1325" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1326" s="11" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C1326" s="11" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D1326" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1326" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1326" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1326" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1326" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1326" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1326" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1326" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1326" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1326" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1326" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1326" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1326" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1327" s="8" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1327" s="8" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D1327" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1327" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1327" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1327" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1327" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1327" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1327" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1327" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1327" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1327" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1327" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1327" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1327" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1328" s="11" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C1328" s="11" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D1328" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1328" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1328" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1328" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1328" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1328" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1328" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1328" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1328" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1328" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1328" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1328" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1328" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1329" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C1329" s="8" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D1329" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1329" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1329" s="17" t="n">
+        <v>125</v>
+      </c>
+      <c r="G1329" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1329" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1329" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1329" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1329" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1329" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1329" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1329" s="29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O1329" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P1329" s="19" t="n">
+        <v>38.46</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1330" s="11" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C1330" s="11" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D1330" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1330" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F1330" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1330" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1330" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1330" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1330" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1330" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1330" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1330" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1330" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O1330" s="23" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="P1330" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1331" s="8" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C1331" s="8" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D1331" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1331" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1331" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1331" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1331" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1331" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1331" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1331" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1331" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1331" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1331" s="29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O1331" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P1331" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1332" s="11" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C1332" s="11" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D1332" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1332" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1332" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="G1332" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1332" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1332" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1332" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1332" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1332" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1332" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1332" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1332" s="23" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="P1332" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1333" s="8" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C1333" s="8" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D1333" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1333" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1333" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1333" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1333" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1333" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1333" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1333" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1333" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1333" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1333" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1333" s="19" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="P1333" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1334" s="11" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C1334" s="11" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D1334" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1334" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1334" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1334" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1334" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1334" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1334" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1334" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1334" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1334" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1334" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1334" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1334" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1335" s="8" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C1335" s="8" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D1335" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1335" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1335" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1335" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1335" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1335" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1335" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1335" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1335" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1335" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1335" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1335" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1335" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1336" s="11" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C1336" s="11" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D1336" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1336" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1336" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1336" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1336" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1336" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1336" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1336" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1336" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1336" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1336" s="30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O1336" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P1336" s="23" t="n">
+        <v>25.93</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1337" s="8" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C1337" s="8" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D1337" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1337" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F1337" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1337" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1337" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1337" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1337" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1337" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1337" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1337" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1337" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O1337" s="19" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="P1337" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1338" s="11" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C1338" s="11" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D1338" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1338" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F1338" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1338" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1338" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1338" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1338" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1338" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1338" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1338" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1338" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O1338" s="23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P1338" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1339" s="8" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C1339" s="8" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D1339" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1339" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1339" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1339" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1339" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1339" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1339" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1339" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1339" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1339" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1339" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1339" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P1339" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1340" s="11" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C1340" s="11" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D1340" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1340" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1340" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1340" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1340" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1340" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1340" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1340" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1340" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1340" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1340" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1340" s="23" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="P1340" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1341" s="8" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C1341" s="8" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D1341" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1341" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F1341" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1341" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1341" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1341" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1341" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1341" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1341" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1341" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1341" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O1341" s="19" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="P1341" s="19" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -78035,7 +81335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -79154,6 +82454,34 @@
         <v>0</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -79166,7 +82494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -79685,6 +83013,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="C40" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1341"/>
+  <dimension ref="A1:P1396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -81320,6 +81320,3306 @@
         <v>13.79</v>
       </c>
       <c r="P1341" s="19" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1342" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агенты уже работают. Вот как маркетологи экономят 10–15 часов в неделю</t>
+        </is>
+      </c>
+      <c r="C1342" s="8" t="inlineStr">
+        <is>
+          <t>6a05b121208c506aa806e020</t>
+        </is>
+      </c>
+      <c r="D1342" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1342" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1342" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1342" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1342" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1342" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1342" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1342" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1342" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1342" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1342" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1342" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1342" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1343" s="11" t="inlineStr">
+        <is>
+          <t>Почему я перестал нанимать копирайтера на рутину</t>
+        </is>
+      </c>
+      <c r="C1343" s="11" t="inlineStr">
+        <is>
+          <t>6a05a9223dcba176c302be56</t>
+        </is>
+      </c>
+      <c r="D1343" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1343" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1343" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1343" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1343" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1343" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1343" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1343" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1343" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1343" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1343" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1343" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1343" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1344" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ под нишу: один шаблон – три бизнеса</t>
+        </is>
+      </c>
+      <c r="C1344" s="8" t="inlineStr">
+        <is>
+          <t>6a05a22bbc6f8902a0667228</t>
+        </is>
+      </c>
+      <c r="D1344" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1344" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1344" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1344" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1344" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1344" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1344" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1344" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1344" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1344" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1344" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1344" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1344" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1345" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT для бизнеса: почему платная подписка не решает проблему сама по себе</t>
+        </is>
+      </c>
+      <c r="C1345" s="11" t="inlineStr">
+        <is>
+          <t>6a059b14a62f460406a8ba98</t>
+        </is>
+      </c>
+      <c r="D1345" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1345" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1345" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1345" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1345" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1345" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1345" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1345" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1345" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1345" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1345" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1345" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1345" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1346" s="8" t="inlineStr">
+        <is>
+          <t>3 признака, что вы используете ИИ неэффективно (и как это исправить)</t>
+        </is>
+      </c>
+      <c r="C1346" s="8" t="inlineStr">
+        <is>
+          <t>6a05933c4c0cb314940868ee</t>
+        </is>
+      </c>
+      <c r="D1346" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1346" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1346" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="G1346" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1346" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1346" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1346" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1346" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1346" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1346" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1346" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1346" s="19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P1346" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1347" s="11" t="inlineStr">
+        <is>
+          <t>Что такое цепочка агентов и зачем она нужна маркетологу</t>
+        </is>
+      </c>
+      <c r="C1347" s="11" t="inlineStr">
+        <is>
+          <t>6a046691a62f4604067b7c83</t>
+        </is>
+      </c>
+      <c r="D1347" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1347" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1347" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1347" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1347" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1347" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1347" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1347" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1347" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1347" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1347" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1347" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1347" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1348" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг в одиночку: 6 ИИ-агентов вместо отдела из пяти человек</t>
+        </is>
+      </c>
+      <c r="C1348" s="8" t="inlineStr">
+        <is>
+          <t>6a04635ea62f46040676a741</t>
+        </is>
+      </c>
+      <c r="D1348" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1348" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1348" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1348" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1348" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1348" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1348" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1348" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1348" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1348" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1348" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1348" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1348" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1349" s="11" t="inlineStr">
+        <is>
+          <t>ИИ снова написал «не то». Дело не в промпте</t>
+        </is>
+      </c>
+      <c r="C1349" s="11" t="inlineStr">
+        <is>
+          <t>6a045fb61b306979e41e249a</t>
+        </is>
+      </c>
+      <c r="D1349" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1349" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1349" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1349" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1349" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1349" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1349" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1349" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1349" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1349" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1349" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1349" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1349" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1350" s="8" t="inlineStr">
+        <is>
+          <t>Контент-план на месяц за 20 минут. Без воды и страданий над пустой табличкой</t>
+        </is>
+      </c>
+      <c r="C1350" s="8" t="inlineStr">
+        <is>
+          <t>6a045b2229363d25f247f1c2</t>
+        </is>
+      </c>
+      <c r="D1350" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1350" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1350" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1350" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1350" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1350" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1350" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1350" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1350" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1350" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1350" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1350" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1350" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1351" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент для анализа аудитории: почему он бьёт точнее любого опроса</t>
+        </is>
+      </c>
+      <c r="C1351" s="11" t="inlineStr">
+        <is>
+          <t>6a04552f109a6c68d8b08a43</t>
+        </is>
+      </c>
+      <c r="D1351" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1351" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1351" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1351" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1351" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1351" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1351" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1351" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1351" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1351" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1351" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1351" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1351" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1352" s="8" t="inlineStr">
+        <is>
+          <t>Как заставить нейросеть писать твоим голосом</t>
+        </is>
+      </c>
+      <c r="C1352" s="8" t="inlineStr">
+        <is>
+          <t>6a0319609e1e6a5143cf59f2</t>
+        </is>
+      </c>
+      <c r="D1352" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1352" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1352" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1352" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1352" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1352" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1352" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1352" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1352" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1352" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1352" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1352" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1352" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1353" s="11" t="inlineStr">
+        <is>
+          <t>Система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1353" s="11" t="inlineStr">
+        <is>
+          <t>6a0316e9f7cd3124ebb7e2e5</t>
+        </is>
+      </c>
+      <c r="D1353" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1353" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1353" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1353" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1353" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1353" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1353" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1353" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1353" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1353" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1353" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1353" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1353" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1354" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети</t>
+        </is>
+      </c>
+      <c r="C1354" s="8" t="inlineStr">
+        <is>
+          <t>6a03133bbb2ab60cfd65824b</t>
+        </is>
+      </c>
+      <c r="D1354" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1354" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1354" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1354" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1354" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1354" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1354" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1354" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1354" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1354" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1354" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1354" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1354" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1355" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C1355" s="11" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D1355" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1355" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1355" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1355" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1355" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1355" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1355" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1355" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1355" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1355" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1355" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1355" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1355" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1356" s="8" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1356" s="8" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D1356" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1356" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1356" s="17" t="n">
+        <v>99</v>
+      </c>
+      <c r="G1356" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1356" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1356" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1356" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1356" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1356" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1356" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1356" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1356" s="19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P1356" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1357" s="11" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C1357" s="11" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D1357" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1357" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1357" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1357" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1357" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1357" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1357" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1357" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1357" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1357" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1357" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1357" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1357" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1358" s="8" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C1358" s="8" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D1358" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1358" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1358" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1358" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1358" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1358" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1358" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1358" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1358" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1358" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1358" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1358" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1358" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1359" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1359" s="11" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D1359" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1359" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1359" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1359" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1359" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1359" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1359" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1359" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1359" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1359" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1359" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1359" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1359" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1360" s="8" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C1360" s="8" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D1360" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1360" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1360" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G1360" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1360" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1360" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1360" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1360" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1360" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1360" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1360" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1360" s="19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P1360" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1361" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C1361" s="11" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D1361" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1361" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1361" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1361" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1361" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1361" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1361" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1361" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1361" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1361" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1361" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1361" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1361" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1362" s="8" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C1362" s="8" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D1362" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1362" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1362" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1362" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1362" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1362" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1362" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1362" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1362" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1362" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1362" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1362" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="P1362" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1363" s="11" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C1363" s="11" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D1363" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1363" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1363" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1363" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1363" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1363" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1363" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1363" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1363" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1363" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1363" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1363" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1363" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1364" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C1364" s="8" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D1364" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1364" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1364" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1364" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1364" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1364" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1364" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1364" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1364" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1364" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1364" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1364" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1364" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1365" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C1365" s="11" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D1365" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1365" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1365" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1365" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1365" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1365" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1365" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1365" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1365" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1365" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1365" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1365" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1365" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1366" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C1366" s="8" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D1366" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1366" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1366" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1366" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1366" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1366" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1366" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1366" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1366" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1366" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1366" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O1366" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1366" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1367" s="11" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C1367" s="11" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D1367" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1367" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F1367" s="21" t="n">
+        <v>132</v>
+      </c>
+      <c r="G1367" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1367" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1367" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1367" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1367" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1367" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1367" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1367" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1367" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1367" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1368" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1368" s="8" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D1368" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1368" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F1368" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1368" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1368" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1368" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1368" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1368" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1368" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1368" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1368" s="29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O1368" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1368" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1369" s="11" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C1369" s="11" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D1369" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1369" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F1369" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1369" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1369" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1369" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1369" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1369" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1369" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1369" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1369" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1369" s="23" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P1369" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1370" s="8" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C1370" s="8" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D1370" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1370" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1370" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1370" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1370" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1370" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1370" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1370" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1370" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1370" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1370" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1370" s="19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P1370" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1371" s="11" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C1371" s="11" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D1371" s="20" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E1371" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1371" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1371" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="H1371" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1371" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="J1371" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1371" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1371" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1371" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1371" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1371" s="23" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="P1371" s="23" t="n">
+        <v>63.64</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1372" s="8" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C1372" s="8" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D1372" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1372" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F1372" s="17" t="n">
+        <v>106</v>
+      </c>
+      <c r="G1372" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1372" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1372" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1372" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1372" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1372" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1372" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1372" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1372" s="19" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="P1372" s="19" t="n">
+        <v>7.14</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1373" s="11" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C1373" s="11" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D1373" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1373" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F1373" s="21" t="n">
+        <v>85</v>
+      </c>
+      <c r="G1373" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1373" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1373" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1373" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1373" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1373" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1373" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1373" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1373" s="23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P1373" s="23" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1374" s="8" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C1374" s="8" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D1374" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1374" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F1374" s="17" t="n">
+        <v>77</v>
+      </c>
+      <c r="G1374" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1374" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1374" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1374" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1374" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1374" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1374" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1374" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O1374" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P1374" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1375" s="11" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C1375" s="11" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D1375" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1375" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1375" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1375" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1375" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1375" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1375" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1375" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1375" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1375" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1375" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1375" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="P1375" s="23" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1376" s="8" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C1376" s="8" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D1376" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1376" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1376" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="G1376" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1376" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1376" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1376" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1376" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1376" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1376" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1376" s="29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O1376" s="19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P1376" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1377" s="11" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C1377" s="11" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D1377" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1377" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1377" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1377" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1377" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1377" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1377" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1377" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1377" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1377" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1377" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1377" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1377" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1378" s="8" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C1378" s="8" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D1378" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1378" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1378" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1378" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1378" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1378" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1378" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1378" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1378" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1378" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1378" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1378" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1378" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1379" s="11" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1379" s="11" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D1379" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1379" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1379" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1379" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1379" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1379" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1379" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1379" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1379" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1379" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1379" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1379" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1379" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1380" s="8" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C1380" s="8" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D1380" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1380" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1380" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G1380" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1380" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1380" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1380" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1380" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1380" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1380" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1380" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1380" s="19" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="P1380" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1381" s="11" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C1381" s="11" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D1381" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1381" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1381" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1381" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1381" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1381" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1381" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1381" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1381" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1381" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1381" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1381" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1381" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1382" s="8" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1382" s="8" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D1382" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1382" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1382" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1382" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1382" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1382" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1382" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1382" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1382" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1382" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1382" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1382" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1382" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1383" s="11" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C1383" s="11" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D1383" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1383" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1383" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1383" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1383" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1383" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1383" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1383" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1383" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1383" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1383" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1383" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1383" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1384" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C1384" s="8" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D1384" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1384" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1384" s="17" t="n">
+        <v>125</v>
+      </c>
+      <c r="G1384" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1384" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1384" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1384" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1384" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1384" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1384" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1384" s="29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O1384" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P1384" s="19" t="n">
+        <v>38.46</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1385" s="11" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C1385" s="11" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D1385" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1385" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F1385" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1385" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1385" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1385" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1385" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1385" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1385" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1385" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1385" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O1385" s="23" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="P1385" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1386" s="8" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C1386" s="8" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D1386" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1386" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1386" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1386" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1386" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1386" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1386" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1386" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1386" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1386" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1386" s="29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O1386" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P1386" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1387" s="11" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C1387" s="11" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D1387" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1387" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1387" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="G1387" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1387" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1387" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1387" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1387" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1387" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1387" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1387" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1387" s="23" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="P1387" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1388" s="8" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C1388" s="8" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D1388" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1388" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1388" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1388" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1388" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1388" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1388" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1388" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1388" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1388" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1388" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1388" s="19" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="P1388" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1389" s="11" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C1389" s="11" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D1389" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1389" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1389" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1389" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1389" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1389" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1389" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1389" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1389" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1389" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1389" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1389" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1389" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1390" s="8" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C1390" s="8" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D1390" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1390" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1390" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1390" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1390" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1390" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1390" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1390" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1390" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1390" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1390" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1390" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1390" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1391" s="11" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C1391" s="11" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D1391" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1391" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1391" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1391" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1391" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1391" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1391" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1391" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1391" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1391" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1391" s="30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O1391" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P1391" s="23" t="n">
+        <v>25.93</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1392" s="8" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C1392" s="8" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D1392" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1392" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F1392" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1392" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1392" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1392" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1392" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1392" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1392" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1392" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1392" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O1392" s="19" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="P1392" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1393" s="11" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C1393" s="11" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D1393" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1393" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F1393" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1393" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1393" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1393" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1393" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1393" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1393" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1393" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1393" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O1393" s="23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P1393" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1394" s="8" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C1394" s="8" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D1394" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1394" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1394" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1394" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1394" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1394" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1394" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1394" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1394" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1394" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1394" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1394" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P1394" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1395" s="11" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C1395" s="11" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D1395" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1395" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1395" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1395" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1395" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1395" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1395" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1395" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1395" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1395" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1395" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1395" s="23" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="P1395" s="23" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1396" s="8" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C1396" s="8" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D1396" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1396" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F1396" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1396" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1396" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1396" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1396" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1396" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1396" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1396" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1396" s="29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O1396" s="19" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="P1396" s="19" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4"/>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1814</v>
+        <v>1820</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1396"/>
+  <dimension ref="A1:P1456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -84620,6 +84620,3606 @@
         <v>13.79</v>
       </c>
       <c r="P1396" s="19" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1397" s="8" t="inlineStr">
+        <is>
+          <t>Почему контент без стратегии – это деньги на ветер</t>
+        </is>
+      </c>
+      <c r="C1397" s="8" t="inlineStr">
+        <is>
+          <t>6a0707b10343a536dffdea82</t>
+        </is>
+      </c>
+      <c r="D1397" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1397" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F1397" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1397" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1397" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1397" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1397" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1397" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1397" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1397" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1397" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1397" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1397" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1398" s="11" t="inlineStr">
+        <is>
+          <t>7 задач маркетолога, которые ИИ уже делает лучше человека</t>
+        </is>
+      </c>
+      <c r="C1398" s="11" t="inlineStr">
+        <is>
+          <t>6a0704b87a176c57a895a90d</t>
+        </is>
+      </c>
+      <c r="D1398" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1398" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F1398" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1398" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1398" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1398" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1398" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1398" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1398" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1398" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1398" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1398" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1398" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1399" s="8" t="inlineStr">
+        <is>
+          <t>Позиционирование бренда за один сеанс с ИИ: реально ли это</t>
+        </is>
+      </c>
+      <c r="C1399" s="8" t="inlineStr">
+        <is>
+          <t>6a06ff7a208c506aa85cf677</t>
+        </is>
+      </c>
+      <c r="D1399" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1399" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F1399" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1399" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1399" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1399" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1399" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1399" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1399" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1399" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1399" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1399" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1399" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1400" s="11" t="inlineStr">
+        <is>
+          <t>Как ИИ помогает понять, чего на самом деле хочет ваша аудитория</t>
+        </is>
+      </c>
+      <c r="C1400" s="11" t="inlineStr">
+        <is>
+          <t>6a06f641ff82e6477e894d91</t>
+        </is>
+      </c>
+      <c r="D1400" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1400" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F1400" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1400" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1400" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1400" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1400" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1400" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1400" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1400" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1400" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1400" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1400" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1401" s="8" t="inlineStr">
+        <is>
+          <t>Что такое ИИ-ассистент – объясняю на пальцах, без технического жаргона</t>
+        </is>
+      </c>
+      <c r="C1401" s="8" t="inlineStr">
+        <is>
+          <t>6a06ef26fdfa1c0b69d61fa5</t>
+        </is>
+      </c>
+      <c r="D1401" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1401" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F1401" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1401" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1401" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1401" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1401" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1401" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1401" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1401" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1401" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1401" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1401" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1402" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агенты уже работают. Вот как маркетологи экономят 10–15 часов в неделю</t>
+        </is>
+      </c>
+      <c r="C1402" s="11" t="inlineStr">
+        <is>
+          <t>6a05b121208c506aa806e020</t>
+        </is>
+      </c>
+      <c r="D1402" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1402" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1402" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1402" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1402" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1402" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1402" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1402" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1402" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1402" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1402" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1402" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1402" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1403" s="8" t="inlineStr">
+        <is>
+          <t>Почему я перестал нанимать копирайтера на рутину</t>
+        </is>
+      </c>
+      <c r="C1403" s="8" t="inlineStr">
+        <is>
+          <t>6a05a9223dcba176c302be56</t>
+        </is>
+      </c>
+      <c r="D1403" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1403" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1403" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1403" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1403" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1403" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1403" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1403" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1403" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1403" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1403" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1403" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1403" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1404" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ под нишу: один шаблон – три бизнеса</t>
+        </is>
+      </c>
+      <c r="C1404" s="11" t="inlineStr">
+        <is>
+          <t>6a05a22bbc6f8902a0667228</t>
+        </is>
+      </c>
+      <c r="D1404" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1404" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1404" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1404" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1404" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1404" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1404" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1404" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1404" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1404" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1404" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1404" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1404" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1405" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT для бизнеса: почему платная подписка не решает проблему сама по себе</t>
+        </is>
+      </c>
+      <c r="C1405" s="8" t="inlineStr">
+        <is>
+          <t>6a059b14a62f460406a8ba98</t>
+        </is>
+      </c>
+      <c r="D1405" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1405" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1405" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1405" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1405" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1405" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1405" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1405" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1405" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1405" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1405" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1405" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1405" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1406" s="11" t="inlineStr">
+        <is>
+          <t>3 признака, что вы используете ИИ неэффективно (и как это исправить)</t>
+        </is>
+      </c>
+      <c r="C1406" s="11" t="inlineStr">
+        <is>
+          <t>6a05933c4c0cb314940868ee</t>
+        </is>
+      </c>
+      <c r="D1406" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1406" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1406" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="G1406" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1406" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1406" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1406" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1406" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1406" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1406" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1406" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1406" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P1406" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1407" s="8" t="inlineStr">
+        <is>
+          <t>Что такое цепочка агентов и зачем она нужна маркетологу</t>
+        </is>
+      </c>
+      <c r="C1407" s="8" t="inlineStr">
+        <is>
+          <t>6a046691a62f4604067b7c83</t>
+        </is>
+      </c>
+      <c r="D1407" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1407" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1407" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1407" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1407" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1407" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1407" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1407" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1407" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1407" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1407" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1407" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1407" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1408" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинг в одиночку: 6 ИИ-агентов вместо отдела из пяти человек</t>
+        </is>
+      </c>
+      <c r="C1408" s="11" t="inlineStr">
+        <is>
+          <t>6a04635ea62f46040676a741</t>
+        </is>
+      </c>
+      <c r="D1408" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1408" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1408" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1408" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1408" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1408" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1408" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1408" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1408" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1408" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1408" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1408" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1408" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1409" s="8" t="inlineStr">
+        <is>
+          <t>ИИ снова написал «не то». Дело не в промпте</t>
+        </is>
+      </c>
+      <c r="C1409" s="8" t="inlineStr">
+        <is>
+          <t>6a045fb61b306979e41e249a</t>
+        </is>
+      </c>
+      <c r="D1409" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1409" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1409" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1409" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1409" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1409" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1409" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1409" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1409" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1409" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1409" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1409" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1409" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1410" s="11" t="inlineStr">
+        <is>
+          <t>Контент-план на месяц за 20 минут. Без воды и страданий над пустой табличкой</t>
+        </is>
+      </c>
+      <c r="C1410" s="11" t="inlineStr">
+        <is>
+          <t>6a045b2229363d25f247f1c2</t>
+        </is>
+      </c>
+      <c r="D1410" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1410" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1410" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1410" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1410" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1410" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1410" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1410" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1410" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1410" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1410" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1410" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1410" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1411" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агент для анализа аудитории: почему он бьёт точнее любого опроса</t>
+        </is>
+      </c>
+      <c r="C1411" s="8" t="inlineStr">
+        <is>
+          <t>6a04552f109a6c68d8b08a43</t>
+        </is>
+      </c>
+      <c r="D1411" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1411" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1411" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1411" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1411" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1411" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1411" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1411" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1411" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1411" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1411" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1411" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1411" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1412" s="11" t="inlineStr">
+        <is>
+          <t>Как заставить нейросеть писать твоим голосом</t>
+        </is>
+      </c>
+      <c r="C1412" s="11" t="inlineStr">
+        <is>
+          <t>6a0319609e1e6a5143cf59f2</t>
+        </is>
+      </c>
+      <c r="D1412" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1412" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1412" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1412" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1412" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1412" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1412" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1412" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1412" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1412" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1412" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1412" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1412" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1413" s="8" t="inlineStr">
+        <is>
+          <t>Система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1413" s="8" t="inlineStr">
+        <is>
+          <t>6a0316e9f7cd3124ebb7e2e5</t>
+        </is>
+      </c>
+      <c r="D1413" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1413" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1413" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1413" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1413" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1413" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1413" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1413" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1413" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1413" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1413" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1413" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1413" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1414" s="11" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети</t>
+        </is>
+      </c>
+      <c r="C1414" s="11" t="inlineStr">
+        <is>
+          <t>6a03133bbb2ab60cfd65824b</t>
+        </is>
+      </c>
+      <c r="D1414" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1414" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1414" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1414" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1414" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1414" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1414" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1414" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1414" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1414" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1414" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1414" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1414" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1415" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C1415" s="8" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D1415" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1415" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1415" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1415" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1415" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1415" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1415" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1415" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1415" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1415" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1415" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1415" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1415" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1416" s="11" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1416" s="11" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D1416" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1416" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1416" s="21" t="n">
+        <v>99</v>
+      </c>
+      <c r="G1416" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1416" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1416" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1416" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1416" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1416" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1416" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1416" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1416" s="23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P1416" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1417" s="8" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C1417" s="8" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D1417" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1417" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1417" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1417" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1417" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1417" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1417" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1417" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1417" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1417" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1417" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1417" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1417" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1418" s="11" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C1418" s="11" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D1418" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1418" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1418" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1418" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1418" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1418" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1418" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1418" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1418" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1418" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1418" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1418" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1418" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1419" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1419" s="8" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D1419" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1419" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1419" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1419" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1419" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1419" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1419" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1419" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1419" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1419" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1419" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1419" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1419" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1420" s="11" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C1420" s="11" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D1420" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1420" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1420" s="21" t="n">
+        <v>84</v>
+      </c>
+      <c r="G1420" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1420" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1420" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1420" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1420" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1420" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1420" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1420" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1420" s="23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P1420" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1421" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C1421" s="8" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D1421" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1421" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1421" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1421" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1421" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1421" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1421" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1421" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1421" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1421" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1421" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1421" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1421" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1422" s="11" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C1422" s="11" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D1422" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1422" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1422" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1422" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1422" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1422" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1422" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1422" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1422" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1422" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1422" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1422" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="P1422" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1423" s="8" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C1423" s="8" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D1423" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1423" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1423" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1423" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1423" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1423" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1423" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1423" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1423" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1423" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1423" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1423" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1423" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1424" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C1424" s="11" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D1424" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1424" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1424" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1424" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1424" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1424" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1424" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1424" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1424" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1424" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1424" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1424" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1424" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1425" s="8" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C1425" s="8" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D1425" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1425" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1425" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1425" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1425" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1425" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1425" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1425" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1425" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1425" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1425" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1425" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1425" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1426" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C1426" s="11" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D1426" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1426" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1426" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1426" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1426" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1426" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1426" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1426" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1426" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1426" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1426" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O1426" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1426" s="23" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1427" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C1427" s="8" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D1427" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1427" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F1427" s="17" t="n">
+        <v>132</v>
+      </c>
+      <c r="G1427" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1427" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1427" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1427" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1427" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1427" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1427" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1427" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1427" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1427" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1428" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1428" s="11" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D1428" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1428" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F1428" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1428" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1428" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1428" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1428" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1428" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1428" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1428" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1428" s="30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O1428" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1428" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1429" s="8" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C1429" s="8" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D1429" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1429" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F1429" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1429" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1429" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1429" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1429" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1429" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1429" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1429" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1429" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1429" s="19" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P1429" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1430" s="11" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C1430" s="11" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D1430" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1430" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1430" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1430" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1430" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1430" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1430" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1430" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1430" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1430" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1430" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1430" s="23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P1430" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1431" s="8" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C1431" s="8" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D1431" s="16" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E1431" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1431" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1431" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1431" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1431" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="J1431" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1431" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1431" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1431" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1431" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1431" s="19" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="P1431" s="19" t="n">
+        <v>63.64</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1432" s="11" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C1432" s="11" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D1432" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1432" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F1432" s="21" t="n">
+        <v>106</v>
+      </c>
+      <c r="G1432" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1432" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1432" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1432" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1432" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1432" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1432" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1432" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1432" s="23" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="P1432" s="23" t="n">
+        <v>7.14</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1433" s="8" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C1433" s="8" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D1433" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1433" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F1433" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="G1433" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1433" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1433" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1433" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1433" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1433" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1433" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1433" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1433" s="19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P1433" s="19" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1434" s="11" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C1434" s="11" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D1434" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1434" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F1434" s="21" t="n">
+        <v>77</v>
+      </c>
+      <c r="G1434" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1434" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1434" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1434" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1434" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1434" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1434" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1434" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O1434" s="23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P1434" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1435" s="8" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C1435" s="8" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D1435" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1435" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1435" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1435" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1435" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1435" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1435" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1435" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1435" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1435" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1435" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1435" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="P1435" s="19" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1436" s="11" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C1436" s="11" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D1436" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1436" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1436" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="G1436" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1436" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1436" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1436" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1436" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1436" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1436" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1436" s="30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O1436" s="23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P1436" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1437" s="8" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C1437" s="8" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D1437" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1437" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1437" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1437" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1437" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1437" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1437" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1437" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1437" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1437" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1437" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1437" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1437" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1438" s="11" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C1438" s="11" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D1438" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1438" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1438" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1438" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1438" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1438" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1438" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1438" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1438" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1438" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1438" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1438" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1438" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1439" s="8" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1439" s="8" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D1439" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1439" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1439" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1439" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1439" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1439" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1439" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1439" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1439" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1439" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1439" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1439" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1439" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1440" s="11" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C1440" s="11" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D1440" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1440" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1440" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G1440" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1440" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1440" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1440" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1440" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1440" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1440" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1440" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1440" s="23" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="P1440" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1441" s="8" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C1441" s="8" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D1441" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1441" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1441" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1441" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1441" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1441" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1441" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1441" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1441" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1441" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1441" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1441" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1441" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1442" s="11" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1442" s="11" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D1442" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1442" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1442" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1442" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1442" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1442" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1442" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1442" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1442" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1442" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1442" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1442" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1442" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1443" s="8" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C1443" s="8" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D1443" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1443" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1443" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1443" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1443" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1443" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1443" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1443" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1443" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1443" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1443" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1443" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1443" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1444" s="11" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C1444" s="11" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D1444" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1444" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1444" s="21" t="n">
+        <v>125</v>
+      </c>
+      <c r="G1444" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1444" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1444" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1444" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1444" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1444" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1444" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1444" s="30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O1444" s="23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P1444" s="23" t="n">
+        <v>38.46</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1445" s="8" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C1445" s="8" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D1445" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1445" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F1445" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1445" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1445" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1445" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1445" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1445" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1445" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1445" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1445" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O1445" s="19" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="P1445" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1446" s="11" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C1446" s="11" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D1446" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1446" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1446" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1446" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1446" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1446" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1446" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1446" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1446" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1446" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1446" s="30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O1446" s="23" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P1446" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1447" s="8" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C1447" s="8" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D1447" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1447" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1447" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="G1447" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1447" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1447" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1447" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1447" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1447" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1447" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1447" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1447" s="19" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="P1447" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1448" s="11" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C1448" s="11" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D1448" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1448" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1448" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1448" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1448" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1448" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1448" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1448" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1448" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1448" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1448" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1448" s="23" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="P1448" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1449" s="8" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C1449" s="8" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D1449" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1449" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1449" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1449" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1449" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1449" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1449" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1449" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1449" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1449" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1449" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1449" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1449" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1450" s="11" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C1450" s="11" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D1450" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1450" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1450" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1450" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1450" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1450" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1450" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1450" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1450" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1450" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1450" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1450" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1450" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1451" s="8" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C1451" s="8" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D1451" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1451" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1451" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1451" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1451" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1451" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1451" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1451" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1451" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1451" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1451" s="29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O1451" s="19" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P1451" s="19" t="n">
+        <v>25.93</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1452" s="11" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C1452" s="11" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D1452" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1452" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F1452" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1452" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1452" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1452" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1452" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1452" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1452" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1452" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1452" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O1452" s="23" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="P1452" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1453" s="8" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C1453" s="8" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D1453" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1453" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F1453" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1453" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1453" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1453" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1453" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1453" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1453" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1453" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1453" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O1453" s="19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P1453" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1454" s="11" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C1454" s="11" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D1454" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1454" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1454" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1454" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1454" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1454" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1454" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1454" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1454" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1454" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1454" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1454" s="23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P1454" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1455" s="8" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C1455" s="8" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </is>
+      </c>
+      <c r="D1455" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1455" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1455" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1455" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1455" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1455" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1455" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1455" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1455" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1455" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1455" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1455" s="19" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="P1455" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1456" s="11" t="inlineStr">
+        <is>
+          <t>Экосистема СОЗИДАЙ: обучение, агенты и услуги, которые экономят ваш маркетинг</t>
+        </is>
+      </c>
+      <c r="C1456" s="11" t="inlineStr">
+        <is>
+          <t>69d4b5f4fdd043526e0f2cbb</t>
+        </is>
+      </c>
+      <c r="D1456" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1456" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F1456" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1456" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1456" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1456" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1456" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1456" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L1456" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1456" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1456" s="30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O1456" s="23" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="P1456" s="23" t="n">
         <v>26.67</v>
       </c>
     </row>

--- a/dzen_analytics.xlsx
+++ b/dzen_analytics.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4"/>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>1820</v>
+        <v>1842</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1456"/>
+  <dimension ref="A1:P1517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -88223,6 +88223,3666 @@
         <v>26.67</v>
       </c>
     </row>
+    <row r="1457">
+      <c r="A1457" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1457" s="8" t="inlineStr">
+        <is>
+          <t>Perplexity для маркетинга: 6 агентов, которые заменят тебе платный аналитический отдел</t>
+        </is>
+      </c>
+      <c r="C1457" s="8" t="inlineStr">
+        <is>
+          <t>6a070ab06d579f57157b3d33</t>
+        </is>
+      </c>
+      <c r="D1457" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1457" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="F1457" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G1457" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1457" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1457" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1457" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1457" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1457" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1457" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1457" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1457" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1457" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1458" s="11" t="inlineStr">
+        <is>
+          <t>Почему контент без стратегии – это деньги на ветер</t>
+        </is>
+      </c>
+      <c r="C1458" s="11" t="inlineStr">
+        <is>
+          <t>6a0707b10343a536dffdea82</t>
+        </is>
+      </c>
+      <c r="D1458" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1458" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F1458" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1458" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1458" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1458" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1458" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1458" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1458" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1458" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1458" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1458" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1458" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1459" s="8" t="inlineStr">
+        <is>
+          <t>7 задач маркетолога, которые ИИ уже делает лучше человека</t>
+        </is>
+      </c>
+      <c r="C1459" s="8" t="inlineStr">
+        <is>
+          <t>6a0704b87a176c57a895a90d</t>
+        </is>
+      </c>
+      <c r="D1459" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1459" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F1459" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1459" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1459" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1459" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1459" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1459" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1459" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1459" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1459" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1459" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1459" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1460" s="11" t="inlineStr">
+        <is>
+          <t>Позиционирование бренда за один сеанс с ИИ: реально ли это</t>
+        </is>
+      </c>
+      <c r="C1460" s="11" t="inlineStr">
+        <is>
+          <t>6a06ff7a208c506aa85cf677</t>
+        </is>
+      </c>
+      <c r="D1460" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1460" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F1460" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1460" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1460" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1460" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1460" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1460" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1460" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1460" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1460" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1460" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1460" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1461" s="8" t="inlineStr">
+        <is>
+          <t>Как ИИ помогает понять, чего на самом деле хочет ваша аудитория</t>
+        </is>
+      </c>
+      <c r="C1461" s="8" t="inlineStr">
+        <is>
+          <t>6a06f641ff82e6477e894d91</t>
+        </is>
+      </c>
+      <c r="D1461" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1461" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F1461" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1461" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1461" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1461" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1461" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1461" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1461" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1461" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1461" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1461" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1461" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1462" s="11" t="inlineStr">
+        <is>
+          <t>Что такое ИИ-ассистент – объясняю на пальцах, без технического жаргона</t>
+        </is>
+      </c>
+      <c r="C1462" s="11" t="inlineStr">
+        <is>
+          <t>6a06ef26fdfa1c0b69d61fa5</t>
+        </is>
+      </c>
+      <c r="D1462" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1462" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F1462" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1462" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1462" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1462" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1462" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1462" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1462" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1462" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1462" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1462" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1462" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1463" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агенты уже работают. Вот как маркетологи экономят 10–15 часов в неделю</t>
+        </is>
+      </c>
+      <c r="C1463" s="8" t="inlineStr">
+        <is>
+          <t>6a05b121208c506aa806e020</t>
+        </is>
+      </c>
+      <c r="D1463" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1463" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1463" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1463" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1463" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1463" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1463" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1463" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1463" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1463" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1463" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1463" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1463" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1464" s="11" t="inlineStr">
+        <is>
+          <t>Почему я перестал нанимать копирайтера на рутину</t>
+        </is>
+      </c>
+      <c r="C1464" s="11" t="inlineStr">
+        <is>
+          <t>6a05a9223dcba176c302be56</t>
+        </is>
+      </c>
+      <c r="D1464" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1464" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1464" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1464" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1464" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1464" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1464" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1464" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1464" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1464" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1464" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1464" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1464" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1465" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ под нишу: один шаблон – три бизнеса</t>
+        </is>
+      </c>
+      <c r="C1465" s="8" t="inlineStr">
+        <is>
+          <t>6a05a22bbc6f8902a0667228</t>
+        </is>
+      </c>
+      <c r="D1465" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1465" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1465" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1465" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1465" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1465" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1465" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1465" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1465" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1465" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1465" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1465" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1465" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1466" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT для бизнеса: почему платная подписка не решает проблему сама по себе</t>
+        </is>
+      </c>
+      <c r="C1466" s="11" t="inlineStr">
+        <is>
+          <t>6a059b14a62f460406a8ba98</t>
+        </is>
+      </c>
+      <c r="D1466" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1466" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1466" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1466" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1466" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1466" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1466" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1466" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1466" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1466" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1466" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1466" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1466" s="23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1467" s="8" t="inlineStr">
+        <is>
+          <t>3 признака, что вы используете ИИ неэффективно (и как это исправить)</t>
+        </is>
+      </c>
+      <c r="C1467" s="8" t="inlineStr">
+        <is>
+          <t>6a05933c4c0cb314940868ee</t>
+        </is>
+      </c>
+      <c r="D1467" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1467" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F1467" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="G1467" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1467" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1467" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1467" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1467" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1467" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1467" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1467" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1467" s="19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P1467" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1468" s="11" t="inlineStr">
+        <is>
+          <t>Что такое цепочка агентов и зачем она нужна маркетологу</t>
+        </is>
+      </c>
+      <c r="C1468" s="11" t="inlineStr">
+        <is>
+          <t>6a046691a62f4604067b7c83</t>
+        </is>
+      </c>
+      <c r="D1468" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1468" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1468" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1468" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1468" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1468" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1468" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1468" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1468" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1468" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1468" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1468" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1468" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1469" s="8" t="inlineStr">
+        <is>
+          <t>Маркетинг в одиночку: 6 ИИ-агентов вместо отдела из пяти человек</t>
+        </is>
+      </c>
+      <c r="C1469" s="8" t="inlineStr">
+        <is>
+          <t>6a04635ea62f46040676a741</t>
+        </is>
+      </c>
+      <c r="D1469" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1469" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1469" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1469" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1469" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1469" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1469" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1469" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1469" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1469" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1469" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1469" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1469" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1470" s="11" t="inlineStr">
+        <is>
+          <t>ИИ снова написал «не то». Дело не в промпте</t>
+        </is>
+      </c>
+      <c r="C1470" s="11" t="inlineStr">
+        <is>
+          <t>6a045fb61b306979e41e249a</t>
+        </is>
+      </c>
+      <c r="D1470" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1470" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1470" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1470" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1470" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1470" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1470" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1470" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1470" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1470" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1470" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1470" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1470" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1471" s="8" t="inlineStr">
+        <is>
+          <t>Контент-план на месяц за 20 минут. Без воды и страданий над пустой табличкой</t>
+        </is>
+      </c>
+      <c r="C1471" s="8" t="inlineStr">
+        <is>
+          <t>6a045b2229363d25f247f1c2</t>
+        </is>
+      </c>
+      <c r="D1471" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1471" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1471" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1471" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1471" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1471" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1471" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1471" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1471" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1471" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1471" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1471" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1471" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1472" s="11" t="inlineStr">
+        <is>
+          <t>ИИ-агент для анализа аудитории: почему он бьёт точнее любого опроса</t>
+        </is>
+      </c>
+      <c r="C1472" s="11" t="inlineStr">
+        <is>
+          <t>6a04552f109a6c68d8b08a43</t>
+        </is>
+      </c>
+      <c r="D1472" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1472" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="F1472" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1472" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1472" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1472" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1472" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1472" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1472" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1472" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1472" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1472" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1472" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1473" s="8" t="inlineStr">
+        <is>
+          <t>Как заставить нейросеть писать твоим голосом</t>
+        </is>
+      </c>
+      <c r="C1473" s="8" t="inlineStr">
+        <is>
+          <t>6a0319609e1e6a5143cf59f2</t>
+        </is>
+      </c>
+      <c r="D1473" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1473" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1473" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1473" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1473" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1473" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1473" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1473" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1473" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1473" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1473" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1473" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1473" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1474" s="11" t="inlineStr">
+        <is>
+          <t>Система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1474" s="11" t="inlineStr">
+        <is>
+          <t>6a0316e9f7cd3124ebb7e2e5</t>
+        </is>
+      </c>
+      <c r="D1474" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1474" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1474" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1474" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1474" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1474" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1474" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1474" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1474" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1474" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1474" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1474" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1474" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1475" s="8" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети</t>
+        </is>
+      </c>
+      <c r="C1475" s="8" t="inlineStr">
+        <is>
+          <t>6a03133bbb2ab60cfd65824b</t>
+        </is>
+      </c>
+      <c r="D1475" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1475" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F1475" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1475" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1475" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1475" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1475" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1475" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1475" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1475" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1475" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1475" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1475" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1476" s="11" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов за вечер. Зачем платить 54 тысячи, если можно не платить</t>
+        </is>
+      </c>
+      <c r="C1476" s="11" t="inlineStr">
+        <is>
+          <t>69fdb79102c39929c4eb52f6</t>
+        </is>
+      </c>
+      <c r="D1476" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1476" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1476" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1476" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1476" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1476" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1476" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1476" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1476" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1476" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1476" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1476" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1476" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1477" s="8" t="inlineStr">
+        <is>
+          <t>Как малый бизнес может работать с ИИ как крупная компания: система из 6 агентов, которая закрывает отдел маркетинга</t>
+        </is>
+      </c>
+      <c r="C1477" s="8" t="inlineStr">
+        <is>
+          <t>69fdb21556684d60c17b5a38</t>
+        </is>
+      </c>
+      <c r="D1477" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1477" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1477" s="17" t="n">
+        <v>101</v>
+      </c>
+      <c r="G1477" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1477" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1477" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1477" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1477" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1477" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1477" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1477" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1477" s="19" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P1477" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1478" s="11" t="inlineStr">
+        <is>
+          <t>5 вопросов, на которые бизнес должен ответить до того, как открыть чат с нейросетью</t>
+        </is>
+      </c>
+      <c r="C1478" s="11" t="inlineStr">
+        <is>
+          <t>69fdafce4004402c50ca4986</t>
+        </is>
+      </c>
+      <c r="D1478" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1478" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1478" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1478" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1478" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1478" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1478" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1478" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1478" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1478" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1478" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1478" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1478" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1479" s="8" t="inlineStr">
+        <is>
+          <t>Что произойдёт с твоим контентом, если добавить в цепочку агента-копирайтера</t>
+        </is>
+      </c>
+      <c r="C1479" s="8" t="inlineStr">
+        <is>
+          <t>69fdab55bfc6ca73e626fb34</t>
+        </is>
+      </c>
+      <c r="D1479" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1479" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1479" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1479" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1479" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1479" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1479" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1479" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1479" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1479" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1479" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1479" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1479" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1480" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинг за 0 ₽: 6 ИИ-агентов на бесплатных ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1480" s="11" t="inlineStr">
+        <is>
+          <t>69fda7a3c82a8d14f28b9254</t>
+        </is>
+      </c>
+      <c r="D1480" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1480" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1480" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1480" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1480" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1480" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1480" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1480" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1480" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1480" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1480" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1480" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1480" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1481" s="8" t="inlineStr">
+        <is>
+          <t>Tone of voice для ИИ: как заставить нейросеть писать твоим голосом, а не «средним голосом интернета»</t>
+        </is>
+      </c>
+      <c r="C1481" s="8" t="inlineStr">
+        <is>
+          <t>69fda61ce57b1778c5d05f99</t>
+        </is>
+      </c>
+      <c r="D1481" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1481" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1481" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G1481" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1481" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1481" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1481" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1481" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1481" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1481" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1481" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1481" s="19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P1481" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1482" s="11" t="inlineStr">
+        <is>
+          <t>Маркетинговый паспорт бизнеса: один документ, который превращает любой ИИ в нормального копирайтера</t>
+        </is>
+      </c>
+      <c r="C1482" s="11" t="inlineStr">
+        <is>
+          <t>69fd994956684d60c15742a5</t>
+        </is>
+      </c>
+      <c r="D1482" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1482" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1482" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1482" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1482" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1482" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1482" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1482" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1482" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1482" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1482" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1482" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1482" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1483" s="8" t="inlineStr">
+        <is>
+          <t>Perplexity как маркетинговый инструмент: 6 нестандартных применений, до которых никто не доходит</t>
+        </is>
+      </c>
+      <c r="C1483" s="8" t="inlineStr">
+        <is>
+          <t>69fd940056684d60c14fb228</t>
+        </is>
+      </c>
+      <c r="D1483" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1483" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1483" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1483" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1483" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1483" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1483" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1483" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1483" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1483" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1483" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1483" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="P1483" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1484" s="11" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов за 15 минут: как ИИ-агент делает то, на что ты тратишь 5 часов</t>
+        </is>
+      </c>
+      <c r="C1484" s="11" t="inlineStr">
+        <is>
+          <t>69fd8c8d65f57a6647e5e5f8</t>
+        </is>
+      </c>
+      <c r="D1484" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1484" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1484" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1484" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1484" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1484" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1484" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1484" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1484" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1484" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1484" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1484" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1484" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1485" s="8" t="inlineStr">
+        <is>
+          <t>ИИ-агент против фрилансера: кому я теперь отдаю маркетинг – и где до сих пор плачу людям</t>
+        </is>
+      </c>
+      <c r="C1485" s="8" t="inlineStr">
+        <is>
+          <t>69fd86ca517e3a7edb33bff8</t>
+        </is>
+      </c>
+      <c r="D1485" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1485" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F1485" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1485" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1485" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1485" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1485" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1485" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1485" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1485" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1485" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1485" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1485" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1486" s="11" t="inlineStr">
+        <is>
+          <t>ChatGPT vs Perplexity: 6 маркетинговых агентов, которые закроют 80% рутины</t>
+        </is>
+      </c>
+      <c r="C1486" s="11" t="inlineStr">
+        <is>
+          <t>69fc282f9414e9308a2cfd59</t>
+        </is>
+      </c>
+      <c r="D1486" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1486" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1486" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1486" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1486" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1486" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1486" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1486" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1486" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1486" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1486" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1486" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1486" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1487" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-маркетолога за 1 день: пошаговая схема из 6 агентов</t>
+        </is>
+      </c>
+      <c r="C1487" s="8" t="inlineStr">
+        <is>
+          <t>69fb351049f7d667707db2bb</t>
+        </is>
+      </c>
+      <c r="D1487" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1487" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F1487" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1487" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1487" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1487" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1487" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1487" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1487" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1487" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1487" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O1487" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1487" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1488" s="11" t="inlineStr">
+        <is>
+          <t>Бизнес-бриф для нейросети: 34 вопроса, после которых ChatGPT начинает работать именно на ваш бизнес</t>
+        </is>
+      </c>
+      <c r="C1488" s="11" t="inlineStr">
+        <is>
+          <t>69fb21600060d97e813f2808</t>
+        </is>
+      </c>
+      <c r="D1488" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1488" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F1488" s="21" t="n">
+        <v>132</v>
+      </c>
+      <c r="G1488" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1488" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1488" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1488" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1488" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1488" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1488" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1488" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1488" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1488" s="23" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1489" s="8" t="inlineStr">
+        <is>
+          <t>6 ИИ-агентов вместо отдела маркетинга: как собрать их бесплатно в ChatGPT и Perplexity</t>
+        </is>
+      </c>
+      <c r="C1489" s="8" t="inlineStr">
+        <is>
+          <t>69f9c672db22e333c4a6de0c</t>
+        </is>
+      </c>
+      <c r="D1489" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1489" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F1489" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1489" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1489" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1489" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1489" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1489" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1489" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1489" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1489" s="29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O1489" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1489" s="19" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1490" s="11" t="inlineStr">
+        <is>
+          <t>90% маркетологов используют ИИ неправильно. Я 3 года смотрю, как они повторяют одну и ту же ошибку</t>
+        </is>
+      </c>
+      <c r="C1490" s="11" t="inlineStr">
+        <is>
+          <t>69f8962e1172e554b92d3bbe</t>
+        </is>
+      </c>
+      <c r="D1490" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1490" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F1490" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1490" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1490" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1490" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1490" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1490" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1490" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1490" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1490" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1490" s="23" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P1490" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1491" s="8" t="inlineStr">
+        <is>
+          <t>Почему нейросеть не знает ваш бизнес — и что с этим делать</t>
+        </is>
+      </c>
+      <c r="C1491" s="8" t="inlineStr">
+        <is>
+          <t>69f3479e44c9f40182de3d68</t>
+        </is>
+      </c>
+      <c r="D1491" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1491" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1491" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1491" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1491" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1491" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1491" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1491" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1491" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1491" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1491" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1491" s="19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P1491" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1492" s="11" t="inlineStr">
+        <is>
+          <t>Бесплатный курс «6 готовых ИИ-агентов»</t>
+        </is>
+      </c>
+      <c r="C1492" s="11" t="inlineStr">
+        <is>
+          <t>69f32f876c96204aceb32dbb</t>
+        </is>
+      </c>
+      <c r="D1492" s="20" t="inlineStr">
+        <is>
+          <t>Пост/Гифка</t>
+        </is>
+      </c>
+      <c r="E1492" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F1492" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1492" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1492" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1492" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="J1492" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1492" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1492" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1492" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1492" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1492" s="23" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="P1492" s="23" t="n">
+        <v>63.64</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1493" s="8" t="inlineStr">
+        <is>
+          <t>От анализа конкурентов к контент-плану за 3 часа: пошаговая схема</t>
+        </is>
+      </c>
+      <c r="C1493" s="8" t="inlineStr">
+        <is>
+          <t>69e5e294720368291496c7b3</t>
+        </is>
+      </c>
+      <c r="D1493" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1493" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="F1493" s="17" t="n">
+        <v>106</v>
+      </c>
+      <c r="G1493" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1493" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1493" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1493" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1493" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1493" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1493" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1493" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1493" s="19" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="P1493" s="19" t="n">
+        <v>7.14</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1494" s="11" t="inlineStr">
+        <is>
+          <t>Как проанализировать ЦА за 2 дня вместо 2 недель: схема с ИИ</t>
+        </is>
+      </c>
+      <c r="C1494" s="11" t="inlineStr">
+        <is>
+          <t>69e21c9ca049d744bba66183</t>
+        </is>
+      </c>
+      <c r="D1494" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1494" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="F1494" s="21" t="n">
+        <v>85</v>
+      </c>
+      <c r="G1494" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1494" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1494" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1494" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1494" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1494" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1494" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1494" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1494" s="23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P1494" s="23" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1495" s="8" t="inlineStr">
+        <is>
+          <t>Чек-лист хорошего промпта: 10 признаков, которые отличают рабочий запрос от слабого</t>
+        </is>
+      </c>
+      <c r="C1495" s="8" t="inlineStr">
+        <is>
+          <t>69e211ed0588e06d11b0fdba</t>
+        </is>
+      </c>
+      <c r="D1495" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1495" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F1495" s="17" t="n">
+        <v>77</v>
+      </c>
+      <c r="G1495" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1495" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1495" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1495" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1495" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1495" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1495" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1495" s="29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O1495" s="19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P1495" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1496" s="11" t="inlineStr">
+        <is>
+          <t>11 промптов для маркетингового анализа: ЦА, конкуренты, позиционирование, контент</t>
+        </is>
+      </c>
+      <c r="C1496" s="11" t="inlineStr">
+        <is>
+          <t>69e1c258285d501373a07ff0</t>
+        </is>
+      </c>
+      <c r="D1496" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1496" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1496" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1496" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1496" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1496" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1496" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1496" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1496" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1496" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1496" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1496" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="P1496" s="23" t="n">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1497" s="8" t="inlineStr">
+        <is>
+          <t>Как создать агента-копирайтера в Perplexity: пошаговая инструкция от промпта до результата</t>
+        </is>
+      </c>
+      <c r="C1497" s="8" t="inlineStr">
+        <is>
+          <t>69e0bd4902509c6e387f2681</t>
+        </is>
+      </c>
+      <c r="D1497" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1497" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1497" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1497" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1497" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1497" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1497" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1497" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1497" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1497" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1497" s="29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O1497" s="19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P1497" s="19" t="n">
+        <v>27.27</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1498" s="11" t="inlineStr">
+        <is>
+          <t>Как маркетологи теряют время на ИИ: 7 неочевидных ловушек</t>
+        </is>
+      </c>
+      <c r="C1498" s="11" t="inlineStr">
+        <is>
+          <t>69e09e17c067675e6332d38e</t>
+        </is>
+      </c>
+      <c r="D1498" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1498" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F1498" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1498" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1498" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1498" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1498" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1498" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1498" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1498" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1498" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1498" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1498" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1499" s="8" t="inlineStr">
+        <is>
+          <t>Файл описания бизнеса: почему без него ИИ работает вхолостую</t>
+        </is>
+      </c>
+      <c r="C1499" s="8" t="inlineStr">
+        <is>
+          <t>69e06e968600a54f99db5da7</t>
+        </is>
+      </c>
+      <c r="D1499" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1499" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1499" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1499" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1499" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1499" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1499" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1499" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1499" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1499" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1499" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1499" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1499" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1500" s="11" t="inlineStr">
+        <is>
+          <t>Почему тексты ChatGPT похожи друг на друга – и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1500" s="11" t="inlineStr">
+        <is>
+          <t>69df540500c2772fb2032d5f</t>
+        </is>
+      </c>
+      <c r="D1500" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1500" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1500" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1500" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1500" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1500" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1500" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1500" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1500" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1500" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1500" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1500" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1500" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1501" s="8" t="inlineStr">
+        <is>
+          <t>10 параметров конкурентного анализа, которые SMM обычно игнорирует</t>
+        </is>
+      </c>
+      <c r="C1501" s="8" t="inlineStr">
+        <is>
+          <t>69df3dcad323d73e835077bb</t>
+        </is>
+      </c>
+      <c r="D1501" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1501" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="F1501" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G1501" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1501" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1501" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1501" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1501" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1501" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1501" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1501" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1501" s="19" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="P1501" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1502" s="11" t="inlineStr">
+        <is>
+          <t>Стиль бренда в ИИ: как научить нейросеть писать «вашим голосом»</t>
+        </is>
+      </c>
+      <c r="C1502" s="11" t="inlineStr">
+        <is>
+          <t>69de331dfd89f7546881dcab</t>
+        </is>
+      </c>
+      <c r="D1502" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1502" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1502" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1502" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1502" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1502" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1502" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1502" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1502" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1502" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1502" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1502" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1502" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1503" s="8" t="inlineStr">
+        <is>
+          <t>Почему ИИ пишет «воду» — и как это исправить</t>
+        </is>
+      </c>
+      <c r="C1503" s="8" t="inlineStr">
+        <is>
+          <t>69de2664230a213955cde41d</t>
+        </is>
+      </c>
+      <c r="D1503" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1503" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1503" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1503" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1503" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1503" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1503" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1503" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1503" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1503" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1503" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1503" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1503" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1504" s="11" t="inlineStr">
+        <is>
+          <t>Слабые места конкурентов за 15 минут: 5 промптов для ИИ</t>
+        </is>
+      </c>
+      <c r="C1504" s="11" t="inlineStr">
+        <is>
+          <t>69de155bfec7647cbc3a7919</t>
+        </is>
+      </c>
+      <c r="D1504" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1504" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1504" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1504" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1504" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1504" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1504" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1504" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1504" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1504" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1504" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1504" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1504" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1505" s="8" t="inlineStr">
+        <is>
+          <t>Как настроить ИИ-агента один раз и анализировать конкурентов за 5 минут</t>
+        </is>
+      </c>
+      <c r="C1505" s="8" t="inlineStr">
+        <is>
+          <t>69de0b84d698251a58a64ac5</t>
+        </is>
+      </c>
+      <c r="D1505" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1505" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F1505" s="17" t="n">
+        <v>125</v>
+      </c>
+      <c r="G1505" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1505" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1505" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1505" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1505" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1505" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1505" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1505" s="29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O1505" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P1505" s="19" t="n">
+        <v>38.46</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1506" s="11" t="inlineStr">
+        <is>
+          <t>Как составить ToV-документ за один вечер: 4 промпта для нейросети</t>
+        </is>
+      </c>
+      <c r="C1506" s="11" t="inlineStr">
+        <is>
+          <t>69ddd20a7406736c715c268b</t>
+        </is>
+      </c>
+      <c r="D1506" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1506" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F1506" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1506" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1506" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1506" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1506" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1506" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1506" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1506" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1506" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O1506" s="23" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="P1506" s="23" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1507" s="8" t="inlineStr">
+        <is>
+          <t>Какой тип SEO выбрать для бизнеса в 2026 году</t>
+        </is>
+      </c>
+      <c r="C1507" s="8" t="inlineStr">
+        <is>
+          <t>69dcdff7d250b343c4e88fd3</t>
+        </is>
+      </c>
+      <c r="D1507" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1507" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1507" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1507" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1507" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1507" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1507" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1507" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1507" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1507" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1507" s="29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O1507" s="19" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="P1507" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1508" s="11" t="inlineStr">
+        <is>
+          <t>GPT vs Perplexity для маркетингового анализа: что выбрать?</t>
+        </is>
+      </c>
+      <c r="C1508" s="11" t="inlineStr">
+        <is>
+          <t>69d8de77ddcf6236004d848b</t>
+        </is>
+      </c>
+      <c r="D1508" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1508" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F1508" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="G1508" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1508" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1508" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1508" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1508" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1508" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1508" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1508" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1508" s="23" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="P1508" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1509" s="8" t="inlineStr">
+        <is>
+          <t>Как правильно писать запросы в нейронки: разбор 10 типичных ошибок</t>
+        </is>
+      </c>
+      <c r="C1509" s="8" t="inlineStr">
+        <is>
+          <t>69d8cf598f164c75fadda0c1</t>
+        </is>
+      </c>
+      <c r="D1509" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1509" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1509" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1509" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1509" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1509" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1509" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1509" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1509" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1509" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1509" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1509" s="19" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="P1509" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1510" s="11" t="inlineStr">
+        <is>
+          <t>Что такое Tone of Voice и почему без него ИИ пишет «ни для кого»</t>
+        </is>
+      </c>
+      <c r="C1510" s="11" t="inlineStr">
+        <is>
+          <t>69d8c9f1eb93124f5332b62e</t>
+        </is>
+      </c>
+      <c r="D1510" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1510" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="F1510" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1510" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1510" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1510" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1510" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1510" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1510" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1510" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1510" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1510" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1510" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1511" s="8" t="inlineStr">
+        <is>
+          <t>Как анализировать конкурентов в SMM: полный разбор с нуля</t>
+        </is>
+      </c>
+      <c r="C1511" s="8" t="inlineStr">
+        <is>
+          <t>69d8c0d88f409a0935cbf50a</t>
+        </is>
+      </c>
+      <c r="D1511" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1511" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1511" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1511" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1511" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1511" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1511" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1511" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1511" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1511" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1511" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1511" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1511" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1512" s="11" t="inlineStr">
+        <is>
+          <t>30 фраз, которые выдают текст ИИ с головой: полный список</t>
+        </is>
+      </c>
+      <c r="C1512" s="11" t="inlineStr">
+        <is>
+          <t>69d8a1f8dcf8776f14a5104f</t>
+        </is>
+      </c>
+      <c r="D1512" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1512" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="F1512" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1512" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="H1512" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="I1512" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="J1512" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1512" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1512" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1512" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1512" s="30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O1512" s="23" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P1512" s="23" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1513" s="8" t="inlineStr">
+        <is>
+          <t>Почему ChatGPT пишет «воду»: 5 причин, о которых никто не говорит</t>
+        </is>
+      </c>
+      <c r="C1513" s="8" t="inlineStr">
+        <is>
+          <t>69d88edffb6a431289545887</t>
+        </is>
+      </c>
+      <c r="D1513" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1513" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F1513" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1513" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1513" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1513" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1513" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1513" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1513" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1513" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1513" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O1513" s="19" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="P1513" s="19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1514" s="11" t="inlineStr">
+        <is>
+          <t>Тренды ИИ 2026: агенты под угрозой, дефицит мощностей и взрослая экономика роста</t>
+        </is>
+      </c>
+      <c r="C1514" s="11" t="inlineStr">
+        <is>
+          <t>69d5d97d4282c550d543e273</t>
+        </is>
+      </c>
+      <c r="D1514" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1514" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F1514" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1514" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1514" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1514" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1514" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1514" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1514" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1514" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1514" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O1514" s="23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P1514" s="23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1515" s="8" t="inlineStr">
+        <is>
+          <t>Где сейчас AI‑маркетинг и почему всё не так радужно</t>
+        </is>
+      </c>
+      <c r="C1515" s="8" t="inlineStr">
+        <is>
+          <t>69d4ecac2b46ec470ee469c5</t>
+        </is>
+      </c>
+      <c r="D1515" s="16" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="E1515" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F1515" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1515" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1515" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1515" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1515" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1515" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1515" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1515" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1515" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1515" s="19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P1515" s="19" t="n">
+        <v>16.67</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1516" s="11" t="inlineStr">
+        <is>
+          <t>ИИ в контент‑маркетинге: выигрывает не тот, кто просто пользуется ИИ</t>
+        </is>
+      </c>
+      <c r="C1516" s="11" t="inlineStr">
+        <is>
+          <t>69d4e2c6114bdd72c01e4631</t>
+        </i